--- a/workbooks/older_runs/unclassified_legacy/Baselines/baseline_fixeddefault.xlsx
+++ b/workbooks/older_runs/unclassified_legacy/Baselines/baseline_fixeddefault.xlsx
@@ -13788,10 +13788,10 @@
         </is>
       </c>
       <c r="F212" t="n">
-        <v>0.79</v>
+        <v>0.9</v>
       </c>
       <c r="G212" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H212" t="n">
         <v>0.74</v>
@@ -13800,7 +13800,7 @@
         <v>0.62</v>
       </c>
       <c r="J212" t="n">
-        <v>0.751</v>
+        <v>0.8330000000000001</v>
       </c>
       <c r="K212" t="n">
         <v>2</v>
@@ -13826,7 +13826,7 @@
         <v>3</v>
       </c>
       <c r="T212" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U212" t="inlineStr"/>
       <c r="V212" t="inlineStr"/>
@@ -13857,10 +13857,10 @@
         </is>
       </c>
       <c r="F213" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="G213" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H213" t="n">
         <v>0.89</v>
@@ -13869,7 +13869,7 @@
         <v>0.83</v>
       </c>
       <c r="J213" t="n">
-        <v>0.8485</v>
+        <v>0.9155</v>
       </c>
       <c r="K213" t="n">
         <v>1</v>
@@ -13895,7 +13895,7 @@
         <v>3</v>
       </c>
       <c r="T213" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U213" t="inlineStr"/>
       <c r="V213" t="inlineStr"/>
@@ -13926,10 +13926,10 @@
         </is>
       </c>
       <c r="F214" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="G214" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="H214" t="n">
         <v>0.18</v>
@@ -13938,7 +13938,7 @@
         <v>0.3</v>
       </c>
       <c r="J214" t="n">
-        <v>0.6305000000000001</v>
+        <v>0.6975000000000001</v>
       </c>
       <c r="K214" t="n">
         <v>3</v>
@@ -13964,7 +13964,7 @@
         <v>3</v>
       </c>
       <c r="T214" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U214" t="inlineStr"/>
       <c r="V214" t="inlineStr"/>
@@ -13995,10 +13995,10 @@
         </is>
       </c>
       <c r="F215" t="n">
-        <v>0.79</v>
+        <v>0.51</v>
       </c>
       <c r="G215" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H215" t="n">
         <v>1</v>
@@ -14007,7 +14007,7 @@
         <v>1</v>
       </c>
       <c r="J215" t="n">
-        <v>0.86</v>
+        <v>0.6535000000000001</v>
       </c>
       <c r="K215" t="n">
         <v>1</v>
@@ -14023,7 +14023,7 @@
       </c>
       <c r="Q215" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R215" t="n">
@@ -14033,7 +14033,7 @@
         <v>4</v>
       </c>
       <c r="T215" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U215" t="inlineStr"/>
       <c r="V215" t="inlineStr"/>
@@ -14064,22 +14064,22 @@
         </is>
       </c>
       <c r="F216" t="n">
-        <v>0.91</v>
+        <v>0.77</v>
       </c>
       <c r="G216" t="n">
-        <v>0.79</v>
+        <v>0.47</v>
       </c>
       <c r="H216" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="I216" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="J216" t="n">
-        <v>0.7404999999999999</v>
+        <v>0.583</v>
       </c>
       <c r="K216" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L216" t="inlineStr"/>
       <c r="M216" t="inlineStr"/>
@@ -14092,7 +14092,7 @@
       </c>
       <c r="Q216" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R216" t="n">
@@ -14102,7 +14102,7 @@
         <v>4</v>
       </c>
       <c r="T216" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U216" t="inlineStr"/>
       <c r="V216" t="inlineStr"/>
@@ -14133,22 +14133,22 @@
         </is>
       </c>
       <c r="F217" t="n">
-        <v>0.79</v>
+        <v>0.51</v>
       </c>
       <c r="G217" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H217" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="I217" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="J217" t="n">
-        <v>0.751</v>
+        <v>0.5395</v>
       </c>
       <c r="K217" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L217" t="inlineStr"/>
       <c r="M217" t="inlineStr"/>
@@ -14161,7 +14161,7 @@
       </c>
       <c r="Q217" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R217" t="n">
@@ -14171,7 +14171,7 @@
         <v>4</v>
       </c>
       <c r="T217" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U217" t="inlineStr"/>
       <c r="V217" t="inlineStr"/>
@@ -14208,16 +14208,16 @@
         <v>0.79</v>
       </c>
       <c r="H218" t="n">
-        <v>0.55</v>
+        <v>0.78</v>
       </c>
       <c r="I218" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="J218" t="n">
-        <v>0.742</v>
+        <v>0.791</v>
       </c>
       <c r="K218" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L218" t="inlineStr"/>
       <c r="M218" t="inlineStr"/>
@@ -14230,7 +14230,7 @@
       </c>
       <c r="Q218" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R218" t="n">
@@ -14277,16 +14277,16 @@
         <v>0.78</v>
       </c>
       <c r="H219" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="I219" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="J219" t="n">
-        <v>0.7595000000000001</v>
+        <v>0.7665000000000001</v>
       </c>
       <c r="K219" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L219" t="inlineStr"/>
       <c r="M219" t="inlineStr"/>
@@ -14299,7 +14299,7 @@
       </c>
       <c r="Q219" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R219" t="n">
@@ -14368,7 +14368,7 @@
       </c>
       <c r="Q220" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R220" t="n">
@@ -14409,10 +14409,10 @@
         </is>
       </c>
       <c r="F221" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="G221" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H221" t="n">
         <v>0.55</v>
@@ -14421,7 +14421,7 @@
         <v>0.39</v>
       </c>
       <c r="J221" t="n">
-        <v>0.7145</v>
+        <v>0.7815</v>
       </c>
       <c r="K221" t="n">
         <v>3</v>
@@ -14447,7 +14447,7 @@
         <v>3</v>
       </c>
       <c r="T221" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U221" t="inlineStr"/>
       <c r="V221" t="inlineStr"/>
@@ -14478,10 +14478,10 @@
         </is>
       </c>
       <c r="F222" t="n">
-        <v>0.79</v>
+        <v>0.9</v>
       </c>
       <c r="G222" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H222" t="n">
         <v>0.74</v>
@@ -14490,7 +14490,7 @@
         <v>0.62</v>
       </c>
       <c r="J222" t="n">
-        <v>0.751</v>
+        <v>0.8330000000000001</v>
       </c>
       <c r="K222" t="n">
         <v>2</v>
@@ -14516,7 +14516,7 @@
         <v>3</v>
       </c>
       <c r="T222" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U222" t="inlineStr"/>
       <c r="V222" t="inlineStr"/>
@@ -14547,10 +14547,10 @@
         </is>
       </c>
       <c r="F223" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="G223" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H223" t="n">
         <v>0.71</v>
@@ -14559,7 +14559,7 @@
         <v>0.66</v>
       </c>
       <c r="J223" t="n">
-        <v>0.787</v>
+        <v>0.854</v>
       </c>
       <c r="K223" t="n">
         <v>1</v>
@@ -14585,7 +14585,7 @@
         <v>3</v>
       </c>
       <c r="T223" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U223" t="inlineStr"/>
       <c r="V223" t="inlineStr"/>
@@ -14616,10 +14616,10 @@
         </is>
       </c>
       <c r="F224" t="n">
-        <v>0.79</v>
+        <v>0.51</v>
       </c>
       <c r="G224" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H224" t="n">
         <v>0.91</v>
@@ -14628,7 +14628,7 @@
         <v>0.85</v>
       </c>
       <c r="J224" t="n">
-        <v>0.8195000000000001</v>
+        <v>0.613</v>
       </c>
       <c r="K224" t="n">
         <v>1</v>
@@ -14644,7 +14644,7 @@
       </c>
       <c r="Q224" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R224" t="n">
@@ -14654,7 +14654,7 @@
         <v>2</v>
       </c>
       <c r="T224" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U224" t="inlineStr"/>
       <c r="V224" t="inlineStr"/>
@@ -14685,10 +14685,10 @@
         </is>
       </c>
       <c r="F225" t="n">
-        <v>0.79</v>
+        <v>0.51</v>
       </c>
       <c r="G225" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H225" t="n">
         <v>0.78</v>
@@ -14697,10 +14697,10 @@
         <v>0.67</v>
       </c>
       <c r="J225" t="n">
-        <v>0.7665000000000001</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K225" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L225" t="inlineStr"/>
       <c r="M225" t="inlineStr"/>
@@ -14713,7 +14713,7 @@
       </c>
       <c r="Q225" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R225" t="n">
@@ -14723,7 +14723,7 @@
         <v>2</v>
       </c>
       <c r="T225" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U225" t="inlineStr"/>
       <c r="V225" t="inlineStr"/>
@@ -14754,10 +14754,10 @@
         </is>
       </c>
       <c r="F226" t="n">
-        <v>0.91</v>
+        <v>0.77</v>
       </c>
       <c r="G226" t="n">
-        <v>0.79</v>
+        <v>0.47</v>
       </c>
       <c r="H226" t="n">
         <v>0.62</v>
@@ -14766,10 +14766,10 @@
         <v>0.62</v>
       </c>
       <c r="J226" t="n">
-        <v>0.7665</v>
+        <v>0.6124999999999999</v>
       </c>
       <c r="K226" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L226" t="inlineStr"/>
       <c r="M226" t="inlineStr"/>
@@ -14782,7 +14782,7 @@
       </c>
       <c r="Q226" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R226" t="n">
@@ -14792,7 +14792,7 @@
         <v>2</v>
       </c>
       <c r="T226" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U226" t="inlineStr"/>
       <c r="V226" t="inlineStr"/>
@@ -14823,10 +14823,10 @@
         </is>
       </c>
       <c r="F227" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="G227" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="H227" t="n">
         <v>0.33</v>
@@ -14835,7 +14835,7 @@
         <v>0.27</v>
       </c>
       <c r="J227" t="n">
-        <v>0.6559999999999999</v>
+        <v>0.7230000000000001</v>
       </c>
       <c r="K227" t="n">
         <v>3</v>
@@ -14861,7 +14861,7 @@
         <v>5</v>
       </c>
       <c r="T227" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U227" t="inlineStr"/>
       <c r="V227" t="inlineStr"/>
@@ -14892,10 +14892,10 @@
         </is>
       </c>
       <c r="F228" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="G228" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H228" t="n">
         <v>0.44</v>
@@ -14904,7 +14904,7 @@
         <v>0.25</v>
       </c>
       <c r="J228" t="n">
-        <v>0.6715</v>
+        <v>0.7384999999999999</v>
       </c>
       <c r="K228" t="n">
         <v>2</v>
@@ -14930,7 +14930,7 @@
         <v>5</v>
       </c>
       <c r="T228" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U228" t="inlineStr"/>
       <c r="V228" t="inlineStr"/>
@@ -14961,10 +14961,10 @@
         </is>
       </c>
       <c r="F229" t="n">
-        <v>0.79</v>
+        <v>0.9</v>
       </c>
       <c r="G229" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H229" t="n">
         <v>0.71</v>
@@ -14973,7 +14973,7 @@
         <v>0.58</v>
       </c>
       <c r="J229" t="n">
-        <v>0.739</v>
+        <v>0.8210000000000001</v>
       </c>
       <c r="K229" t="n">
         <v>1</v>
@@ -14999,7 +14999,7 @@
         <v>5</v>
       </c>
       <c r="T229" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U229" t="inlineStr"/>
       <c r="V229" t="inlineStr"/>
@@ -15030,22 +15030,22 @@
         </is>
       </c>
       <c r="F230" t="n">
-        <v>0.79</v>
+        <v>0.51</v>
       </c>
       <c r="G230" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H230" t="n">
         <v>0.78</v>
       </c>
-      <c r="H230" t="n">
-        <v>0.79</v>
-      </c>
       <c r="I230" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="J230" t="n">
-        <v>0.77</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K230" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L230" t="inlineStr"/>
       <c r="M230" t="inlineStr"/>
@@ -15058,7 +15058,7 @@
       </c>
       <c r="Q230" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R230" t="n">
@@ -15068,7 +15068,7 @@
         <v>4</v>
       </c>
       <c r="T230" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U230" t="inlineStr"/>
       <c r="V230" t="inlineStr"/>
@@ -15099,19 +15099,19 @@
         </is>
       </c>
       <c r="F231" t="n">
-        <v>0.79</v>
+        <v>0.51</v>
       </c>
       <c r="G231" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H231" t="n">
         <v>0.95</v>
       </c>
       <c r="I231" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="J231" t="n">
-        <v>0.838</v>
+        <v>0.63</v>
       </c>
       <c r="K231" t="n">
         <v>1</v>
@@ -15127,7 +15127,7 @@
       </c>
       <c r="Q231" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R231" t="n">
@@ -15137,7 +15137,7 @@
         <v>4</v>
       </c>
       <c r="T231" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U231" t="inlineStr"/>
       <c r="V231" t="inlineStr"/>
@@ -15168,22 +15168,22 @@
         </is>
       </c>
       <c r="F232" t="n">
-        <v>0.91</v>
+        <v>0.77</v>
       </c>
       <c r="G232" t="n">
-        <v>0.79</v>
+        <v>0.47</v>
       </c>
       <c r="H232" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="I232" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="J232" t="n">
-        <v>0.7524999999999999</v>
+        <v>0.595</v>
       </c>
       <c r="K232" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L232" t="inlineStr"/>
       <c r="M232" t="inlineStr"/>
@@ -15196,7 +15196,7 @@
       </c>
       <c r="Q232" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R232" t="n">
@@ -15206,7 +15206,7 @@
         <v>4</v>
       </c>
       <c r="T232" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U232" t="inlineStr"/>
       <c r="V232" t="inlineStr"/>
@@ -15243,13 +15243,13 @@
         <v>0.78</v>
       </c>
       <c r="H233" t="n">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="I233" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="J233" t="n">
-        <v>0.736</v>
+        <v>0.743</v>
       </c>
       <c r="K233" t="n">
         <v>3</v>
@@ -15265,7 +15265,7 @@
       </c>
       <c r="Q233" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R233" t="n">
@@ -15312,16 +15312,16 @@
         <v>0.78</v>
       </c>
       <c r="H234" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="I234" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J234" t="n">
-        <v>0.755</v>
+        <v>0.7585000000000001</v>
       </c>
       <c r="K234" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L234" t="inlineStr"/>
       <c r="M234" t="inlineStr"/>
@@ -15334,7 +15334,7 @@
       </c>
       <c r="Q234" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R234" t="n">
@@ -15381,16 +15381,16 @@
         <v>0.79</v>
       </c>
       <c r="H235" t="n">
-        <v>0.58</v>
+        <v>0.8</v>
       </c>
       <c r="I235" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="J235" t="n">
-        <v>0.7464999999999999</v>
+        <v>0.792</v>
       </c>
       <c r="K235" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L235" t="inlineStr"/>
       <c r="M235" t="inlineStr"/>
@@ -15403,7 +15403,7 @@
       </c>
       <c r="Q235" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R235" t="n">
@@ -15444,19 +15444,19 @@
         </is>
       </c>
       <c r="F236" t="n">
-        <v>0.57</v>
+        <v>0.06</v>
       </c>
       <c r="G236" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H236" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="I236" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="J236" t="n">
-        <v>0.6849999999999999</v>
+        <v>0.4045</v>
       </c>
       <c r="K236" t="n">
         <v>3</v>
@@ -15472,7 +15472,7 @@
       </c>
       <c r="Q236" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R236" t="n">
@@ -15482,7 +15482,7 @@
         <v>3</v>
       </c>
       <c r="T236" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U236" t="inlineStr"/>
       <c r="V236" t="inlineStr"/>
@@ -15513,19 +15513,19 @@
         </is>
       </c>
       <c r="F237" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="G237" t="n">
-        <v>0.79</v>
+        <v>0.47</v>
       </c>
       <c r="H237" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="I237" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="J237" t="n">
-        <v>0.7585</v>
+        <v>0.604</v>
       </c>
       <c r="K237" t="n">
         <v>2</v>
@@ -15541,7 +15541,7 @@
       </c>
       <c r="Q237" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R237" t="n">
@@ -15551,7 +15551,7 @@
         <v>3</v>
       </c>
       <c r="T237" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U237" t="inlineStr"/>
       <c r="V237" t="inlineStr"/>
@@ -15582,10 +15582,10 @@
         </is>
       </c>
       <c r="F238" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="G238" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H238" t="n">
         <v>1</v>
@@ -15594,7 +15594,7 @@
         <v>1</v>
       </c>
       <c r="J238" t="n">
-        <v>0.902</v>
+        <v>0.7405</v>
       </c>
       <c r="K238" t="n">
         <v>1</v>
@@ -15610,7 +15610,7 @@
       </c>
       <c r="Q238" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R238" t="n">
@@ -15620,7 +15620,7 @@
         <v>3</v>
       </c>
       <c r="T238" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U238" t="inlineStr"/>
       <c r="V238" t="inlineStr"/>
@@ -15679,7 +15679,7 @@
       </c>
       <c r="Q239" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R239" t="n">
@@ -15726,13 +15726,13 @@
         <v>0.78</v>
       </c>
       <c r="H240" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="I240" t="n">
         <v>0.83</v>
       </c>
       <c r="J240" t="n">
-        <v>0.7464999999999999</v>
+        <v>0.7484999999999999</v>
       </c>
       <c r="K240" t="n">
         <v>2</v>
@@ -15748,7 +15748,7 @@
       </c>
       <c r="Q240" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R240" t="n">
@@ -15795,13 +15795,13 @@
         <v>0.78</v>
       </c>
       <c r="H241" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="I241" t="n">
         <v>0.76</v>
       </c>
       <c r="J241" t="n">
-        <v>0.726</v>
+        <v>0.728</v>
       </c>
       <c r="K241" t="n">
         <v>3</v>
@@ -15817,7 +15817,7 @@
       </c>
       <c r="Q241" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R241" t="n">
@@ -15886,7 +15886,7 @@
       </c>
       <c r="Q242" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R242" t="n">
@@ -15933,13 +15933,13 @@
         <v>0.78</v>
       </c>
       <c r="H243" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="I243" t="n">
         <v>0.83</v>
       </c>
       <c r="J243" t="n">
-        <v>0.8274999999999999</v>
+        <v>0.8294999999999999</v>
       </c>
       <c r="K243" t="n">
         <v>2</v>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="Q243" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R243" t="n">
@@ -16002,13 +16002,13 @@
         <v>0.79</v>
       </c>
       <c r="H244" t="n">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="I244" t="n">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="J244" t="n">
-        <v>0.6875</v>
+        <v>0.7245</v>
       </c>
       <c r="K244" t="n">
         <v>3</v>
@@ -16024,7 +16024,7 @@
       </c>
       <c r="Q244" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R244" t="n">
@@ -16065,10 +16065,10 @@
         </is>
       </c>
       <c r="F245" t="n">
-        <v>0.57</v>
+        <v>0.78</v>
       </c>
       <c r="G245" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H245" t="n">
         <v>0.74</v>
@@ -16077,7 +16077,7 @@
         <v>0.62</v>
       </c>
       <c r="J245" t="n">
-        <v>0.6849999999999999</v>
+        <v>0.797</v>
       </c>
       <c r="K245" t="n">
         <v>2</v>
@@ -16103,7 +16103,7 @@
         <v>3</v>
       </c>
       <c r="T245" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U245" t="inlineStr"/>
       <c r="V245" t="inlineStr"/>
@@ -16134,10 +16134,10 @@
         </is>
       </c>
       <c r="F246" t="n">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
       <c r="G246" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H246" t="n">
         <v>0.58</v>
@@ -16146,7 +16146,7 @@
         <v>0.66</v>
       </c>
       <c r="J246" t="n">
-        <v>0.767</v>
+        <v>0.831</v>
       </c>
       <c r="K246" t="n">
         <v>1</v>
@@ -16172,7 +16172,7 @@
         <v>3</v>
       </c>
       <c r="T246" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U246" t="inlineStr"/>
       <c r="V246" t="inlineStr"/>
@@ -16203,10 +16203,10 @@
         </is>
       </c>
       <c r="F247" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G247" t="n">
         <v>0.93</v>
-      </c>
-      <c r="G247" t="n">
-        <v>0.79</v>
       </c>
       <c r="H247" t="n">
         <v>0.39</v>
@@ -16215,7 +16215,7 @@
         <v>0.34</v>
       </c>
       <c r="J247" t="n">
-        <v>0.6845</v>
+        <v>0.7485000000000001</v>
       </c>
       <c r="K247" t="n">
         <v>3</v>
@@ -16241,7 +16241,7 @@
         <v>3</v>
       </c>
       <c r="T247" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U247" t="inlineStr"/>
       <c r="V247" t="inlineStr"/>
@@ -16272,22 +16272,22 @@
         </is>
       </c>
       <c r="F248" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="G248" t="n">
-        <v>0.79</v>
+        <v>0.47</v>
       </c>
       <c r="H248" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="I248" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="J248" t="n">
-        <v>0.6985</v>
+        <v>0.539</v>
       </c>
       <c r="K248" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L248" t="inlineStr"/>
       <c r="M248" t="inlineStr"/>
@@ -16300,7 +16300,7 @@
       </c>
       <c r="Q248" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R248" t="n">
@@ -16310,7 +16310,7 @@
         <v>4</v>
       </c>
       <c r="T248" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U248" t="inlineStr"/>
       <c r="V248" t="inlineStr"/>
@@ -16341,22 +16341,22 @@
         </is>
       </c>
       <c r="F249" t="n">
-        <v>0.57</v>
+        <v>0.06</v>
       </c>
       <c r="G249" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H249" t="n">
         <v>0.78</v>
       </c>
-      <c r="H249" t="n">
-        <v>0.79</v>
-      </c>
       <c r="I249" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="J249" t="n">
-        <v>0.704</v>
+        <v>0.425</v>
       </c>
       <c r="K249" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L249" t="inlineStr"/>
       <c r="M249" t="inlineStr"/>
@@ -16369,7 +16369,7 @@
       </c>
       <c r="Q249" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R249" t="n">
@@ -16379,7 +16379,7 @@
         <v>4</v>
       </c>
       <c r="T249" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U249" t="inlineStr"/>
       <c r="V249" t="inlineStr"/>
@@ -16410,19 +16410,19 @@
         </is>
       </c>
       <c r="F250" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="G250" t="n">
-        <v>0.79</v>
+        <v>0.47</v>
       </c>
       <c r="H250" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="I250" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="J250" t="n">
-        <v>0.7585</v>
+        <v>0.604</v>
       </c>
       <c r="K250" t="n">
         <v>1</v>
@@ -16438,7 +16438,7 @@
       </c>
       <c r="Q250" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R250" t="n">
@@ -16448,7 +16448,7 @@
         <v>4</v>
       </c>
       <c r="T250" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U250" t="inlineStr"/>
       <c r="V250" t="inlineStr"/>
@@ -16479,22 +16479,22 @@
         </is>
       </c>
       <c r="F251" t="n">
-        <v>0.57</v>
+        <v>0.06</v>
       </c>
       <c r="G251" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H251" t="n">
         <v>0.78</v>
       </c>
-      <c r="H251" t="n">
-        <v>0.79</v>
-      </c>
       <c r="I251" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="J251" t="n">
-        <v>0.704</v>
+        <v>0.425</v>
       </c>
       <c r="K251" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L251" t="inlineStr"/>
       <c r="M251" t="inlineStr"/>
@@ -16507,7 +16507,7 @@
       </c>
       <c r="Q251" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R251" t="n">
@@ -16517,7 +16517,7 @@
         <v>3</v>
       </c>
       <c r="T251" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U251" t="inlineStr"/>
       <c r="V251" t="inlineStr"/>
@@ -16548,19 +16548,19 @@
         </is>
       </c>
       <c r="F252" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="G252" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H252" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="I252" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="J252" t="n">
-        <v>0.767</v>
+        <v>0.602</v>
       </c>
       <c r="K252" t="n">
         <v>1</v>
@@ -16576,7 +16576,7 @@
       </c>
       <c r="Q252" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R252" t="n">
@@ -16586,7 +16586,7 @@
         <v>3</v>
       </c>
       <c r="T252" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U252" t="inlineStr"/>
       <c r="V252" t="inlineStr"/>
@@ -16617,10 +16617,10 @@
         </is>
       </c>
       <c r="F253" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="G253" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H253" t="n">
         <v>0.47</v>
@@ -16629,10 +16629,10 @@
         <v>0.3</v>
       </c>
       <c r="J253" t="n">
-        <v>0.6910000000000001</v>
+        <v>0.5295</v>
       </c>
       <c r="K253" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L253" t="inlineStr"/>
       <c r="M253" t="inlineStr"/>
@@ -16645,7 +16645,7 @@
       </c>
       <c r="Q253" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R253" t="n">
@@ -16655,7 +16655,7 @@
         <v>3</v>
       </c>
       <c r="T253" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U253" t="inlineStr"/>
       <c r="V253" t="inlineStr"/>
@@ -16692,16 +16692,16 @@
         <v>0.78</v>
       </c>
       <c r="H254" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="I254" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="J254" t="n">
-        <v>0.8015000000000001</v>
+        <v>0.805</v>
       </c>
       <c r="K254" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L254" t="inlineStr"/>
       <c r="M254" t="inlineStr"/>
@@ -16714,7 +16714,7 @@
       </c>
       <c r="Q254" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R254" t="n">
@@ -16761,13 +16761,13 @@
         <v>0.78</v>
       </c>
       <c r="H255" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="I255" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
       <c r="J255" t="n">
-        <v>0.733</v>
+        <v>0.7415</v>
       </c>
       <c r="K255" t="n">
         <v>3</v>
@@ -16783,7 +16783,7 @@
       </c>
       <c r="Q255" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R255" t="n">
@@ -16830,16 +16830,16 @@
         <v>0.78</v>
       </c>
       <c r="H256" t="n">
-        <v>0.61</v>
+        <v>0.83</v>
       </c>
       <c r="I256" t="n">
-        <v>0.64</v>
+        <v>0.66</v>
       </c>
       <c r="J256" t="n">
-        <v>0.7609999999999999</v>
+        <v>0.8079999999999999</v>
       </c>
       <c r="K256" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L256" t="inlineStr"/>
       <c r="M256" t="inlineStr"/>
@@ -16852,7 +16852,7 @@
       </c>
       <c r="Q256" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R256" t="n">
@@ -16893,10 +16893,10 @@
         </is>
       </c>
       <c r="F257" t="n">
-        <v>0.84</v>
+        <v>0.93</v>
       </c>
       <c r="G257" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="H257" t="n">
         <v>0.62</v>
@@ -16905,7 +16905,7 @@
         <v>0.55</v>
       </c>
       <c r="J257" t="n">
-        <v>0.735</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="K257" t="n">
         <v>3</v>
@@ -16931,7 +16931,7 @@
         <v>5</v>
       </c>
       <c r="T257" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U257" t="inlineStr"/>
       <c r="V257" t="inlineStr"/>
@@ -16962,10 +16962,10 @@
         </is>
       </c>
       <c r="F258" t="n">
-        <v>0.84</v>
+        <v>0.93</v>
       </c>
       <c r="G258" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H258" t="n">
         <v>0.76</v>
@@ -16974,7 +16974,7 @@
         <v>0.65</v>
       </c>
       <c r="J258" t="n">
-        <v>0.7745</v>
+        <v>0.8505</v>
       </c>
       <c r="K258" t="n">
         <v>2</v>
@@ -17000,7 +17000,7 @@
         <v>5</v>
       </c>
       <c r="T258" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U258" t="inlineStr"/>
       <c r="V258" t="inlineStr"/>
@@ -17031,10 +17031,10 @@
         </is>
       </c>
       <c r="F259" t="n">
-        <v>0.84</v>
+        <v>0.93</v>
       </c>
       <c r="G259" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H259" t="n">
         <v>0.88</v>
@@ -17043,7 +17043,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="J259" t="n">
-        <v>0.8225</v>
+        <v>0.8985000000000001</v>
       </c>
       <c r="K259" t="n">
         <v>1</v>
@@ -17069,7 +17069,7 @@
         <v>5</v>
       </c>
       <c r="T259" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U259" t="inlineStr"/>
       <c r="V259" t="inlineStr"/>
@@ -17100,10 +17100,10 @@
         </is>
       </c>
       <c r="F260" t="n">
-        <v>0.77</v>
+        <v>0.89</v>
       </c>
       <c r="G260" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H260" t="n">
         <v>0.89</v>
@@ -17112,7 +17112,7 @@
         <v>0.83</v>
       </c>
       <c r="J260" t="n">
-        <v>0.8065</v>
+        <v>0.8915</v>
       </c>
       <c r="K260" t="n">
         <v>2</v>
@@ -17138,7 +17138,7 @@
         <v>3</v>
       </c>
       <c r="T260" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U260" t="inlineStr"/>
       <c r="V260" t="inlineStr"/>
@@ -17169,10 +17169,10 @@
         </is>
       </c>
       <c r="F261" t="n">
-        <v>0.77</v>
+        <v>0.89</v>
       </c>
       <c r="G261" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H261" t="n">
         <v>0.74</v>
@@ -17181,7 +17181,7 @@
         <v>0.62</v>
       </c>
       <c r="J261" t="n">
-        <v>0.745</v>
+        <v>0.83</v>
       </c>
       <c r="K261" t="n">
         <v>3</v>
@@ -17207,7 +17207,7 @@
         <v>3</v>
       </c>
       <c r="T261" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U261" t="inlineStr"/>
       <c r="V261" t="inlineStr"/>
@@ -17238,10 +17238,10 @@
         </is>
       </c>
       <c r="F262" t="n">
-        <v>0.9</v>
+        <v>0.96</v>
       </c>
       <c r="G262" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H262" t="n">
         <v>0.89</v>
@@ -17250,7 +17250,7 @@
         <v>0.83</v>
       </c>
       <c r="J262" t="n">
-        <v>0.8454999999999999</v>
+        <v>0.9125</v>
       </c>
       <c r="K262" t="n">
         <v>1</v>
@@ -17276,7 +17276,7 @@
         <v>3</v>
       </c>
       <c r="T262" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U262" t="inlineStr"/>
       <c r="V262" t="inlineStr"/>
@@ -17307,22 +17307,22 @@
         </is>
       </c>
       <c r="F263" t="n">
-        <v>0.77</v>
+        <v>0.47</v>
       </c>
       <c r="G263" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H263" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="I263" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="J263" t="n">
-        <v>0.786</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="K263" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L263" t="inlineStr"/>
       <c r="M263" t="inlineStr"/>
@@ -17335,7 +17335,7 @@
       </c>
       <c r="Q263" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R263" t="n">
@@ -17345,7 +17345,7 @@
         <v>3</v>
       </c>
       <c r="T263" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U263" t="inlineStr"/>
       <c r="V263" t="inlineStr"/>
@@ -17376,19 +17376,19 @@
         </is>
       </c>
       <c r="F264" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="G264" t="n">
-        <v>0.79</v>
+        <v>0.47</v>
       </c>
       <c r="H264" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="I264" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="J264" t="n">
-        <v>0.7055</v>
+        <v>0.5399999999999999</v>
       </c>
       <c r="K264" t="n">
         <v>3</v>
@@ -17404,7 +17404,7 @@
       </c>
       <c r="Q264" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R264" t="n">
@@ -17414,7 +17414,7 @@
         <v>3</v>
       </c>
       <c r="T264" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U264" t="inlineStr"/>
       <c r="V264" t="inlineStr"/>
@@ -17445,22 +17445,22 @@
         </is>
       </c>
       <c r="F265" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="G265" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H265" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="I265" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="J265" t="n">
-        <v>0.7839999999999999</v>
+        <v>0.613</v>
       </c>
       <c r="K265" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L265" t="inlineStr"/>
       <c r="M265" t="inlineStr"/>
@@ -17473,7 +17473,7 @@
       </c>
       <c r="Q265" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R265" t="n">
@@ -17483,7 +17483,7 @@
         <v>3</v>
       </c>
       <c r="T265" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U265" t="inlineStr"/>
       <c r="V265" t="inlineStr"/>
@@ -17514,10 +17514,10 @@
         </is>
       </c>
       <c r="F266" t="n">
-        <v>0.77</v>
+        <v>0.89</v>
       </c>
       <c r="G266" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H266" t="n">
         <v>0.84</v>
@@ -17526,7 +17526,7 @@
         <v>0.76</v>
       </c>
       <c r="J266" t="n">
-        <v>0.786</v>
+        <v>0.871</v>
       </c>
       <c r="K266" t="n">
         <v>2</v>
@@ -17552,7 +17552,7 @@
         <v>4</v>
       </c>
       <c r="T266" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U266" t="inlineStr"/>
       <c r="V266" t="inlineStr"/>
@@ -17583,10 +17583,10 @@
         </is>
       </c>
       <c r="F267" t="n">
-        <v>0.9</v>
+        <v>0.96</v>
       </c>
       <c r="G267" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H267" t="n">
         <v>0.64</v>
@@ -17595,7 +17595,7 @@
         <v>0.5</v>
       </c>
       <c r="J267" t="n">
-        <v>0.7459999999999999</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="K267" t="n">
         <v>3</v>
@@ -17621,7 +17621,7 @@
         <v>4</v>
       </c>
       <c r="T267" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U267" t="inlineStr"/>
       <c r="V267" t="inlineStr"/>
@@ -17652,10 +17652,10 @@
         </is>
       </c>
       <c r="F268" t="n">
-        <v>0.9</v>
+        <v>0.96</v>
       </c>
       <c r="G268" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H268" t="n">
         <v>0.89</v>
@@ -17664,7 +17664,7 @@
         <v>0.83</v>
       </c>
       <c r="J268" t="n">
-        <v>0.8454999999999999</v>
+        <v>0.9125</v>
       </c>
       <c r="K268" t="n">
         <v>1</v>
@@ -17690,7 +17690,7 @@
         <v>4</v>
       </c>
       <c r="T268" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U268" t="inlineStr"/>
       <c r="V268" t="inlineStr"/>
@@ -17749,7 +17749,7 @@
       </c>
       <c r="Q269" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R269" t="n">
@@ -17796,13 +17796,13 @@
         <v>0.79</v>
       </c>
       <c r="H270" t="n">
-        <v>0.52</v>
+        <v>0.74</v>
       </c>
       <c r="I270" t="n">
         <v>0.41</v>
       </c>
       <c r="J270" t="n">
-        <v>0.709</v>
+        <v>0.753</v>
       </c>
       <c r="K270" t="n">
         <v>3</v>
@@ -17818,7 +17818,7 @@
       </c>
       <c r="Q270" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R270" t="n">
@@ -17887,7 +17887,7 @@
       </c>
       <c r="Q271" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R271" t="n">
@@ -17928,10 +17928,10 @@
         </is>
       </c>
       <c r="F272" t="n">
-        <v>0.74</v>
+        <v>0.87</v>
       </c>
       <c r="G272" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H272" t="n">
         <v>1</v>
@@ -17940,7 +17940,7 @@
         <v>1</v>
       </c>
       <c r="J272" t="n">
-        <v>0.8450000000000001</v>
+        <v>0.9329999999999999</v>
       </c>
       <c r="K272" t="n">
         <v>1</v>
@@ -17966,7 +17966,7 @@
         <v>3</v>
       </c>
       <c r="T272" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U272" t="inlineStr"/>
       <c r="V272" t="inlineStr"/>
@@ -17997,10 +17997,10 @@
         </is>
       </c>
       <c r="F273" t="n">
-        <v>0.74</v>
+        <v>0.87</v>
       </c>
       <c r="G273" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H273" t="n">
         <v>0.74</v>
@@ -18009,7 +18009,7 @@
         <v>0.62</v>
       </c>
       <c r="J273" t="n">
-        <v>0.736</v>
+        <v>0.824</v>
       </c>
       <c r="K273" t="n">
         <v>2</v>
@@ -18035,7 +18035,7 @@
         <v>3</v>
       </c>
       <c r="T273" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U273" t="inlineStr"/>
       <c r="V273" t="inlineStr"/>
@@ -18066,10 +18066,10 @@
         </is>
       </c>
       <c r="F274" t="n">
-        <v>0.89</v>
+        <v>0.96</v>
       </c>
       <c r="G274" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="H274" t="n">
         <v>0.54</v>
@@ -18078,7 +18078,7 @@
         <v>0.34</v>
       </c>
       <c r="J274" t="n">
-        <v>0.7025</v>
+        <v>0.7725</v>
       </c>
       <c r="K274" t="n">
         <v>3</v>
@@ -18104,7 +18104,7 @@
         <v>3</v>
       </c>
       <c r="T274" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U274" t="inlineStr"/>
       <c r="V274" t="inlineStr"/>
@@ -18135,22 +18135,22 @@
         </is>
       </c>
       <c r="F275" t="n">
-        <v>0.74</v>
+        <v>0.41</v>
       </c>
       <c r="G275" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H275" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="I275" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="J275" t="n">
-        <v>0.7925</v>
+        <v>0.5675</v>
       </c>
       <c r="K275" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L275" t="inlineStr"/>
       <c r="M275" t="inlineStr"/>
@@ -18163,7 +18163,7 @@
       </c>
       <c r="Q275" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R275" t="n">
@@ -18173,7 +18173,7 @@
         <v>5</v>
       </c>
       <c r="T275" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U275" t="inlineStr"/>
       <c r="V275" t="inlineStr"/>
@@ -18204,22 +18204,22 @@
         </is>
       </c>
       <c r="F276" t="n">
-        <v>0.89</v>
+        <v>0.73</v>
       </c>
       <c r="G276" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H276" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
       <c r="I276" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="J276" t="n">
-        <v>0.758</v>
+        <v>0.5825</v>
       </c>
       <c r="K276" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L276" t="inlineStr"/>
       <c r="M276" t="inlineStr"/>
@@ -18232,7 +18232,7 @@
       </c>
       <c r="Q276" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R276" t="n">
@@ -18242,7 +18242,7 @@
         <v>5</v>
       </c>
       <c r="T276" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U276" t="inlineStr"/>
       <c r="V276" t="inlineStr"/>
@@ -18273,19 +18273,19 @@
         </is>
       </c>
       <c r="F277" t="n">
-        <v>0.89</v>
+        <v>0.73</v>
       </c>
       <c r="G277" t="n">
-        <v>0.79</v>
+        <v>0.47</v>
       </c>
       <c r="H277" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="I277" t="n">
-        <v>0.27</v>
+        <v>0.22</v>
       </c>
       <c r="J277" t="n">
-        <v>0.6639999999999999</v>
+        <v>0.4884999999999999</v>
       </c>
       <c r="K277" t="n">
         <v>3</v>
@@ -18301,7 +18301,7 @@
       </c>
       <c r="Q277" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R277" t="n">
@@ -18311,7 +18311,7 @@
         <v>5</v>
       </c>
       <c r="T277" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U277" t="inlineStr"/>
       <c r="V277" t="inlineStr"/>
@@ -18342,22 +18342,22 @@
         </is>
       </c>
       <c r="F278" t="n">
-        <v>0.57</v>
+        <v>0.06</v>
       </c>
       <c r="G278" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H278" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="I278" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="J278" t="n">
-        <v>0.726</v>
+        <v>0.447</v>
       </c>
       <c r="K278" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L278" t="inlineStr"/>
       <c r="M278" t="inlineStr"/>
@@ -18370,7 +18370,7 @@
       </c>
       <c r="Q278" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R278" t="n">
@@ -18380,7 +18380,7 @@
         <v>4</v>
       </c>
       <c r="T278" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U278" t="inlineStr"/>
       <c r="V278" t="inlineStr"/>
@@ -18411,19 +18411,19 @@
         </is>
       </c>
       <c r="F279" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="G279" t="n">
-        <v>0.79</v>
+        <v>0.47</v>
       </c>
       <c r="H279" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="I279" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="J279" t="n">
-        <v>0.7464999999999999</v>
+        <v>0.592</v>
       </c>
       <c r="K279" t="n">
         <v>1</v>
@@ -18439,7 +18439,7 @@
       </c>
       <c r="Q279" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R279" t="n">
@@ -18449,7 +18449,7 @@
         <v>4</v>
       </c>
       <c r="T279" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U279" t="inlineStr"/>
       <c r="V279" t="inlineStr"/>
@@ -18480,10 +18480,10 @@
         </is>
       </c>
       <c r="F280" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="G280" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H280" t="n">
         <v>0.51</v>
@@ -18492,10 +18492,10 @@
         <v>0.34</v>
       </c>
       <c r="J280" t="n">
-        <v>0.7050000000000001</v>
+        <v>0.5435</v>
       </c>
       <c r="K280" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L280" t="inlineStr"/>
       <c r="M280" t="inlineStr"/>
@@ -18508,7 +18508,7 @@
       </c>
       <c r="Q280" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R280" t="n">
@@ -18518,7 +18518,7 @@
         <v>4</v>
       </c>
       <c r="T280" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U280" t="inlineStr"/>
       <c r="V280" t="inlineStr"/>
@@ -18555,16 +18555,16 @@
         <v>0.78</v>
       </c>
       <c r="H281" t="n">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="I281" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="J281" t="n">
-        <v>0.7659999999999999</v>
+        <v>0.7729999999999999</v>
       </c>
       <c r="K281" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L281" t="inlineStr"/>
       <c r="M281" t="inlineStr"/>
@@ -18577,7 +18577,7 @@
       </c>
       <c r="Q281" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R281" t="n">
@@ -18624,13 +18624,13 @@
         <v>0.79</v>
       </c>
       <c r="H282" t="n">
-        <v>0.46</v>
+        <v>0.76</v>
       </c>
       <c r="I282" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="J282" t="n">
-        <v>0.6819999999999999</v>
+        <v>0.745</v>
       </c>
       <c r="K282" t="n">
         <v>3</v>
@@ -18646,7 +18646,7 @@
       </c>
       <c r="Q282" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R282" t="n">
@@ -18693,16 +18693,16 @@
         <v>0.79</v>
       </c>
       <c r="H283" t="n">
-        <v>0.52</v>
+        <v>0.8</v>
       </c>
       <c r="I283" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="J283" t="n">
-        <v>0.7194999999999999</v>
+        <v>0.777</v>
       </c>
       <c r="K283" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L283" t="inlineStr"/>
       <c r="M283" t="inlineStr"/>
@@ -18715,7 +18715,7 @@
       </c>
       <c r="Q283" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R283" t="n">
@@ -18756,19 +18756,19 @@
         </is>
       </c>
       <c r="F284" t="n">
-        <v>0.84</v>
+        <v>0.61</v>
       </c>
       <c r="G284" t="n">
-        <v>0.79</v>
+        <v>0.47</v>
       </c>
       <c r="H284" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="I284" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="J284" t="n">
-        <v>0.6715</v>
+        <v>0.482</v>
       </c>
       <c r="K284" t="n">
         <v>3</v>
@@ -18784,7 +18784,7 @@
       </c>
       <c r="Q284" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R284" t="n">
@@ -18794,7 +18794,7 @@
         <v>4</v>
       </c>
       <c r="T284" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U284" t="inlineStr"/>
       <c r="V284" t="inlineStr"/>
@@ -18825,19 +18825,19 @@
         </is>
       </c>
       <c r="F285" t="n">
-        <v>0.84</v>
+        <v>0.61</v>
       </c>
       <c r="G285" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H285" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="I285" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="J285" t="n">
-        <v>0.7659999999999999</v>
+        <v>0.5695</v>
       </c>
       <c r="K285" t="n">
         <v>2</v>
@@ -18853,7 +18853,7 @@
       </c>
       <c r="Q285" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R285" t="n">
@@ -18863,7 +18863,7 @@
         <v>4</v>
       </c>
       <c r="T285" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U285" t="inlineStr"/>
       <c r="V285" t="inlineStr"/>
@@ -18894,19 +18894,19 @@
         </is>
       </c>
       <c r="F286" t="n">
-        <v>0.84</v>
+        <v>0.61</v>
       </c>
       <c r="G286" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H286" t="n">
         <v>0.95</v>
       </c>
       <c r="I286" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="J286" t="n">
-        <v>0.8529999999999999</v>
+        <v>0.6600000000000001</v>
       </c>
       <c r="K286" t="n">
         <v>1</v>
@@ -18922,7 +18922,7 @@
       </c>
       <c r="Q286" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R286" t="n">
@@ -18932,7 +18932,7 @@
         <v>4</v>
       </c>
       <c r="T286" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U286" t="inlineStr"/>
       <c r="V286" t="inlineStr"/>
@@ -18963,10 +18963,10 @@
         </is>
       </c>
       <c r="F287" t="n">
-        <v>0.84</v>
+        <v>0.93</v>
       </c>
       <c r="G287" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H287" t="n">
         <v>0.95</v>
@@ -18975,7 +18975,7 @@
         <v>0.92</v>
       </c>
       <c r="J287" t="n">
-        <v>0.8529999999999999</v>
+        <v>0.9289999999999999</v>
       </c>
       <c r="K287" t="n">
         <v>1</v>
@@ -19001,7 +19001,7 @@
         <v>3</v>
       </c>
       <c r="T287" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U287" t="inlineStr"/>
       <c r="V287" t="inlineStr"/>
@@ -19032,10 +19032,10 @@
         </is>
       </c>
       <c r="F288" t="n">
-        <v>0.84</v>
+        <v>0.93</v>
       </c>
       <c r="G288" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H288" t="n">
         <v>0.55</v>
@@ -19044,7 +19044,7 @@
         <v>0.39</v>
       </c>
       <c r="J288" t="n">
-        <v>0.6934999999999999</v>
+        <v>0.7695</v>
       </c>
       <c r="K288" t="n">
         <v>3</v>
@@ -19070,7 +19070,7 @@
         <v>3</v>
       </c>
       <c r="T288" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U288" t="inlineStr"/>
       <c r="V288" t="inlineStr"/>
@@ -19101,10 +19101,10 @@
         </is>
       </c>
       <c r="F289" t="n">
-        <v>0.84</v>
+        <v>0.93</v>
       </c>
       <c r="G289" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H289" t="n">
         <v>0.84</v>
@@ -19113,7 +19113,7 @@
         <v>0.76</v>
       </c>
       <c r="J289" t="n">
-        <v>0.8069999999999999</v>
+        <v>0.883</v>
       </c>
       <c r="K289" t="n">
         <v>2</v>
@@ -19139,7 +19139,7 @@
         <v>3</v>
       </c>
       <c r="T289" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U289" t="inlineStr"/>
       <c r="V289" t="inlineStr"/>
@@ -19170,22 +19170,22 @@
         </is>
       </c>
       <c r="F290" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="G290" t="n">
-        <v>0.79</v>
+        <v>0.47</v>
       </c>
       <c r="H290" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="I290" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="J290" t="n">
-        <v>0.6985</v>
+        <v>0.539</v>
       </c>
       <c r="K290" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L290" t="inlineStr"/>
       <c r="M290" t="inlineStr"/>
@@ -19198,7 +19198,7 @@
       </c>
       <c r="Q290" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R290" t="n">
@@ -19208,7 +19208,7 @@
         <v>3</v>
       </c>
       <c r="T290" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U290" t="inlineStr"/>
       <c r="V290" t="inlineStr"/>
@@ -19239,19 +19239,19 @@
         </is>
       </c>
       <c r="F291" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="G291" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H291" t="n">
         <v>0.89</v>
       </c>
       <c r="I291" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="J291" t="n">
-        <v>0.8545</v>
+        <v>0.6915</v>
       </c>
       <c r="K291" t="n">
         <v>1</v>
@@ -19267,7 +19267,7 @@
       </c>
       <c r="Q291" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R291" t="n">
@@ -19277,7 +19277,7 @@
         <v>3</v>
       </c>
       <c r="T291" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U291" t="inlineStr"/>
       <c r="V291" t="inlineStr"/>
@@ -19308,22 +19308,22 @@
         </is>
       </c>
       <c r="F292" t="n">
-        <v>0.57</v>
+        <v>0.06</v>
       </c>
       <c r="G292" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H292" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="I292" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="J292" t="n">
-        <v>0.726</v>
+        <v>0.447</v>
       </c>
       <c r="K292" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L292" t="inlineStr"/>
       <c r="M292" t="inlineStr"/>
@@ -19336,7 +19336,7 @@
       </c>
       <c r="Q292" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R292" t="n">
@@ -19346,7 +19346,7 @@
         <v>3</v>
       </c>
       <c r="T292" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U292" t="inlineStr"/>
       <c r="V292" t="inlineStr"/>
@@ -19377,19 +19377,19 @@
         </is>
       </c>
       <c r="F293" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="G293" t="n">
-        <v>0.79</v>
+        <v>0.47</v>
       </c>
       <c r="H293" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="I293" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="J293" t="n">
-        <v>0.7</v>
+        <v>0.536</v>
       </c>
       <c r="K293" t="n">
         <v>3</v>
@@ -19405,7 +19405,7 @@
       </c>
       <c r="Q293" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R293" t="n">
@@ -19415,7 +19415,7 @@
         <v>4</v>
       </c>
       <c r="T293" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U293" t="inlineStr"/>
       <c r="V293" t="inlineStr"/>
@@ -19446,10 +19446,10 @@
         </is>
       </c>
       <c r="F294" t="n">
-        <v>0.77</v>
+        <v>0.47</v>
       </c>
       <c r="G294" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H294" t="n">
         <v>1</v>
@@ -19458,7 +19458,7 @@
         <v>1</v>
       </c>
       <c r="J294" t="n">
-        <v>0.854</v>
+        <v>0.6415</v>
       </c>
       <c r="K294" t="n">
         <v>1</v>
@@ -19474,7 +19474,7 @@
       </c>
       <c r="Q294" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R294" t="n">
@@ -19484,7 +19484,7 @@
         <v>4</v>
       </c>
       <c r="T294" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U294" t="inlineStr"/>
       <c r="V294" t="inlineStr"/>
@@ -19515,19 +19515,19 @@
         </is>
       </c>
       <c r="F295" t="n">
-        <v>0.77</v>
+        <v>0.47</v>
       </c>
       <c r="G295" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H295" t="n">
         <v>0.78</v>
       </c>
-      <c r="H295" t="n">
-        <v>0.79</v>
-      </c>
       <c r="I295" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="J295" t="n">
-        <v>0.764</v>
+        <v>0.548</v>
       </c>
       <c r="K295" t="n">
         <v>2</v>
@@ -19543,7 +19543,7 @@
       </c>
       <c r="Q295" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R295" t="n">
@@ -19553,7 +19553,7 @@
         <v>4</v>
       </c>
       <c r="T295" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U295" t="inlineStr"/>
       <c r="V295" t="inlineStr"/>
@@ -19590,13 +19590,13 @@
         <v>0.79</v>
       </c>
       <c r="H296" t="n">
-        <v>0.57</v>
+        <v>0.78</v>
       </c>
       <c r="I296" t="n">
         <v>0.46</v>
       </c>
       <c r="J296" t="n">
-        <v>0.7384999999999999</v>
+        <v>0.7805</v>
       </c>
       <c r="K296" t="n">
         <v>2</v>
@@ -19612,7 +19612,7 @@
       </c>
       <c r="Q296" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R296" t="n">
@@ -19659,13 +19659,13 @@
         <v>0.78</v>
       </c>
       <c r="H297" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="I297" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="J297" t="n">
-        <v>0.7895000000000001</v>
+        <v>0.8275000000000001</v>
       </c>
       <c r="K297" t="n">
         <v>1</v>
@@ -19681,7 +19681,7 @@
       </c>
       <c r="Q297" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R297" t="n">
@@ -19750,7 +19750,7 @@
       </c>
       <c r="Q298" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R298" t="n">
@@ -19791,10 +19791,10 @@
         </is>
       </c>
       <c r="F299" t="n">
-        <v>0.77</v>
+        <v>0.89</v>
       </c>
       <c r="G299" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H299" t="n">
         <v>0.86</v>
@@ -19803,7 +19803,7 @@
         <v>0.78</v>
       </c>
       <c r="J299" t="n">
-        <v>0.793</v>
+        <v>0.878</v>
       </c>
       <c r="K299" t="n">
         <v>1</v>
@@ -19829,7 +19829,7 @@
         <v>2</v>
       </c>
       <c r="T299" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U299" t="inlineStr"/>
       <c r="V299" t="inlineStr"/>
@@ -19860,10 +19860,10 @@
         </is>
       </c>
       <c r="F300" t="n">
-        <v>0.9</v>
+        <v>0.96</v>
       </c>
       <c r="G300" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H300" t="n">
         <v>0.73</v>
@@ -19872,7 +19872,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="J300" t="n">
-        <v>0.7925</v>
+        <v>0.8595</v>
       </c>
       <c r="K300" t="n">
         <v>2</v>
@@ -19898,7 +19898,7 @@
         <v>2</v>
       </c>
       <c r="T300" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U300" t="inlineStr"/>
       <c r="V300" t="inlineStr"/>
@@ -19929,10 +19929,10 @@
         </is>
       </c>
       <c r="F301" t="n">
-        <v>0.9</v>
+        <v>0.96</v>
       </c>
       <c r="G301" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="H301" t="n">
         <v>0.38</v>
@@ -19941,7 +19941,7 @@
         <v>0.39</v>
       </c>
       <c r="J301" t="n">
-        <v>0.681</v>
+        <v>0.748</v>
       </c>
       <c r="K301" t="n">
         <v>3</v>
@@ -19967,7 +19967,7 @@
         <v>2</v>
       </c>
       <c r="T301" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U301" t="inlineStr"/>
       <c r="V301" t="inlineStr"/>
@@ -19998,10 +19998,10 @@
         </is>
       </c>
       <c r="F302" t="n">
-        <v>0.74</v>
+        <v>0.41</v>
       </c>
       <c r="G302" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H302" t="n">
         <v>0.82</v>
@@ -20010,10 +20010,10 @@
         <v>0.72</v>
       </c>
       <c r="J302" t="n">
-        <v>0.767</v>
+        <v>0.5455</v>
       </c>
       <c r="K302" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L302" t="inlineStr"/>
       <c r="M302" t="inlineStr"/>
@@ -20026,7 +20026,7 @@
       </c>
       <c r="Q302" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R302" t="n">
@@ -20036,7 +20036,7 @@
         <v>2</v>
       </c>
       <c r="T302" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U302" t="inlineStr"/>
       <c r="V302" t="inlineStr"/>
@@ -20067,10 +20067,10 @@
         </is>
       </c>
       <c r="F303" t="n">
-        <v>0.89</v>
+        <v>0.73</v>
       </c>
       <c r="G303" t="n">
-        <v>0.79</v>
+        <v>0.47</v>
       </c>
       <c r="H303" t="n">
         <v>0.62</v>
@@ -20079,10 +20079,10 @@
         <v>0.62</v>
       </c>
       <c r="J303" t="n">
-        <v>0.7605</v>
+        <v>0.6004999999999999</v>
       </c>
       <c r="K303" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L303" t="inlineStr"/>
       <c r="M303" t="inlineStr"/>
@@ -20095,7 +20095,7 @@
       </c>
       <c r="Q303" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R303" t="n">
@@ -20105,7 +20105,7 @@
         <v>2</v>
       </c>
       <c r="T303" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U303" t="inlineStr"/>
       <c r="V303" t="inlineStr"/>
@@ -20136,10 +20136,10 @@
         </is>
       </c>
       <c r="F304" t="n">
-        <v>0.89</v>
+        <v>0.73</v>
       </c>
       <c r="G304" t="n">
-        <v>0.79</v>
+        <v>0.47</v>
       </c>
       <c r="H304" t="n">
         <v>0.52</v>
@@ -20148,10 +20148,10 @@
         <v>0.41</v>
       </c>
       <c r="J304" t="n">
-        <v>0.709</v>
+        <v>0.5489999999999999</v>
       </c>
       <c r="K304" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L304" t="inlineStr"/>
       <c r="M304" t="inlineStr"/>
@@ -20164,7 +20164,7 @@
       </c>
       <c r="Q304" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R304" t="n">
@@ -20174,7 +20174,7 @@
         <v>2</v>
       </c>
       <c r="T304" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U304" t="inlineStr"/>
       <c r="V304" t="inlineStr"/>
@@ -20205,10 +20205,10 @@
         </is>
       </c>
       <c r="F305" t="n">
-        <v>0.74</v>
+        <v>0.41</v>
       </c>
       <c r="G305" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H305" t="n">
         <v>0.78</v>
@@ -20217,7 +20217,7 @@
         <v>0.67</v>
       </c>
       <c r="J305" t="n">
-        <v>0.7515000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="K305" t="n">
         <v>2</v>
@@ -20233,7 +20233,7 @@
       </c>
       <c r="Q305" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R305" t="n">
@@ -20243,7 +20243,7 @@
         <v>2</v>
       </c>
       <c r="T305" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U305" t="inlineStr"/>
       <c r="V305" t="inlineStr"/>
@@ -20274,10 +20274,10 @@
         </is>
       </c>
       <c r="F306" t="n">
-        <v>0.89</v>
+        <v>0.73</v>
       </c>
       <c r="G306" t="n">
-        <v>0.79</v>
+        <v>0.47</v>
       </c>
       <c r="H306" t="n">
         <v>0.41</v>
@@ -20286,7 +20286,7 @@
         <v>0.35</v>
       </c>
       <c r="J306" t="n">
-        <v>0.6779999999999999</v>
+        <v>0.518</v>
       </c>
       <c r="K306" t="n">
         <v>3</v>
@@ -20302,7 +20302,7 @@
       </c>
       <c r="Q306" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R306" t="n">
@@ -20312,7 +20312,7 @@
         <v>2</v>
       </c>
       <c r="T306" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U306" t="inlineStr"/>
       <c r="V306" t="inlineStr"/>
@@ -20343,10 +20343,10 @@
         </is>
       </c>
       <c r="F307" t="n">
-        <v>0.89</v>
+        <v>0.73</v>
       </c>
       <c r="G307" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H307" t="n">
         <v>0.91</v>
@@ -20355,7 +20355,7 @@
         <v>0.85</v>
       </c>
       <c r="J307" t="n">
-        <v>0.8495000000000001</v>
+        <v>0.679</v>
       </c>
       <c r="K307" t="n">
         <v>1</v>
@@ -20371,7 +20371,7 @@
       </c>
       <c r="Q307" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R307" t="n">
@@ -20381,7 +20381,7 @@
         <v>2</v>
       </c>
       <c r="T307" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U307" t="inlineStr"/>
       <c r="V307" t="inlineStr"/>
@@ -20440,7 +20440,7 @@
       </c>
       <c r="Q308" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R308" t="n">
@@ -20487,13 +20487,13 @@
         <v>0.78</v>
       </c>
       <c r="H309" t="n">
-        <v>0.64</v>
+        <v>0.85</v>
       </c>
       <c r="I309" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="J309" t="n">
-        <v>0.767</v>
+        <v>0.8105000000000001</v>
       </c>
       <c r="K309" t="n">
         <v>2</v>
@@ -20509,7 +20509,7 @@
       </c>
       <c r="Q309" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R309" t="n">
@@ -20556,13 +20556,13 @@
         <v>0.79</v>
       </c>
       <c r="H310" t="n">
-        <v>0.46</v>
+        <v>0.71</v>
       </c>
       <c r="I310" t="n">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="J310" t="n">
-        <v>0.6865</v>
+        <v>0.7395</v>
       </c>
       <c r="K310" t="n">
         <v>3</v>
@@ -20578,7 +20578,7 @@
       </c>
       <c r="Q310" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R310" t="n">
@@ -20647,7 +20647,7 @@
       </c>
       <c r="Q311" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R311" t="n">
@@ -20694,13 +20694,13 @@
         <v>0.79</v>
       </c>
       <c r="H312" t="n">
-        <v>0.66</v>
+        <v>0.8</v>
       </c>
       <c r="I312" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="J312" t="n">
-        <v>0.7745</v>
+        <v>0.804</v>
       </c>
       <c r="K312" t="n">
         <v>2</v>
@@ -20716,7 +20716,7 @@
       </c>
       <c r="Q312" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R312" t="n">
@@ -20763,13 +20763,13 @@
         <v>0.79</v>
       </c>
       <c r="H313" t="n">
-        <v>0.48</v>
+        <v>0.66</v>
       </c>
       <c r="I313" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="J313" t="n">
-        <v>0.6905</v>
+        <v>0.731</v>
       </c>
       <c r="K313" t="n">
         <v>3</v>
@@ -20785,7 +20785,7 @@
       </c>
       <c r="Q313" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R313" t="n">
@@ -20854,7 +20854,7 @@
       </c>
       <c r="Q314" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R314" t="n">
@@ -20901,13 +20901,13 @@
         <v>0.78</v>
       </c>
       <c r="H315" t="n">
-        <v>0.61</v>
+        <v>0.86</v>
       </c>
       <c r="I315" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="J315" t="n">
-        <v>0.7504999999999999</v>
+        <v>0.8005</v>
       </c>
       <c r="K315" t="n">
         <v>2</v>
@@ -20923,7 +20923,7 @@
       </c>
       <c r="Q315" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R315" t="n">
@@ -20970,13 +20970,13 @@
         <v>0.79</v>
       </c>
       <c r="H316" t="n">
-        <v>0.51</v>
+        <v>0.78</v>
       </c>
       <c r="I316" t="n">
         <v>0.46</v>
       </c>
       <c r="J316" t="n">
-        <v>0.6995</v>
+        <v>0.7535000000000001</v>
       </c>
       <c r="K316" t="n">
         <v>3</v>
@@ -20992,7 +20992,7 @@
       </c>
       <c r="Q316" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R316" t="n">
@@ -21033,10 +21033,10 @@
         </is>
       </c>
       <c r="F317" t="n">
-        <v>0.9</v>
+        <v>0.96</v>
       </c>
       <c r="G317" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H317" t="n">
         <v>0.51</v>
@@ -21045,7 +21045,7 @@
         <v>0.35</v>
       </c>
       <c r="J317" t="n">
-        <v>0.6974999999999999</v>
+        <v>0.7645</v>
       </c>
       <c r="K317" t="n">
         <v>3</v>
@@ -21071,7 +21071,7 @@
         <v>2</v>
       </c>
       <c r="T317" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U317" t="inlineStr"/>
       <c r="V317" t="inlineStr"/>
@@ -21102,10 +21102,10 @@
         </is>
       </c>
       <c r="F318" t="n">
-        <v>0.9</v>
+        <v>0.96</v>
       </c>
       <c r="G318" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H318" t="n">
         <v>0.63</v>
@@ -21114,7 +21114,7 @@
         <v>0.48</v>
       </c>
       <c r="J318" t="n">
-        <v>0.7409999999999999</v>
+        <v>0.8079999999999999</v>
       </c>
       <c r="K318" t="n">
         <v>2</v>
@@ -21140,7 +21140,7 @@
         <v>2</v>
       </c>
       <c r="T318" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U318" t="inlineStr"/>
       <c r="V318" t="inlineStr"/>
@@ -21171,10 +21171,10 @@
         </is>
       </c>
       <c r="F319" t="n">
-        <v>0.9</v>
+        <v>0.96</v>
       </c>
       <c r="G319" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H319" t="n">
         <v>0.74</v>
@@ -21183,7 +21183,7 @@
         <v>0.62</v>
       </c>
       <c r="J319" t="n">
-        <v>0.7839999999999999</v>
+        <v>0.851</v>
       </c>
       <c r="K319" t="n">
         <v>1</v>
@@ -21209,7 +21209,7 @@
         <v>2</v>
       </c>
       <c r="T319" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U319" t="inlineStr"/>
       <c r="V319" t="inlineStr"/>
@@ -21240,22 +21240,22 @@
         </is>
       </c>
       <c r="F320" t="n">
-        <v>0.57</v>
+        <v>0.06</v>
       </c>
       <c r="G320" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H320" t="n">
         <v>0.89</v>
       </c>
       <c r="I320" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
       <c r="J320" t="n">
-        <v>0.7464999999999999</v>
+        <v>0.4695</v>
       </c>
       <c r="K320" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L320" t="inlineStr"/>
       <c r="M320" t="inlineStr"/>
@@ -21268,7 +21268,7 @@
       </c>
       <c r="Q320" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R320" t="n">
@@ -21278,7 +21278,7 @@
         <v>4</v>
       </c>
       <c r="T320" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U320" t="inlineStr"/>
       <c r="V320" t="inlineStr"/>
@@ -21309,19 +21309,19 @@
         </is>
       </c>
       <c r="F321" t="n">
-        <v>0.57</v>
+        <v>0.06</v>
       </c>
       <c r="G321" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H321" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="I321" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="J321" t="n">
-        <v>0.6849999999999999</v>
+        <v>0.4045</v>
       </c>
       <c r="K321" t="n">
         <v>3</v>
@@ -21337,7 +21337,7 @@
       </c>
       <c r="Q321" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R321" t="n">
@@ -21347,7 +21347,7 @@
         <v>4</v>
       </c>
       <c r="T321" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U321" t="inlineStr"/>
       <c r="V321" t="inlineStr"/>
@@ -21378,22 +21378,22 @@
         </is>
       </c>
       <c r="F322" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="G322" t="n">
-        <v>0.79</v>
+        <v>0.47</v>
       </c>
       <c r="H322" t="n">
-        <v>0.52</v>
+        <v>0.51</v>
       </c>
       <c r="I322" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="J322" t="n">
-        <v>0.721</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="K322" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L322" t="inlineStr"/>
       <c r="M322" t="inlineStr"/>
@@ -21406,7 +21406,7 @@
       </c>
       <c r="Q322" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R322" t="n">
@@ -21416,7 +21416,7 @@
         <v>4</v>
       </c>
       <c r="T322" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U322" t="inlineStr"/>
       <c r="V322" t="inlineStr"/>
@@ -21447,10 +21447,10 @@
         </is>
       </c>
       <c r="F323" t="n">
-        <v>0.89</v>
+        <v>0.96</v>
       </c>
       <c r="G323" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H323" t="n">
         <v>0.43</v>
@@ -21459,7 +21459,7 @@
         <v>0.25</v>
       </c>
       <c r="J323" t="n">
-        <v>0.6635</v>
+        <v>0.7334999999999999</v>
       </c>
       <c r="K323" t="n">
         <v>3</v>
@@ -21485,7 +21485,7 @@
         <v>3</v>
       </c>
       <c r="T323" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U323" t="inlineStr"/>
       <c r="V323" t="inlineStr"/>
@@ -21516,10 +21516,10 @@
         </is>
       </c>
       <c r="F324" t="n">
-        <v>0.89</v>
+        <v>0.96</v>
       </c>
       <c r="G324" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H324" t="n">
         <v>0.55</v>
@@ -21528,7 +21528,7 @@
         <v>0.39</v>
       </c>
       <c r="J324" t="n">
-        <v>0.7085</v>
+        <v>0.7785</v>
       </c>
       <c r="K324" t="n">
         <v>2</v>
@@ -21554,7 +21554,7 @@
         <v>3</v>
       </c>
       <c r="T324" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U324" t="inlineStr"/>
       <c r="V324" t="inlineStr"/>
@@ -21585,10 +21585,10 @@
         </is>
       </c>
       <c r="F325" t="n">
-        <v>0.74</v>
+        <v>0.87</v>
       </c>
       <c r="G325" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H325" t="n">
         <v>0.74</v>
@@ -21597,7 +21597,7 @@
         <v>0.62</v>
       </c>
       <c r="J325" t="n">
-        <v>0.736</v>
+        <v>0.824</v>
       </c>
       <c r="K325" t="n">
         <v>1</v>
@@ -21623,7 +21623,7 @@
         <v>3</v>
       </c>
       <c r="T325" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U325" t="inlineStr"/>
       <c r="V325" t="inlineStr"/>
@@ -21654,10 +21654,10 @@
         </is>
       </c>
       <c r="F326" t="n">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
       <c r="G326" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H326" t="n">
         <v>0.39</v>
@@ -21666,7 +21666,7 @@
         <v>0.2</v>
       </c>
       <c r="J326" t="n">
-        <v>0.6600000000000001</v>
+        <v>0.724</v>
       </c>
       <c r="K326" t="n">
         <v>3</v>
@@ -21692,7 +21692,7 @@
         <v>5</v>
       </c>
       <c r="T326" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U326" t="inlineStr"/>
       <c r="V326" t="inlineStr"/>
@@ -21723,10 +21723,10 @@
         </is>
       </c>
       <c r="F327" t="n">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
       <c r="G327" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H327" t="n">
         <v>0.58</v>
@@ -21735,10 +21735,10 @@
         <v>0.43</v>
       </c>
       <c r="J327" t="n">
-        <v>0.7325</v>
+        <v>0.7965</v>
       </c>
       <c r="K327" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L327" t="inlineStr"/>
       <c r="M327" t="inlineStr"/>
@@ -21761,7 +21761,7 @@
         <v>5</v>
       </c>
       <c r="T327" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U327" t="inlineStr"/>
       <c r="V327" t="inlineStr"/>
@@ -21792,10 +21792,10 @@
         </is>
       </c>
       <c r="F328" t="n">
-        <v>0.57</v>
+        <v>0.78</v>
       </c>
       <c r="G328" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H328" t="n">
         <v>0.82</v>
@@ -21804,10 +21804,10 @@
         <v>0.73</v>
       </c>
       <c r="J328" t="n">
-        <v>0.7175</v>
+        <v>0.8295000000000001</v>
       </c>
       <c r="K328" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L328" t="inlineStr"/>
       <c r="M328" t="inlineStr"/>
@@ -21830,7 +21830,7 @@
         <v>5</v>
       </c>
       <c r="T328" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U328" t="inlineStr"/>
       <c r="V328" t="inlineStr"/>
@@ -21861,10 +21861,10 @@
         </is>
       </c>
       <c r="F329" t="n">
-        <v>0.93</v>
+        <v>0.82</v>
       </c>
       <c r="G329" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H329" t="n">
         <v>0.59</v>
@@ -21873,7 +21873,7 @@
         <v>0.44</v>
       </c>
       <c r="J329" t="n">
-        <v>0.736</v>
+        <v>0.5805</v>
       </c>
       <c r="K329" t="n">
         <v>3</v>
@@ -21889,7 +21889,7 @@
       </c>
       <c r="Q329" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R329" t="n">
@@ -21899,7 +21899,7 @@
         <v>2</v>
       </c>
       <c r="T329" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U329" t="inlineStr"/>
       <c r="V329" t="inlineStr"/>
@@ -21930,10 +21930,10 @@
         </is>
       </c>
       <c r="F330" t="n">
-        <v>0.93</v>
+        <v>0.82</v>
       </c>
       <c r="G330" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H330" t="n">
         <v>0.7</v>
@@ -21942,10 +21942,10 @@
         <v>0.57</v>
       </c>
       <c r="J330" t="n">
-        <v>0.7775000000000001</v>
+        <v>0.622</v>
       </c>
       <c r="K330" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L330" t="inlineStr"/>
       <c r="M330" t="inlineStr"/>
@@ -21958,7 +21958,7 @@
       </c>
       <c r="Q330" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R330" t="n">
@@ -21968,7 +21968,7 @@
         <v>2</v>
       </c>
       <c r="T330" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U330" t="inlineStr"/>
       <c r="V330" t="inlineStr"/>
@@ -21999,10 +21999,10 @@
         </is>
       </c>
       <c r="F331" t="n">
-        <v>0.8</v>
+        <v>0.55</v>
       </c>
       <c r="G331" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H331" t="n">
         <v>0.82</v>
@@ -22011,10 +22011,10 @@
         <v>0.72</v>
       </c>
       <c r="J331" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.5875</v>
       </c>
       <c r="K331" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L331" t="inlineStr"/>
       <c r="M331" t="inlineStr"/>
@@ -22027,7 +22027,7 @@
       </c>
       <c r="Q331" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R331" t="n">
@@ -22037,7 +22037,7 @@
         <v>2</v>
       </c>
       <c r="T331" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U331" t="inlineStr"/>
       <c r="V331" t="inlineStr"/>
@@ -22074,13 +22074,13 @@
         <v>0.78</v>
       </c>
       <c r="H332" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="I332" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="J332" t="n">
-        <v>0.7205</v>
+        <v>0.7275</v>
       </c>
       <c r="K332" t="n">
         <v>2</v>
@@ -22096,7 +22096,7 @@
       </c>
       <c r="Q332" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R332" t="n">
@@ -22143,13 +22143,13 @@
         <v>0.78</v>
       </c>
       <c r="H333" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="I333" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J333" t="n">
-        <v>0.704</v>
+        <v>0.7075</v>
       </c>
       <c r="K333" t="n">
         <v>3</v>
@@ -22165,7 +22165,7 @@
       </c>
       <c r="Q333" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R333" t="n">
@@ -22212,13 +22212,13 @@
         <v>0.79</v>
       </c>
       <c r="H334" t="n">
-        <v>0.58</v>
+        <v>0.8</v>
       </c>
       <c r="I334" t="n">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="J334" t="n">
-        <v>0.7585</v>
+        <v>0.804</v>
       </c>
       <c r="K334" t="n">
         <v>1</v>
@@ -22234,7 +22234,7 @@
       </c>
       <c r="Q334" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R334" t="n">
@@ -22275,10 +22275,10 @@
         </is>
       </c>
       <c r="F335" t="n">
-        <v>0.93</v>
+        <v>0.82</v>
       </c>
       <c r="G335" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H335" t="n">
         <v>0.47</v>
@@ -22287,7 +22287,7 @@
         <v>0.3</v>
       </c>
       <c r="J335" t="n">
-        <v>0.6910000000000001</v>
+        <v>0.5355</v>
       </c>
       <c r="K335" t="n">
         <v>3</v>
@@ -22303,7 +22303,7 @@
       </c>
       <c r="Q335" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R335" t="n">
@@ -22313,7 +22313,7 @@
         <v>3</v>
       </c>
       <c r="T335" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U335" t="inlineStr"/>
       <c r="V335" t="inlineStr"/>
@@ -22344,19 +22344,19 @@
         </is>
       </c>
       <c r="F336" t="n">
-        <v>0.93</v>
+        <v>0.82</v>
       </c>
       <c r="G336" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H336" t="n">
         <v>0.95</v>
       </c>
       <c r="I336" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="J336" t="n">
-        <v>0.88</v>
+        <v>0.7230000000000001</v>
       </c>
       <c r="K336" t="n">
         <v>1</v>
@@ -22372,7 +22372,7 @@
       </c>
       <c r="Q336" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R336" t="n">
@@ -22382,7 +22382,7 @@
         <v>3</v>
       </c>
       <c r="T336" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U336" t="inlineStr"/>
       <c r="V336" t="inlineStr"/>
@@ -22413,19 +22413,19 @@
         </is>
       </c>
       <c r="F337" t="n">
-        <v>0.93</v>
+        <v>0.82</v>
       </c>
       <c r="G337" t="n">
-        <v>0.79</v>
+        <v>0.47</v>
       </c>
       <c r="H337" t="n">
-        <v>0.6</v>
+        <v>0.59</v>
       </c>
       <c r="I337" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="J337" t="n">
-        <v>0.737</v>
+        <v>0.587</v>
       </c>
       <c r="K337" t="n">
         <v>2</v>
@@ -22441,7 +22441,7 @@
       </c>
       <c r="Q337" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R337" t="n">
@@ -22451,7 +22451,7 @@
         <v>3</v>
       </c>
       <c r="T337" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U337" t="inlineStr"/>
       <c r="V337" t="inlineStr"/>
@@ -22510,7 +22510,7 @@
       </c>
       <c r="Q338" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R338" t="n">
@@ -22579,7 +22579,7 @@
       </c>
       <c r="Q339" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R339" t="n">
@@ -22626,13 +22626,13 @@
         <v>0.79</v>
       </c>
       <c r="H340" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="I340" t="n">
         <v>0.62</v>
       </c>
       <c r="J340" t="n">
-        <v>0.7334999999999999</v>
+        <v>0.7855</v>
       </c>
       <c r="K340" t="n">
         <v>2</v>
@@ -22648,7 +22648,7 @@
       </c>
       <c r="Q340" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R340" t="n">
@@ -22689,10 +22689,10 @@
         </is>
       </c>
       <c r="F341" t="n">
-        <v>0.84</v>
+        <v>0.93</v>
       </c>
       <c r="G341" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H341" t="n">
         <v>0.79</v>
@@ -22701,7 +22701,7 @@
         <v>0.68</v>
       </c>
       <c r="J341" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.861</v>
       </c>
       <c r="K341" t="n">
         <v>2</v>
@@ -22727,7 +22727,7 @@
         <v>4</v>
       </c>
       <c r="T341" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U341" t="inlineStr"/>
       <c r="V341" t="inlineStr"/>
@@ -22758,10 +22758,10 @@
         </is>
       </c>
       <c r="F342" t="n">
-        <v>0.84</v>
+        <v>0.93</v>
       </c>
       <c r="G342" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H342" t="n">
         <v>1</v>
@@ -22770,7 +22770,7 @@
         <v>1</v>
       </c>
       <c r="J342" t="n">
-        <v>0.8749999999999999</v>
+        <v>0.951</v>
       </c>
       <c r="K342" t="n">
         <v>1</v>
@@ -22796,7 +22796,7 @@
         <v>4</v>
       </c>
       <c r="T342" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U342" t="inlineStr"/>
       <c r="V342" t="inlineStr"/>
@@ -22827,10 +22827,10 @@
         </is>
       </c>
       <c r="F343" t="n">
-        <v>0.84</v>
+        <v>0.93</v>
       </c>
       <c r="G343" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="H343" t="n">
         <v>0.6</v>
@@ -22839,7 +22839,7 @@
         <v>0.41</v>
       </c>
       <c r="J343" t="n">
-        <v>0.71</v>
+        <v>0.786</v>
       </c>
       <c r="K343" t="n">
         <v>3</v>
@@ -22865,7 +22865,7 @@
         <v>4</v>
       </c>
       <c r="T343" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U343" t="inlineStr"/>
       <c r="V343" t="inlineStr"/>
@@ -22924,7 +22924,7 @@
       </c>
       <c r="Q344" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R344" t="n">
@@ -22971,13 +22971,13 @@
         <v>0.78</v>
       </c>
       <c r="H345" t="n">
-        <v>0.58</v>
+        <v>0.85</v>
       </c>
       <c r="I345" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="J345" t="n">
-        <v>0.7399999999999999</v>
+        <v>0.7955</v>
       </c>
       <c r="K345" t="n">
         <v>2</v>
@@ -22993,7 +22993,7 @@
       </c>
       <c r="Q345" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R345" t="n">
@@ -23040,13 +23040,13 @@
         <v>0.79</v>
       </c>
       <c r="H346" t="n">
-        <v>0.46</v>
+        <v>0.76</v>
       </c>
       <c r="I346" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="J346" t="n">
-        <v>0.6819999999999999</v>
+        <v>0.745</v>
       </c>
       <c r="K346" t="n">
         <v>3</v>
@@ -23062,7 +23062,7 @@
       </c>
       <c r="Q346" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R346" t="n">
@@ -23103,10 +23103,10 @@
         </is>
       </c>
       <c r="F347" t="n">
-        <v>0.84</v>
+        <v>0.93</v>
       </c>
       <c r="G347" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H347" t="n">
         <v>0.78</v>
@@ -23115,7 +23115,7 @@
         <v>0.67</v>
       </c>
       <c r="J347" t="n">
-        <v>0.7815</v>
+        <v>0.8575</v>
       </c>
       <c r="K347" t="n">
         <v>1</v>
@@ -23141,7 +23141,7 @@
         <v>2</v>
       </c>
       <c r="T347" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U347" t="inlineStr"/>
       <c r="V347" t="inlineStr"/>
@@ -23172,10 +23172,10 @@
         </is>
       </c>
       <c r="F348" t="n">
-        <v>0.84</v>
+        <v>0.93</v>
       </c>
       <c r="G348" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H348" t="n">
         <v>0.51</v>
@@ -23184,7 +23184,7 @@
         <v>0.35</v>
       </c>
       <c r="J348" t="n">
-        <v>0.6794999999999999</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="K348" t="n">
         <v>3</v>
@@ -23210,7 +23210,7 @@
         <v>2</v>
       </c>
       <c r="T348" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U348" t="inlineStr"/>
       <c r="V348" t="inlineStr"/>
@@ -23241,10 +23241,10 @@
         </is>
       </c>
       <c r="F349" t="n">
-        <v>0.84</v>
+        <v>0.93</v>
       </c>
       <c r="G349" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H349" t="n">
         <v>0.67</v>
@@ -23253,7 +23253,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="J349" t="n">
-        <v>0.7625</v>
+        <v>0.8385</v>
       </c>
       <c r="K349" t="n">
         <v>2</v>
@@ -23279,7 +23279,7 @@
         <v>2</v>
       </c>
       <c r="T349" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U349" t="inlineStr"/>
       <c r="V349" t="inlineStr"/>
@@ -23310,22 +23310,22 @@
         </is>
       </c>
       <c r="F350" t="n">
-        <v>0.57</v>
+        <v>0.06</v>
       </c>
       <c r="G350" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H350" t="n">
         <v>0.78</v>
       </c>
-      <c r="H350" t="n">
-        <v>0.79</v>
-      </c>
       <c r="I350" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="J350" t="n">
-        <v>0.704</v>
+        <v>0.425</v>
       </c>
       <c r="K350" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L350" t="inlineStr"/>
       <c r="M350" t="inlineStr"/>
@@ -23338,7 +23338,7 @@
       </c>
       <c r="Q350" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R350" t="n">
@@ -23348,7 +23348,7 @@
         <v>4</v>
       </c>
       <c r="T350" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U350" t="inlineStr"/>
       <c r="V350" t="inlineStr"/>
@@ -23379,10 +23379,10 @@
         </is>
       </c>
       <c r="F351" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="G351" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H351" t="n">
         <v>0.47</v>
@@ -23391,10 +23391,10 @@
         <v>0.3</v>
       </c>
       <c r="J351" t="n">
-        <v>0.6910000000000001</v>
+        <v>0.5295</v>
       </c>
       <c r="K351" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L351" t="inlineStr"/>
       <c r="M351" t="inlineStr"/>
@@ -23407,7 +23407,7 @@
       </c>
       <c r="Q351" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R351" t="n">
@@ -23417,7 +23417,7 @@
         <v>4</v>
       </c>
       <c r="T351" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U351" t="inlineStr"/>
       <c r="V351" t="inlineStr"/>
@@ -23448,19 +23448,19 @@
         </is>
       </c>
       <c r="F352" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="G352" t="n">
-        <v>0.79</v>
+        <v>0.47</v>
       </c>
       <c r="H352" t="n">
-        <v>0.66</v>
+        <v>0.64</v>
       </c>
       <c r="I352" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="J352" t="n">
-        <v>0.7745</v>
+        <v>0.618</v>
       </c>
       <c r="K352" t="n">
         <v>1</v>
@@ -23476,7 +23476,7 @@
       </c>
       <c r="Q352" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R352" t="n">
@@ -23486,7 +23486,7 @@
         <v>4</v>
       </c>
       <c r="T352" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U352" t="inlineStr"/>
       <c r="V352" t="inlineStr"/>
@@ -23517,10 +23517,10 @@
         </is>
       </c>
       <c r="F353" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G353" t="n">
         <v>0.93</v>
-      </c>
-      <c r="G353" t="n">
-        <v>0.79</v>
       </c>
       <c r="H353" t="n">
         <v>0.52</v>
@@ -23529,7 +23529,7 @@
         <v>0.58</v>
       </c>
       <c r="J353" t="n">
-        <v>0.7464999999999999</v>
+        <v>0.8104999999999999</v>
       </c>
       <c r="K353" t="n">
         <v>2</v>
@@ -23555,7 +23555,7 @@
         <v>3</v>
       </c>
       <c r="T353" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U353" t="inlineStr"/>
       <c r="V353" t="inlineStr"/>
@@ -23586,10 +23586,10 @@
         </is>
       </c>
       <c r="F354" t="n">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
       <c r="G354" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H354" t="n">
         <v>0.47</v>
@@ -23598,7 +23598,7 @@
         <v>0.3</v>
       </c>
       <c r="J354" t="n">
-        <v>0.6910000000000001</v>
+        <v>0.755</v>
       </c>
       <c r="K354" t="n">
         <v>3</v>
@@ -23624,7 +23624,7 @@
         <v>3</v>
       </c>
       <c r="T354" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U354" t="inlineStr"/>
       <c r="V354" t="inlineStr"/>
@@ -23655,10 +23655,10 @@
         </is>
       </c>
       <c r="F355" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="G355" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H355" t="n">
         <v>0.74</v>
@@ -23667,7 +23667,7 @@
         <v>0.62</v>
       </c>
       <c r="J355" t="n">
-        <v>0.7539999999999999</v>
+        <v>0.836</v>
       </c>
       <c r="K355" t="n">
         <v>1</v>
@@ -23693,7 +23693,7 @@
         <v>3</v>
       </c>
       <c r="T355" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U355" t="inlineStr"/>
       <c r="V355" t="inlineStr"/>
@@ -23724,10 +23724,10 @@
         </is>
       </c>
       <c r="F356" t="n">
-        <v>0.89</v>
+        <v>0.96</v>
       </c>
       <c r="G356" t="n">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="H356" t="n">
         <v>0.51</v>
@@ -23736,7 +23736,7 @@
         <v>0.46</v>
       </c>
       <c r="J356" t="n">
-        <v>0.7144999999999999</v>
+        <v>0.7845</v>
       </c>
       <c r="K356" t="n">
         <v>3</v>
@@ -23762,7 +23762,7 @@
         <v>2</v>
       </c>
       <c r="T356" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U356" t="inlineStr"/>
       <c r="V356" t="inlineStr"/>
@@ -23793,10 +23793,10 @@
         </is>
       </c>
       <c r="F357" t="n">
-        <v>0.89</v>
+        <v>0.96</v>
       </c>
       <c r="G357" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H357" t="n">
         <v>0.63</v>
@@ -23805,7 +23805,7 @@
         <v>0.48</v>
       </c>
       <c r="J357" t="n">
-        <v>0.738</v>
+        <v>0.8079999999999999</v>
       </c>
       <c r="K357" t="n">
         <v>2</v>
@@ -23831,7 +23831,7 @@
         <v>2</v>
       </c>
       <c r="T357" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U357" t="inlineStr"/>
       <c r="V357" t="inlineStr"/>
@@ -23862,10 +23862,10 @@
         </is>
       </c>
       <c r="F358" t="n">
-        <v>0.74</v>
+        <v>0.87</v>
       </c>
       <c r="G358" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H358" t="n">
         <v>0.82</v>
@@ -23874,7 +23874,7 @@
         <v>0.72</v>
       </c>
       <c r="J358" t="n">
-        <v>0.767</v>
+        <v>0.855</v>
       </c>
       <c r="K358" t="n">
         <v>1</v>
@@ -23900,7 +23900,7 @@
         <v>2</v>
       </c>
       <c r="T358" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U358" t="inlineStr"/>
       <c r="V358" t="inlineStr"/>
@@ -23931,10 +23931,10 @@
         </is>
       </c>
       <c r="F359" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="G359" t="n">
-        <v>0.79</v>
+        <v>0.47</v>
       </c>
       <c r="H359" t="n">
         <v>0.46</v>
@@ -23943,7 +23943,7 @@
         <v>0.41</v>
       </c>
       <c r="J359" t="n">
-        <v>0.7</v>
+        <v>0.5429999999999999</v>
       </c>
       <c r="K359" t="n">
         <v>3</v>
@@ -23959,7 +23959,7 @@
       </c>
       <c r="Q359" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R359" t="n">
@@ -23969,7 +23969,7 @@
         <v>2</v>
       </c>
       <c r="T359" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U359" t="inlineStr"/>
       <c r="V359" t="inlineStr"/>
@@ -24000,10 +24000,10 @@
         </is>
       </c>
       <c r="F360" t="n">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="G360" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H360" t="n">
         <v>0.59</v>
@@ -24012,10 +24012,10 @@
         <v>0.44</v>
       </c>
       <c r="J360" t="n">
-        <v>0.7269999999999999</v>
+        <v>0.5594999999999999</v>
       </c>
       <c r="K360" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L360" t="inlineStr"/>
       <c r="M360" t="inlineStr"/>
@@ -24028,7 +24028,7 @@
       </c>
       <c r="Q360" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R360" t="n">
@@ -24038,7 +24038,7 @@
         <v>2</v>
       </c>
       <c r="T360" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U360" t="inlineStr"/>
       <c r="V360" t="inlineStr"/>
@@ -24069,10 +24069,10 @@
         </is>
       </c>
       <c r="F361" t="n">
-        <v>0.77</v>
+        <v>0.47</v>
       </c>
       <c r="G361" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H361" t="n">
         <v>0.78</v>
@@ -24081,10 +24081,10 @@
         <v>0.67</v>
       </c>
       <c r="J361" t="n">
-        <v>0.7605000000000001</v>
+        <v>0.548</v>
       </c>
       <c r="K361" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L361" t="inlineStr"/>
       <c r="M361" t="inlineStr"/>
@@ -24097,7 +24097,7 @@
       </c>
       <c r="Q361" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R361" t="n">
@@ -24107,7 +24107,7 @@
         <v>2</v>
       </c>
       <c r="T361" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U361" t="inlineStr"/>
       <c r="V361" t="inlineStr"/>
@@ -24144,13 +24144,13 @@
         <v>0.78</v>
       </c>
       <c r="H362" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="I362" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="J362" t="n">
-        <v>0.6600000000000001</v>
+        <v>0.667</v>
       </c>
       <c r="K362" t="n">
         <v>3</v>
@@ -24166,7 +24166,7 @@
       </c>
       <c r="Q362" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R362" t="n">
@@ -24213,13 +24213,13 @@
         <v>0.78</v>
       </c>
       <c r="H363" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="I363" t="n">
-        <v>0.43</v>
+        <v>0.48</v>
       </c>
       <c r="J363" t="n">
-        <v>0.7325</v>
+        <v>0.748</v>
       </c>
       <c r="K363" t="n">
         <v>2</v>
@@ -24235,7 +24235,7 @@
       </c>
       <c r="Q363" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R363" t="n">
@@ -24282,13 +24282,13 @@
         <v>0.78</v>
       </c>
       <c r="H364" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="I364" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="J364" t="n">
-        <v>0.8765000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="K364" t="n">
         <v>1</v>
@@ -24304,7 +24304,7 @@
       </c>
       <c r="Q364" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R364" t="n">
@@ -24345,10 +24345,10 @@
         </is>
       </c>
       <c r="F365" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="G365" t="n">
-        <v>0.79</v>
+        <v>0.47</v>
       </c>
       <c r="H365" t="n">
         <v>0.17</v>
@@ -24357,10 +24357,10 @@
         <v>0.15</v>
       </c>
       <c r="J365" t="n">
-        <v>0.612</v>
+        <v>0.461</v>
       </c>
       <c r="K365" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L365" t="inlineStr"/>
       <c r="M365" t="inlineStr"/>
@@ -24373,7 +24373,7 @@
       </c>
       <c r="Q365" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R365" t="n">
@@ -24383,7 +24383,7 @@
         <v>5</v>
       </c>
       <c r="T365" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U365" t="inlineStr"/>
       <c r="V365" t="inlineStr"/>
@@ -24414,10 +24414,10 @@
         </is>
       </c>
       <c r="F366" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="G366" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H366" t="n">
         <v>0.48</v>
@@ -24426,10 +24426,10 @@
         <v>0.3</v>
       </c>
       <c r="J366" t="n">
-        <v>0.6930000000000001</v>
+        <v>0.5315</v>
       </c>
       <c r="K366" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L366" t="inlineStr"/>
       <c r="M366" t="inlineStr"/>
@@ -24442,7 +24442,7 @@
       </c>
       <c r="Q366" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R366" t="n">
@@ -24452,7 +24452,7 @@
         <v>5</v>
       </c>
       <c r="T366" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U366" t="inlineStr"/>
       <c r="V366" t="inlineStr"/>
@@ -24483,22 +24483,22 @@
         </is>
       </c>
       <c r="F367" t="n">
-        <v>0.57</v>
+        <v>0.06</v>
       </c>
       <c r="G367" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H367" t="n">
-        <v>0.76</v>
+        <v>0.74</v>
       </c>
       <c r="I367" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="J367" t="n">
-        <v>0.6935</v>
+        <v>0.4095</v>
       </c>
       <c r="K367" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L367" t="inlineStr"/>
       <c r="M367" t="inlineStr"/>
@@ -24511,7 +24511,7 @@
       </c>
       <c r="Q367" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R367" t="n">
@@ -24521,7 +24521,7 @@
         <v>5</v>
       </c>
       <c r="T367" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U367" t="inlineStr"/>
       <c r="V367" t="inlineStr"/>
@@ -24558,13 +24558,13 @@
         <v>0.78</v>
       </c>
       <c r="H368" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="I368" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="J368" t="n">
-        <v>0.8494999999999999</v>
+        <v>0.8529999999999999</v>
       </c>
       <c r="K368" t="n">
         <v>1</v>
@@ -24580,7 +24580,7 @@
       </c>
       <c r="Q368" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R368" t="n">
@@ -24627,13 +24627,13 @@
         <v>0.78</v>
       </c>
       <c r="H369" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="I369" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="J369" t="n">
-        <v>0.6504999999999999</v>
+        <v>0.6624999999999999</v>
       </c>
       <c r="K369" t="n">
         <v>3</v>
@@ -24649,7 +24649,7 @@
       </c>
       <c r="Q369" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R369" t="n">
@@ -24696,13 +24696,13 @@
         <v>0.79</v>
       </c>
       <c r="H370" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="I370" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="J370" t="n">
-        <v>0.735</v>
+        <v>0.77</v>
       </c>
       <c r="K370" t="n">
         <v>2</v>
@@ -24718,7 +24718,7 @@
       </c>
       <c r="Q370" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R370" t="n">
@@ -24759,22 +24759,22 @@
         </is>
       </c>
       <c r="F371" t="n">
-        <v>0.8</v>
+        <v>0.55</v>
       </c>
       <c r="G371" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H371" t="n">
-        <v>0.84</v>
+        <v>0.83</v>
       </c>
       <c r="I371" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="J371" t="n">
-        <v>0.7949999999999999</v>
+        <v>0.5940000000000001</v>
       </c>
       <c r="K371" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L371" t="inlineStr"/>
       <c r="M371" t="inlineStr"/>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="Q371" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R371" t="n">
@@ -24797,7 +24797,7 @@
         <v>4</v>
       </c>
       <c r="T371" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U371" t="inlineStr"/>
       <c r="V371" t="inlineStr"/>
@@ -24828,19 +24828,19 @@
         </is>
       </c>
       <c r="F372" t="n">
-        <v>0.93</v>
+        <v>0.82</v>
       </c>
       <c r="G372" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H372" t="n">
         <v>0.95</v>
       </c>
       <c r="I372" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="J372" t="n">
-        <v>0.88</v>
+        <v>0.7230000000000001</v>
       </c>
       <c r="K372" t="n">
         <v>1</v>
@@ -24856,7 +24856,7 @@
       </c>
       <c r="Q372" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R372" t="n">
@@ -24866,7 +24866,7 @@
         <v>4</v>
       </c>
       <c r="T372" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U372" t="inlineStr"/>
       <c r="V372" t="inlineStr"/>
@@ -24897,22 +24897,22 @@
         </is>
       </c>
       <c r="F373" t="n">
-        <v>0.93</v>
+        <v>0.82</v>
       </c>
       <c r="G373" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H373" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="I373" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="J373" t="n">
-        <v>0.779</v>
+        <v>0.62</v>
       </c>
       <c r="K373" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L373" t="inlineStr"/>
       <c r="M373" t="inlineStr"/>
@@ -24925,7 +24925,7 @@
       </c>
       <c r="Q373" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R373" t="n">
@@ -24935,7 +24935,7 @@
         <v>4</v>
       </c>
       <c r="T373" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U373" t="inlineStr"/>
       <c r="V373" t="inlineStr"/>
@@ -24966,10 +24966,10 @@
         </is>
       </c>
       <c r="F374" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="G374" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H374" t="n">
         <v>0.91</v>
@@ -24978,7 +24978,7 @@
         <v>0.85</v>
       </c>
       <c r="J374" t="n">
-        <v>0.8225</v>
+        <v>0.9045000000000001</v>
       </c>
       <c r="K374" t="n">
         <v>1</v>
@@ -25004,7 +25004,7 @@
         <v>2</v>
       </c>
       <c r="T374" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U374" t="inlineStr"/>
       <c r="V374" t="inlineStr"/>
@@ -25035,10 +25035,10 @@
         </is>
       </c>
       <c r="F375" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G375" t="n">
         <v>0.93</v>
-      </c>
-      <c r="G375" t="n">
-        <v>0.79</v>
       </c>
       <c r="H375" t="n">
         <v>0.5600000000000001</v>
@@ -25047,7 +25047,7 @@
         <v>0.62</v>
       </c>
       <c r="J375" t="n">
-        <v>0.7605</v>
+        <v>0.8244999999999999</v>
       </c>
       <c r="K375" t="n">
         <v>2</v>
@@ -25073,7 +25073,7 @@
         <v>2</v>
       </c>
       <c r="T375" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U375" t="inlineStr"/>
       <c r="V375" t="inlineStr"/>
@@ -25104,10 +25104,10 @@
         </is>
       </c>
       <c r="F376" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G376" t="n">
         <v>0.93</v>
-      </c>
-      <c r="G376" t="n">
-        <v>0.79</v>
       </c>
       <c r="H376" t="n">
         <v>0.21</v>
@@ -25116,7 +25116,7 @@
         <v>0.39</v>
       </c>
       <c r="J376" t="n">
-        <v>0.656</v>
+        <v>0.72</v>
       </c>
       <c r="K376" t="n">
         <v>3</v>
@@ -25142,7 +25142,7 @@
         <v>2</v>
       </c>
       <c r="T376" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U376" t="inlineStr"/>
       <c r="V376" t="inlineStr"/>
@@ -25201,7 +25201,7 @@
       </c>
       <c r="Q377" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R377" t="n">
@@ -25270,7 +25270,7 @@
       </c>
       <c r="Q378" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R378" t="n">
@@ -25317,13 +25317,13 @@
         <v>0.79</v>
       </c>
       <c r="H379" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="I379" t="n">
         <v>0.62</v>
       </c>
       <c r="J379" t="n">
-        <v>0.7605</v>
+        <v>0.8125</v>
       </c>
       <c r="K379" t="n">
         <v>1</v>
@@ -25339,7 +25339,7 @@
       </c>
       <c r="Q379" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R379" t="n">
@@ -25380,10 +25380,10 @@
         </is>
       </c>
       <c r="F380" t="n">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
       <c r="G380" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H380" t="n">
         <v>0.96</v>
@@ -25392,7 +25392,7 @@
         <v>0.93</v>
       </c>
       <c r="J380" t="n">
-        <v>0.8835</v>
+        <v>0.9475</v>
       </c>
       <c r="K380" t="n">
         <v>1</v>
@@ -25418,7 +25418,7 @@
         <v>1</v>
       </c>
       <c r="T380" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U380" t="inlineStr"/>
       <c r="V380" t="inlineStr"/>
@@ -25449,10 +25449,10 @@
         </is>
       </c>
       <c r="F381" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G381" t="n">
         <v>0.93</v>
-      </c>
-      <c r="G381" t="n">
-        <v>0.79</v>
       </c>
       <c r="H381" t="n">
         <v>0.5600000000000001</v>
@@ -25461,7 +25461,7 @@
         <v>0.62</v>
       </c>
       <c r="J381" t="n">
-        <v>0.7605</v>
+        <v>0.8244999999999999</v>
       </c>
       <c r="K381" t="n">
         <v>2</v>
@@ -25487,7 +25487,7 @@
         <v>1</v>
       </c>
       <c r="T381" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U381" t="inlineStr"/>
       <c r="V381" t="inlineStr"/>
@@ -25518,10 +25518,10 @@
         </is>
       </c>
       <c r="F382" t="n">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
       <c r="G382" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H382" t="n">
         <v>0.55</v>
@@ -25530,7 +25530,7 @@
         <v>0.39</v>
       </c>
       <c r="J382" t="n">
-        <v>0.7205</v>
+        <v>0.7845</v>
       </c>
       <c r="K382" t="n">
         <v>3</v>
@@ -25556,7 +25556,7 @@
         <v>1</v>
       </c>
       <c r="T382" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U382" t="inlineStr"/>
       <c r="V382" t="inlineStr"/>
@@ -25587,10 +25587,10 @@
         </is>
       </c>
       <c r="F383" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="G383" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H383" t="n">
         <v>0.63</v>
@@ -25599,7 +25599,7 @@
         <v>0.48</v>
       </c>
       <c r="J383" t="n">
-        <v>0.75</v>
+        <v>0.5884999999999999</v>
       </c>
       <c r="K383" t="n">
         <v>2</v>
@@ -25615,7 +25615,7 @@
       </c>
       <c r="Q383" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R383" t="n">
@@ -25625,7 +25625,7 @@
         <v>2</v>
       </c>
       <c r="T383" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U383" t="inlineStr"/>
       <c r="V383" t="inlineStr"/>
@@ -25656,10 +25656,10 @@
         </is>
       </c>
       <c r="F384" t="n">
-        <v>0.57</v>
+        <v>0.06</v>
       </c>
       <c r="G384" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H384" t="n">
         <v>0.82</v>
@@ -25668,7 +25668,7 @@
         <v>0.72</v>
       </c>
       <c r="J384" t="n">
-        <v>0.716</v>
+        <v>0.4405</v>
       </c>
       <c r="K384" t="n">
         <v>3</v>
@@ -25684,7 +25684,7 @@
       </c>
       <c r="Q384" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R384" t="n">
@@ -25694,7 +25694,7 @@
         <v>2</v>
       </c>
       <c r="T384" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U384" t="inlineStr"/>
       <c r="V384" t="inlineStr"/>
@@ -25725,10 +25725,10 @@
         </is>
       </c>
       <c r="F385" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="G385" t="n">
-        <v>0.79</v>
+        <v>0.47</v>
       </c>
       <c r="H385" t="n">
         <v>0.5600000000000001</v>
@@ -25737,7 +25737,7 @@
         <v>0.62</v>
       </c>
       <c r="J385" t="n">
-        <v>0.7605</v>
+        <v>0.6094999999999999</v>
       </c>
       <c r="K385" t="n">
         <v>1</v>
@@ -25753,7 +25753,7 @@
       </c>
       <c r="Q385" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R385" t="n">
@@ -25763,7 +25763,7 @@
         <v>2</v>
       </c>
       <c r="T385" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U385" t="inlineStr"/>
       <c r="V385" t="inlineStr"/>
@@ -25800,13 +25800,13 @@
         <v>0.78</v>
       </c>
       <c r="H386" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="I386" t="n">
         <v>0.3</v>
       </c>
       <c r="J386" t="n">
-        <v>0.6910000000000001</v>
+        <v>0.6930000000000001</v>
       </c>
       <c r="K386" t="n">
         <v>3</v>
@@ -25822,7 +25822,7 @@
       </c>
       <c r="Q386" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R386" t="n">
@@ -25869,13 +25869,13 @@
         <v>0.78</v>
       </c>
       <c r="H387" t="n">
-        <v>0.74</v>
+        <v>0.76</v>
       </c>
       <c r="I387" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="J387" t="n">
-        <v>0.7539999999999999</v>
+        <v>0.7609999999999999</v>
       </c>
       <c r="K387" t="n">
         <v>2</v>
@@ -25891,7 +25891,7 @@
       </c>
       <c r="Q387" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R387" t="n">
@@ -25938,13 +25938,13 @@
         <v>0.78</v>
       </c>
       <c r="H388" t="n">
-        <v>0.64</v>
+        <v>0.85</v>
       </c>
       <c r="I388" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="J388" t="n">
-        <v>0.779</v>
+        <v>0.8225000000000001</v>
       </c>
       <c r="K388" t="n">
         <v>1</v>
@@ -25960,7 +25960,7 @@
       </c>
       <c r="Q388" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R388" t="n">
@@ -26001,10 +26001,10 @@
         </is>
       </c>
       <c r="F389" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="G389" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H389" t="n">
         <v>0.82</v>
@@ -26013,7 +26013,7 @@
         <v>0.72</v>
       </c>
       <c r="J389" t="n">
-        <v>0.7849999999999999</v>
+        <v>0.867</v>
       </c>
       <c r="K389" t="n">
         <v>2</v>
@@ -26039,7 +26039,7 @@
         <v>2</v>
       </c>
       <c r="T389" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U389" t="inlineStr"/>
       <c r="V389" t="inlineStr"/>
@@ -26070,10 +26070,10 @@
         </is>
       </c>
       <c r="F390" t="n">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
       <c r="G390" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H390" t="n">
         <v>0.91</v>
@@ -26082,7 +26082,7 @@
         <v>0.85</v>
       </c>
       <c r="J390" t="n">
-        <v>0.8615000000000002</v>
+        <v>0.9255</v>
       </c>
       <c r="K390" t="n">
         <v>1</v>
@@ -26108,7 +26108,7 @@
         <v>2</v>
       </c>
       <c r="T390" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U390" t="inlineStr"/>
       <c r="V390" t="inlineStr"/>
@@ -26139,10 +26139,10 @@
         </is>
       </c>
       <c r="F391" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G391" t="n">
         <v>0.93</v>
-      </c>
-      <c r="G391" t="n">
-        <v>0.79</v>
       </c>
       <c r="H391" t="n">
         <v>0.47</v>
@@ -26151,7 +26151,7 @@
         <v>0.35</v>
       </c>
       <c r="J391" t="n">
-        <v>0.702</v>
+        <v>0.7659999999999999</v>
       </c>
       <c r="K391" t="n">
         <v>3</v>
@@ -26177,7 +26177,7 @@
         <v>2</v>
       </c>
       <c r="T391" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U391" t="inlineStr"/>
       <c r="V391" t="inlineStr"/>
@@ -26208,10 +26208,10 @@
         </is>
       </c>
       <c r="F392" t="n">
-        <v>0.93</v>
+        <v>0.82</v>
       </c>
       <c r="G392" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H392" t="n">
         <v>1</v>
@@ -26220,7 +26220,7 @@
         <v>1</v>
       </c>
       <c r="J392" t="n">
-        <v>0.902</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="K392" t="n">
         <v>1</v>
@@ -26236,7 +26236,7 @@
       </c>
       <c r="Q392" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R392" t="n">
@@ -26246,7 +26246,7 @@
         <v>4</v>
       </c>
       <c r="T392" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U392" t="inlineStr"/>
       <c r="V392" t="inlineStr"/>
@@ -26277,19 +26277,19 @@
         </is>
       </c>
       <c r="F393" t="n">
-        <v>0.93</v>
+        <v>0.82</v>
       </c>
       <c r="G393" t="n">
-        <v>0.79</v>
+        <v>0.47</v>
       </c>
       <c r="H393" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="I393" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="J393" t="n">
-        <v>0.7585</v>
+        <v>0.61</v>
       </c>
       <c r="K393" t="n">
         <v>2</v>
@@ -26305,7 +26305,7 @@
       </c>
       <c r="Q393" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R393" t="n">
@@ -26315,7 +26315,7 @@
         <v>4</v>
       </c>
       <c r="T393" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U393" t="inlineStr"/>
       <c r="V393" t="inlineStr"/>
@@ -26346,10 +26346,10 @@
         </is>
       </c>
       <c r="F394" t="n">
-        <v>0.93</v>
+        <v>0.82</v>
       </c>
       <c r="G394" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H394" t="n">
         <v>0.47</v>
@@ -26358,7 +26358,7 @@
         <v>0.3</v>
       </c>
       <c r="J394" t="n">
-        <v>0.6910000000000001</v>
+        <v>0.5355</v>
       </c>
       <c r="K394" t="n">
         <v>3</v>
@@ -26374,7 +26374,7 @@
       </c>
       <c r="Q394" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R394" t="n">
@@ -26384,7 +26384,7 @@
         <v>4</v>
       </c>
       <c r="T394" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U394" t="inlineStr"/>
       <c r="V394" t="inlineStr"/>
@@ -26443,7 +26443,7 @@
       </c>
       <c r="Q395" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R395" t="n">
@@ -26512,7 +26512,7 @@
       </c>
       <c r="Q396" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R396" t="n">
@@ -26559,13 +26559,13 @@
         <v>0.79</v>
       </c>
       <c r="H397" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="I397" t="n">
         <v>0.62</v>
       </c>
       <c r="J397" t="n">
-        <v>0.7605</v>
+        <v>0.8125</v>
       </c>
       <c r="K397" t="n">
         <v>1</v>
@@ -26581,7 +26581,7 @@
       </c>
       <c r="Q397" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R397" t="n">
@@ -26622,10 +26622,10 @@
         </is>
       </c>
       <c r="F398" t="n">
-        <v>0.57</v>
+        <v>0.78</v>
       </c>
       <c r="G398" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H398" t="n">
         <v>0.82</v>
@@ -26634,7 +26634,7 @@
         <v>0.72</v>
       </c>
       <c r="J398" t="n">
-        <v>0.716</v>
+        <v>0.8280000000000001</v>
       </c>
       <c r="K398" t="n">
         <v>2</v>
@@ -26660,7 +26660,7 @@
         <v>2</v>
       </c>
       <c r="T398" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U398" t="inlineStr"/>
       <c r="V398" t="inlineStr"/>
@@ -26691,10 +26691,10 @@
         </is>
       </c>
       <c r="F399" t="n">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
       <c r="G399" t="n">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="H399" t="n">
         <v>0.91</v>
@@ -26703,7 +26703,7 @@
         <v>0.85</v>
       </c>
       <c r="J399" t="n">
-        <v>0.8615000000000002</v>
+        <v>0.9255</v>
       </c>
       <c r="K399" t="n">
         <v>1</v>
@@ -26729,7 +26729,7 @@
         <v>2</v>
       </c>
       <c r="T399" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U399" t="inlineStr"/>
       <c r="V399" t="inlineStr"/>
@@ -26760,10 +26760,10 @@
         </is>
       </c>
       <c r="F400" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G400" t="n">
         <v>0.93</v>
-      </c>
-      <c r="G400" t="n">
-        <v>0.79</v>
       </c>
       <c r="H400" t="n">
         <v>0.38</v>
@@ -26772,7 +26772,7 @@
         <v>0.39</v>
       </c>
       <c r="J400" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.754</v>
       </c>
       <c r="K400" t="n">
         <v>3</v>
@@ -26798,7 +26798,7 @@
         <v>2</v>
       </c>
       <c r="T400" t="n">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="U400" t="inlineStr"/>
       <c r="V400" t="inlineStr"/>
@@ -26829,10 +26829,10 @@
         </is>
       </c>
       <c r="F401" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="G401" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H401" t="n">
         <v>1</v>
@@ -26841,7 +26841,7 @@
         <v>1</v>
       </c>
       <c r="J401" t="n">
-        <v>0.902</v>
+        <v>0.7405</v>
       </c>
       <c r="K401" t="n">
         <v>1</v>
@@ -26857,7 +26857,7 @@
       </c>
       <c r="Q401" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R401" t="n">
@@ -26867,7 +26867,7 @@
         <v>1</v>
       </c>
       <c r="T401" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U401" t="inlineStr"/>
       <c r="V401" t="inlineStr"/>
@@ -26898,10 +26898,10 @@
         </is>
       </c>
       <c r="F402" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="G402" t="n">
-        <v>0.79</v>
+        <v>0.47</v>
       </c>
       <c r="H402" t="n">
         <v>0.62</v>
@@ -26910,7 +26910,7 @@
         <v>0.62</v>
       </c>
       <c r="J402" t="n">
-        <v>0.7725</v>
+        <v>0.6214999999999999</v>
       </c>
       <c r="K402" t="n">
         <v>2</v>
@@ -26926,7 +26926,7 @@
       </c>
       <c r="Q402" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R402" t="n">
@@ -26936,7 +26936,7 @@
         <v>1</v>
       </c>
       <c r="T402" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U402" t="inlineStr"/>
       <c r="V402" t="inlineStr"/>
@@ -26967,10 +26967,10 @@
         </is>
       </c>
       <c r="F403" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="G403" t="n">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
       <c r="H403" t="n">
         <v>0.55</v>
@@ -26979,7 +26979,7 @@
         <v>0.39</v>
       </c>
       <c r="J403" t="n">
-        <v>0.7205</v>
+        <v>0.5589999999999999</v>
       </c>
       <c r="K403" t="n">
         <v>3</v>
@@ -26995,7 +26995,7 @@
       </c>
       <c r="Q403" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dryer</t>
         </is>
       </c>
       <c r="R403" t="n">
@@ -27005,7 +27005,7 @@
         <v>1</v>
       </c>
       <c r="T403" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="U403" t="inlineStr"/>
       <c r="V403" t="inlineStr"/>
@@ -27064,7 +27064,7 @@
       </c>
       <c r="Q404" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R404" t="n">
@@ -27120,7 +27120,7 @@
         <v>0.7849999999999999</v>
       </c>
       <c r="K405" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L405" t="inlineStr"/>
       <c r="M405" t="inlineStr"/>
@@ -27133,7 +27133,7 @@
       </c>
       <c r="Q405" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R405" t="n">
@@ -27180,16 +27180,16 @@
         <v>0.78</v>
       </c>
       <c r="H406" t="n">
-        <v>0.61</v>
+        <v>0.86</v>
       </c>
       <c r="I406" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="J406" t="n">
-        <v>0.7775000000000001</v>
+        <v>0.8275000000000001</v>
       </c>
       <c r="K406" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L406" t="inlineStr"/>
       <c r="M406" t="inlineStr"/>
@@ -27202,7 +27202,7 @@
       </c>
       <c r="Q406" t="inlineStr">
         <is>
-          <t>washing_machine</t>
+          <t>dishwasher</t>
         </is>
       </c>
       <c r="R406" t="n">
@@ -28353,13 +28353,13 @@
         <v>0.58</v>
       </c>
       <c r="H423" t="n">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="I423" t="n">
         <v>0.52</v>
       </c>
       <c r="J423" t="n">
-        <v>0.597</v>
+        <v>0.605</v>
       </c>
       <c r="K423" t="n">
         <v>2</v>
@@ -28422,13 +28422,13 @@
         <v>0.38</v>
       </c>
       <c r="H424" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="I424" t="n">
         <v>0.67</v>
       </c>
       <c r="J424" t="n">
-        <v>0.4625</v>
+        <v>0.4805</v>
       </c>
       <c r="K424" t="n">
         <v>3</v>
@@ -28836,13 +28836,13 @@
         <v>0.58</v>
       </c>
       <c r="H430" t="n">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="I430" t="n">
         <v>0.52</v>
       </c>
       <c r="J430" t="n">
-        <v>0.597</v>
+        <v>0.605</v>
       </c>
       <c r="K430" t="n">
         <v>3</v>
@@ -29112,13 +29112,13 @@
         <v>0.64</v>
       </c>
       <c r="H434" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="I434" t="n">
         <v>0.46</v>
       </c>
       <c r="J434" t="n">
-        <v>0.6240000000000001</v>
+        <v>0.6260000000000001</v>
       </c>
       <c r="K434" t="n">
         <v>1</v>
@@ -29181,13 +29181,13 @@
         <v>0.38</v>
       </c>
       <c r="H435" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="I435" t="n">
         <v>0.67</v>
       </c>
       <c r="J435" t="n">
-        <v>0.4625</v>
+        <v>0.4805</v>
       </c>
       <c r="K435" t="n">
         <v>2</v>
@@ -29250,13 +29250,13 @@
         <v>0.13</v>
       </c>
       <c r="H436" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="I436" t="n">
         <v>0.48</v>
       </c>
       <c r="J436" t="n">
-        <v>0.2075</v>
+        <v>0.2335</v>
       </c>
       <c r="K436" t="n">
         <v>3</v>
@@ -29595,13 +29595,13 @@
         <v>0.51</v>
       </c>
       <c r="H441" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="I441" t="n">
         <v>0.57</v>
       </c>
       <c r="J441" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.574</v>
       </c>
       <c r="K441" t="n">
         <v>2</v>
@@ -29664,13 +29664,13 @@
         <v>0.19</v>
       </c>
       <c r="H442" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="I442" t="n">
         <v>0.52</v>
       </c>
       <c r="J442" t="n">
-        <v>0.2575</v>
+        <v>0.2815</v>
       </c>
       <c r="K442" t="n">
         <v>3</v>
@@ -30009,13 +30009,13 @@
         <v>0.51</v>
       </c>
       <c r="H447" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="I447" t="n">
         <v>0.57</v>
       </c>
       <c r="J447" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.574</v>
       </c>
       <c r="K447" t="n">
         <v>2</v>
@@ -30078,13 +30078,13 @@
         <v>0.19</v>
       </c>
       <c r="H448" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="I448" t="n">
         <v>0.52</v>
       </c>
       <c r="J448" t="n">
-        <v>0.2575</v>
+        <v>0.2815</v>
       </c>
       <c r="K448" t="n">
         <v>3</v>
@@ -30354,13 +30354,13 @@
         <v>0.38</v>
       </c>
       <c r="H452" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="I452" t="n">
         <v>0.67</v>
       </c>
       <c r="J452" t="n">
-        <v>0.4625</v>
+        <v>0.4805</v>
       </c>
       <c r="K452" t="n">
         <v>1</v>
@@ -30423,13 +30423,13 @@
         <v>0.19</v>
       </c>
       <c r="H453" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="I453" t="n">
         <v>0.52</v>
       </c>
       <c r="J453" t="n">
-        <v>0.2575</v>
+        <v>0.2815</v>
       </c>
       <c r="K453" t="n">
         <v>2</v>
@@ -30492,13 +30492,13 @@
         <v>0</v>
       </c>
       <c r="H454" t="n">
-        <v>0.21</v>
+        <v>0.36</v>
       </c>
       <c r="I454" t="n">
         <v>0.4</v>
       </c>
       <c r="J454" t="n">
-        <v>0.102</v>
+        <v>0.132</v>
       </c>
       <c r="K454" t="n">
         <v>3</v>
@@ -31389,13 +31389,13 @@
         <v>0.64</v>
       </c>
       <c r="H467" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="I467" t="n">
         <v>0.46</v>
       </c>
       <c r="J467" t="n">
-        <v>0.6240000000000001</v>
+        <v>0.6260000000000001</v>
       </c>
       <c r="K467" t="n">
         <v>1</v>
@@ -31458,13 +31458,13 @@
         <v>0.38</v>
       </c>
       <c r="H468" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="I468" t="n">
         <v>0.67</v>
       </c>
       <c r="J468" t="n">
-        <v>0.4625</v>
+        <v>0.4805</v>
       </c>
       <c r="K468" t="n">
         <v>2</v>
@@ -31527,13 +31527,13 @@
         <v>0.19</v>
       </c>
       <c r="H469" t="n">
-        <v>0.55</v>
+        <v>0.67</v>
       </c>
       <c r="I469" t="n">
         <v>0.52</v>
       </c>
       <c r="J469" t="n">
-        <v>0.2575</v>
+        <v>0.2815</v>
       </c>
       <c r="K469" t="n">
         <v>3</v>
@@ -32355,13 +32355,13 @@
         <v>0.51</v>
       </c>
       <c r="H481" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="I481" t="n">
         <v>0.57</v>
       </c>
       <c r="J481" t="n">
-        <v>0.6020000000000001</v>
+        <v>0.614</v>
       </c>
       <c r="K481" t="n">
         <v>3</v>
@@ -32562,13 +32562,13 @@
         <v>0.19</v>
       </c>
       <c r="H484" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="I484" t="n">
         <v>0.52</v>
       </c>
       <c r="J484" t="n">
-        <v>0.3235</v>
+        <v>0.3375</v>
       </c>
       <c r="K484" t="n">
         <v>3</v>
@@ -32907,13 +32907,13 @@
         <v>0.38</v>
       </c>
       <c r="H489" t="n">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="I489" t="n">
         <v>0.67</v>
       </c>
       <c r="J489" t="n">
-        <v>0.4995000000000001</v>
+        <v>0.5135000000000001</v>
       </c>
       <c r="K489" t="n">
         <v>2</v>
@@ -32976,13 +32976,13 @@
         <v>0</v>
       </c>
       <c r="H490" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="I490" t="n">
         <v>0.32</v>
       </c>
       <c r="J490" t="n">
-        <v>0.048</v>
+        <v>0.06</v>
       </c>
       <c r="K490" t="n">
         <v>3</v>
@@ -34356,13 +34356,13 @@
         <v>0.64</v>
       </c>
       <c r="H510" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="I510" t="n">
         <v>0.46</v>
       </c>
       <c r="J510" t="n">
-        <v>0.6519999999999999</v>
+        <v>0.6539999999999999</v>
       </c>
       <c r="K510" t="n">
         <v>2</v>
@@ -34425,13 +34425,13 @@
         <v>0.38</v>
       </c>
       <c r="H511" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="I511" t="n">
         <v>0.67</v>
       </c>
       <c r="J511" t="n">
-        <v>0.4965000000000001</v>
+        <v>0.5125000000000001</v>
       </c>
       <c r="K511" t="n">
         <v>3</v>
@@ -34494,13 +34494,13 @@
         <v>0.64</v>
       </c>
       <c r="H512" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="I512" t="n">
         <v>0.46</v>
       </c>
       <c r="J512" t="n">
-        <v>0.665</v>
+        <v>0.667</v>
       </c>
       <c r="K512" t="n">
         <v>1</v>
@@ -34563,13 +34563,13 @@
         <v>0.51</v>
       </c>
       <c r="H513" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="I513" t="n">
         <v>0.57</v>
       </c>
       <c r="J513" t="n">
-        <v>0.6020000000000001</v>
+        <v>0.614</v>
       </c>
       <c r="K513" t="n">
         <v>2</v>
@@ -34632,13 +34632,13 @@
         <v>0.38</v>
       </c>
       <c r="H514" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="I514" t="n">
         <v>0.67</v>
       </c>
       <c r="J514" t="n">
-        <v>0.5065000000000001</v>
+        <v>0.5185</v>
       </c>
       <c r="K514" t="n">
         <v>3</v>
@@ -34770,13 +34770,13 @@
         <v>0.51</v>
       </c>
       <c r="H516" t="n">
-        <v>0.92</v>
+        <v>0.99</v>
       </c>
       <c r="I516" t="n">
         <v>0.57</v>
       </c>
       <c r="J516" t="n">
-        <v>0.5950000000000001</v>
+        <v>0.6090000000000001</v>
       </c>
       <c r="K516" t="n">
         <v>2</v>
@@ -34839,13 +34839,13 @@
         <v>0.38</v>
       </c>
       <c r="H517" t="n">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="I517" t="n">
         <v>0.67</v>
       </c>
       <c r="J517" t="n">
-        <v>0.4995000000000001</v>
+        <v>0.5135000000000001</v>
       </c>
       <c r="K517" t="n">
         <v>3</v>
@@ -34908,13 +34908,13 @@
         <v>0.64</v>
       </c>
       <c r="H518" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="I518" t="n">
         <v>0.46</v>
       </c>
       <c r="J518" t="n">
-        <v>0.6779999999999999</v>
+        <v>0.6799999999999999</v>
       </c>
       <c r="K518" t="n">
         <v>1</v>
@@ -34977,13 +34977,13 @@
         <v>0.51</v>
       </c>
       <c r="H519" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="I519" t="n">
         <v>0.57</v>
       </c>
       <c r="J519" t="n">
-        <v>0.6090000000000001</v>
+        <v>0.6190000000000001</v>
       </c>
       <c r="K519" t="n">
         <v>2</v>
@@ -35046,13 +35046,13 @@
         <v>0.38</v>
       </c>
       <c r="H520" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="I520" t="n">
         <v>0.67</v>
       </c>
       <c r="J520" t="n">
-        <v>0.5185000000000001</v>
+        <v>0.5265000000000001</v>
       </c>
       <c r="K520" t="n">
         <v>3</v>
@@ -35115,13 +35115,13 @@
         <v>0.64</v>
       </c>
       <c r="H521" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="I521" t="n">
         <v>0.46</v>
       </c>
       <c r="J521" t="n">
-        <v>0.665</v>
+        <v>0.667</v>
       </c>
       <c r="K521" t="n">
         <v>1</v>
@@ -35184,13 +35184,13 @@
         <v>0.51</v>
       </c>
       <c r="H522" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="I522" t="n">
         <v>0.57</v>
       </c>
       <c r="J522" t="n">
-        <v>0.6020000000000001</v>
+        <v>0.614</v>
       </c>
       <c r="K522" t="n">
         <v>2</v>
@@ -35253,13 +35253,13 @@
         <v>0.38</v>
       </c>
       <c r="H523" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="I523" t="n">
         <v>0.67</v>
       </c>
       <c r="J523" t="n">
-        <v>0.5065000000000001</v>
+        <v>0.5185</v>
       </c>
       <c r="K523" t="n">
         <v>3</v>
@@ -35391,13 +35391,13 @@
         <v>0.51</v>
       </c>
       <c r="H525" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="I525" t="n">
         <v>0.57</v>
       </c>
       <c r="J525" t="n">
-        <v>0.6080000000000001</v>
+        <v>0.616</v>
       </c>
       <c r="K525" t="n">
         <v>2</v>
@@ -35460,13 +35460,13 @@
         <v>0.38</v>
       </c>
       <c r="H526" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="I526" t="n">
         <v>0.67</v>
       </c>
       <c r="J526" t="n">
-        <v>0.5155000000000001</v>
+        <v>0.5255000000000001</v>
       </c>
       <c r="K526" t="n">
         <v>3</v>
@@ -36702,13 +36702,13 @@
         <v>0.51</v>
       </c>
       <c r="H544" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="I544" t="n">
         <v>0.57</v>
       </c>
       <c r="J544" t="n">
-        <v>0.5720000000000001</v>
+        <v>0.586</v>
       </c>
       <c r="K544" t="n">
         <v>3</v>
@@ -37668,13 +37668,13 @@
         <v>0.64</v>
       </c>
       <c r="H558" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="I558" t="n">
         <v>0.46</v>
       </c>
       <c r="J558" t="n">
-        <v>0.665</v>
+        <v>0.667</v>
       </c>
       <c r="K558" t="n">
         <v>2</v>
@@ -37737,13 +37737,13 @@
         <v>0.51</v>
       </c>
       <c r="H559" t="n">
-        <v>0.91</v>
+        <v>0.97</v>
       </c>
       <c r="I559" t="n">
         <v>0.57</v>
       </c>
       <c r="J559" t="n">
-        <v>0.6020000000000001</v>
+        <v>0.614</v>
       </c>
       <c r="K559" t="n">
         <v>3</v>
@@ -37875,13 +37875,13 @@
         <v>0.51</v>
       </c>
       <c r="H561" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="I561" t="n">
         <v>0.57</v>
       </c>
       <c r="J561" t="n">
-        <v>0.6080000000000001</v>
+        <v>0.616</v>
       </c>
       <c r="K561" t="n">
         <v>2</v>
@@ -37944,13 +37944,13 @@
         <v>0.38</v>
       </c>
       <c r="H562" t="n">
-        <v>0.78</v>
+        <v>0.83</v>
       </c>
       <c r="I562" t="n">
         <v>0.67</v>
       </c>
       <c r="J562" t="n">
-        <v>0.5155000000000001</v>
+        <v>0.5255000000000001</v>
       </c>
       <c r="K562" t="n">
         <v>3</v>

--- a/workbooks/older_runs/unclassified_legacy/Baselines/baseline_fixeddefault.xlsx
+++ b/workbooks/older_runs/unclassified_legacy/Baselines/baseline_fixeddefault.xlsx
@@ -558,10 +558,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.82</v>
+        <v>0.7</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="H2" t="n">
         <v>0.7</v>
@@ -570,7 +570,7 @@
         <v>0.77</v>
       </c>
       <c r="J2" t="n">
-        <v>0.785</v>
+        <v>0.714</v>
       </c>
       <c r="K2" t="n">
         <v>3</v>
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.84</v>
+        <v>0.73</v>
       </c>
       <c r="G3" t="n">
-        <v>0.84</v>
+        <v>0.73</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -633,7 +633,7 @@
         <v>0.84</v>
       </c>
       <c r="J3" t="n">
-        <v>0.872</v>
+        <v>0.8005</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
@@ -684,10 +684,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.87</v>
+        <v>0.75</v>
       </c>
       <c r="G4" t="n">
-        <v>0.87</v>
+        <v>0.76</v>
       </c>
       <c r="H4" t="n">
         <v>0.7</v>
@@ -696,7 +696,7 @@
         <v>0.84</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8315</v>
+        <v>0.757</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
@@ -747,10 +747,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.87</v>
+        <v>0.97</v>
       </c>
       <c r="G5" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="H5" t="n">
         <v>0.78</v>
@@ -759,7 +759,7 @@
         <v>0.65</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8155</v>
+        <v>0.884</v>
       </c>
       <c r="K5" t="n">
         <v>2</v>
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.83</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>0.83</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
@@ -822,7 +822,7 @@
         <v>0.65</v>
       </c>
       <c r="J6" t="n">
-        <v>0.837</v>
+        <v>0.9085</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
@@ -873,10 +873,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.8</v>
+        <v>0.92</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="H7" t="n">
         <v>0.78</v>
@@ -885,7 +885,7 @@
         <v>0.65</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7735</v>
+        <v>0.848</v>
       </c>
       <c r="K7" t="n">
         <v>3</v>
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.67</v>
+        <v>0.58</v>
       </c>
       <c r="G8" t="n">
-        <v>0.68</v>
+        <v>0.59</v>
       </c>
       <c r="H8" t="n">
         <v>0.93</v>
@@ -948,7 +948,7 @@
         <v>0.84</v>
       </c>
       <c r="J8" t="n">
-        <v>0.751</v>
+        <v>0.6925</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.71</v>
+        <v>0.61</v>
       </c>
       <c r="G9" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="H9" t="n">
         <v>0.7</v>
@@ -1011,7 +1011,7 @@
         <v>0.84</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7275</v>
+        <v>0.666</v>
       </c>
       <c r="K9" t="n">
         <v>2</v>
@@ -1062,10 +1062,10 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.75</v>
+        <v>0.64</v>
       </c>
       <c r="G10" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="H10" t="n">
         <v>0.41</v>
@@ -1074,7 +1074,7 @@
         <v>0.77</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.617</v>
       </c>
       <c r="K10" t="n">
         <v>3</v>
@@ -1125,10 +1125,10 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.67</v>
+        <v>0.89</v>
       </c>
       <c r="G11" t="n">
-        <v>0.67</v>
+        <v>0.89</v>
       </c>
       <c r="H11" t="n">
         <v>0.51</v>
@@ -1137,7 +1137,7 @@
         <v>0.65</v>
       </c>
       <c r="J11" t="n">
-        <v>0.635</v>
+        <v>0.778</v>
       </c>
       <c r="K11" t="n">
         <v>3</v>
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.61</v>
+        <v>0.84</v>
       </c>
       <c r="G12" t="n">
-        <v>0.62</v>
+        <v>0.84</v>
       </c>
       <c r="H12" t="n">
         <v>0.78</v>
@@ -1200,7 +1200,7 @@
         <v>0.65</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6535</v>
+        <v>0.7995</v>
       </c>
       <c r="K12" t="n">
         <v>2</v>
@@ -1251,10 +1251,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="G13" t="n">
-        <v>0.57</v>
+        <v>0.79</v>
       </c>
       <c r="H13" t="n">
         <v>1</v>
@@ -1263,7 +1263,7 @@
         <v>0.65</v>
       </c>
       <c r="J13" t="n">
-        <v>0.665</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.79</v>
+        <v>0.68</v>
       </c>
       <c r="G14" t="n">
-        <v>0.79</v>
+        <v>0.68</v>
       </c>
       <c r="H14" t="n">
         <v>0.86</v>
@@ -1326,7 +1326,7 @@
         <v>0.84</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8115</v>
+        <v>0.74</v>
       </c>
       <c r="K14" t="n">
         <v>3</v>
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="H15" t="n">
         <v>0.93</v>
@@ -1389,7 +1389,7 @@
         <v>0.87</v>
       </c>
       <c r="J15" t="n">
-        <v>0.843</v>
+        <v>0.775</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.84</v>
+        <v>0.73</v>
       </c>
       <c r="G16" t="n">
-        <v>0.84</v>
+        <v>0.73</v>
       </c>
       <c r="H16" t="n">
         <v>0.7</v>
@@ -1452,7 +1452,7 @@
         <v>0.87</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8165</v>
+        <v>0.745</v>
       </c>
       <c r="K16" t="n">
         <v>2</v>
@@ -1503,10 +1503,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0.9</v>
+        <v>0.78</v>
       </c>
       <c r="G17" t="n">
-        <v>0.89</v>
+        <v>0.78</v>
       </c>
       <c r="H17" t="n">
         <v>0.86</v>
@@ -1515,7 +1515,7 @@
         <v>0.84</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8794999999999999</v>
+        <v>0.805</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0.91</v>
+        <v>0.79</v>
       </c>
       <c r="G18" t="n">
-        <v>0.91</v>
+        <v>0.79</v>
       </c>
       <c r="H18" t="n">
         <v>0.61</v>
@@ -1578,7 +1578,7 @@
         <v>0.84</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8395</v>
+        <v>0.7615</v>
       </c>
       <c r="K18" t="n">
         <v>2</v>
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.93</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>0.93</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H19" t="n">
         <v>0.29</v>
@@ -1641,7 +1641,7 @@
         <v>0.65</v>
       </c>
       <c r="J19" t="n">
-        <v>0.76</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="K19" t="n">
         <v>3</v>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
         <v>0.7</v>
@@ -1767,7 +1767,7 @@
         <v>0.65</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.8875</v>
       </c>
       <c r="K21" t="n">
         <v>2</v>
@@ -1818,10 +1818,10 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
         <v>0.93</v>
@@ -1830,7 +1830,7 @@
         <v>0.65</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9075</v>
+        <v>0.9335</v>
       </c>
       <c r="K22" t="n">
         <v>1</v>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
       <c r="G23" t="n">
-        <v>0.73</v>
+        <v>0.64</v>
       </c>
       <c r="H23" t="n">
         <v>1</v>
@@ -1893,7 +1893,7 @@
         <v>0.84</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8005</v>
+        <v>0.739</v>
       </c>
       <c r="K23" t="n">
         <v>1</v>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0.77</v>
+        <v>0.66</v>
       </c>
       <c r="G24" t="n">
-        <v>0.76</v>
+        <v>0.67</v>
       </c>
       <c r="H24" t="n">
         <v>0.78</v>
@@ -1956,7 +1956,7 @@
         <v>0.84</v>
       </c>
       <c r="J24" t="n">
-        <v>0.779</v>
+        <v>0.7145</v>
       </c>
       <c r="K24" t="n">
         <v>2</v>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H25" t="n">
         <v>0.51</v>
@@ -2019,7 +2019,7 @@
         <v>0.87</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7524999999999999</v>
+        <v>0.681</v>
       </c>
       <c r="K25" t="n">
         <v>3</v>
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0.78</v>
+        <v>0.95</v>
       </c>
       <c r="G26" t="n">
-        <v>0.78</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H26" t="n">
         <v>0.7</v>
@@ -2082,7 +2082,7 @@
         <v>0.65</v>
       </c>
       <c r="J26" t="n">
-        <v>0.7445000000000001</v>
+        <v>0.8515</v>
       </c>
       <c r="K26" t="n">
         <v>2</v>
@@ -2133,10 +2133,10 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0.73</v>
+        <v>0.9</v>
       </c>
       <c r="G27" t="n">
-        <v>0.73</v>
+        <v>0.9</v>
       </c>
       <c r="H27" t="n">
         <v>0.93</v>
@@ -2145,7 +2145,7 @@
         <v>0.65</v>
       </c>
       <c r="J27" t="n">
-        <v>0.758</v>
+        <v>0.8685</v>
       </c>
       <c r="K27" t="n">
         <v>1</v>
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="G28" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.86</v>
       </c>
       <c r="H28" t="n">
         <v>0.86</v>
@@ -2208,7 +2208,7 @@
         <v>0.65</v>
       </c>
       <c r="J28" t="n">
-        <v>0.718</v>
+        <v>0.8285</v>
       </c>
       <c r="K28" t="n">
         <v>3</v>
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
         <v>0.78</v>
@@ -2271,7 +2271,7 @@
         <v>0.65</v>
       </c>
       <c r="J29" t="n">
-        <v>0.871</v>
+        <v>0.9035</v>
       </c>
       <c r="K29" t="n">
         <v>2</v>
@@ -2322,10 +2322,10 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
       <c r="G30" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="H30" t="n">
         <v>1</v>
@@ -2334,7 +2334,7 @@
         <v>0.65</v>
       </c>
       <c r="J30" t="n">
-        <v>0.8985</v>
+        <v>0.9345</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0.9</v>
+        <v>0.96</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9</v>
+        <v>0.96</v>
       </c>
       <c r="H31" t="n">
         <v>0.78</v>
@@ -2397,7 +2397,7 @@
         <v>0.65</v>
       </c>
       <c r="J31" t="n">
-        <v>0.8385</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="K31" t="n">
         <v>3</v>
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H32" t="n">
         <v>1</v>
@@ -2460,7 +2460,7 @@
         <v>0.84</v>
       </c>
       <c r="J32" t="n">
-        <v>0.846</v>
+        <v>0.7745</v>
       </c>
       <c r="K32" t="n">
         <v>1</v>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0.82</v>
+        <v>0.71</v>
       </c>
       <c r="G33" t="n">
-        <v>0.82</v>
+        <v>0.72</v>
       </c>
       <c r="H33" t="n">
         <v>0.78</v>
@@ -2523,7 +2523,7 @@
         <v>0.84</v>
       </c>
       <c r="J33" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.747</v>
       </c>
       <c r="K33" t="n">
         <v>2</v>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0.85</v>
+        <v>0.73</v>
       </c>
       <c r="G34" t="n">
-        <v>0.84</v>
+        <v>0.74</v>
       </c>
       <c r="H34" t="n">
         <v>0.51</v>
@@ -2586,7 +2586,7 @@
         <v>0.87</v>
       </c>
       <c r="J34" t="n">
-        <v>0.7815</v>
+        <v>0.7105</v>
       </c>
       <c r="K34" t="n">
         <v>3</v>
@@ -2637,10 +2637,10 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0.83</v>
+        <v>0.98</v>
       </c>
       <c r="G35" t="n">
-        <v>0.82</v>
+        <v>0.98</v>
       </c>
       <c r="H35" t="n">
         <v>0.61</v>
@@ -2649,7 +2649,7 @@
         <v>0.65</v>
       </c>
       <c r="J35" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.8565</v>
       </c>
       <c r="K35" t="n">
         <v>3</v>
@@ -2700,10 +2700,10 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0.79</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>0.79</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H36" t="n">
         <v>0.86</v>
@@ -2712,7 +2712,7 @@
         <v>0.65</v>
       </c>
       <c r="J36" t="n">
-        <v>0.783</v>
+        <v>0.8804999999999999</v>
       </c>
       <c r="K36" t="n">
         <v>1</v>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0.75</v>
+        <v>0.91</v>
       </c>
       <c r="G37" t="n">
-        <v>0.75</v>
+        <v>0.91</v>
       </c>
       <c r="H37" t="n">
         <v>0.93</v>
@@ -2775,7 +2775,7 @@
         <v>0.65</v>
       </c>
       <c r="J37" t="n">
-        <v>0.771</v>
+        <v>0.875</v>
       </c>
       <c r="K37" t="n">
         <v>2</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>0.79</v>
+        <v>0.68</v>
       </c>
       <c r="G38" t="n">
-        <v>0.78</v>
+        <v>0.68</v>
       </c>
       <c r="H38" t="n">
         <v>1</v>
@@ -2838,7 +2838,7 @@
         <v>0.84</v>
       </c>
       <c r="J38" t="n">
-        <v>0.836</v>
+        <v>0.768</v>
       </c>
       <c r="K38" t="n">
         <v>1</v>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="G39" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="H39" t="n">
         <v>0.73</v>
@@ -2901,7 +2901,7 @@
         <v>0.84</v>
       </c>
       <c r="J39" t="n">
-        <v>0.795</v>
+        <v>0.727</v>
       </c>
       <c r="K39" t="n">
         <v>2</v>
@@ -2952,10 +2952,10 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="G40" t="n">
-        <v>0.82</v>
+        <v>0.72</v>
       </c>
       <c r="H40" t="n">
         <v>0.38</v>
@@ -2964,7 +2964,7 @@
         <v>0.84</v>
       </c>
       <c r="J40" t="n">
-        <v>0.738</v>
+        <v>0.667</v>
       </c>
       <c r="K40" t="n">
         <v>3</v>
@@ -3015,10 +3015,10 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>0.79</v>
+        <v>0.68</v>
       </c>
       <c r="G41" t="n">
-        <v>0.79</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H41" t="n">
         <v>0.78</v>
@@ -3027,7 +3027,7 @@
         <v>0.84</v>
       </c>
       <c r="J41" t="n">
-        <v>0.7955</v>
+        <v>0.7275</v>
       </c>
       <c r="K41" t="n">
         <v>3</v>
@@ -3078,10 +3078,10 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>0.82</v>
+        <v>0.7</v>
       </c>
       <c r="G42" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.71</v>
       </c>
       <c r="H42" t="n">
         <v>1</v>
@@ -3090,7 +3090,7 @@
         <v>0.84</v>
       </c>
       <c r="J42" t="n">
-        <v>0.8555</v>
+        <v>0.7845</v>
       </c>
       <c r="K42" t="n">
         <v>1</v>
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>0.84</v>
+        <v>0.73</v>
       </c>
       <c r="G43" t="n">
-        <v>0.84</v>
+        <v>0.73</v>
       </c>
       <c r="H43" t="n">
         <v>0.78</v>
@@ -3153,7 +3153,7 @@
         <v>0.87</v>
       </c>
       <c r="J43" t="n">
-        <v>0.8325</v>
+        <v>0.761</v>
       </c>
       <c r="K43" t="n">
         <v>2</v>
@@ -3204,10 +3204,10 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.59</v>
       </c>
       <c r="G44" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="H44" t="n">
         <v>0.86</v>
@@ -3216,7 +3216,7 @@
         <v>0.84</v>
       </c>
       <c r="J44" t="n">
-        <v>0.7465000000000001</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K44" t="n">
         <v>1</v>
@@ -3267,10 +3267,10 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
       <c r="G45" t="n">
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
       <c r="H45" t="n">
         <v>0.61</v>
@@ -3279,7 +3279,7 @@
         <v>0.84</v>
       </c>
       <c r="J45" t="n">
-        <v>0.7225</v>
+        <v>0.6575</v>
       </c>
       <c r="K45" t="n">
         <v>2</v>
@@ -3330,10 +3330,10 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>0.76</v>
+        <v>0.66</v>
       </c>
       <c r="G46" t="n">
-        <v>0.76</v>
+        <v>0.66</v>
       </c>
       <c r="H46" t="n">
         <v>0.29</v>
@@ -3342,7 +3342,7 @@
         <v>0.65</v>
       </c>
       <c r="J46" t="n">
-        <v>0.6495</v>
+        <v>0.5845</v>
       </c>
       <c r="K46" t="n">
         <v>3</v>
@@ -3393,10 +3393,10 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>0.61</v>
+        <v>0.85</v>
       </c>
       <c r="G47" t="n">
-        <v>0.61</v>
+        <v>0.85</v>
       </c>
       <c r="H47" t="n">
         <v>0.51</v>
@@ -3405,7 +3405,7 @@
         <v>0.65</v>
       </c>
       <c r="J47" t="n">
-        <v>0.596</v>
+        <v>0.752</v>
       </c>
       <c r="K47" t="n">
         <v>3</v>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="G48" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="H48" t="n">
         <v>0.78</v>
@@ -3468,7 +3468,7 @@
         <v>0.65</v>
       </c>
       <c r="J48" t="n">
-        <v>0.6175</v>
+        <v>0.7735</v>
       </c>
       <c r="K48" t="n">
         <v>2</v>
@@ -3519,10 +3519,10 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="G49" t="n">
-        <v>0.51</v>
+        <v>0.75</v>
       </c>
       <c r="H49" t="n">
         <v>1</v>
@@ -3531,7 +3531,7 @@
         <v>0.65</v>
       </c>
       <c r="J49" t="n">
-        <v>0.626</v>
+        <v>0.785</v>
       </c>
       <c r="K49" t="n">
         <v>1</v>
@@ -3582,10 +3582,10 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>0.71</v>
+        <v>0.61</v>
       </c>
       <c r="G50" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="H50" t="n">
         <v>0.93</v>
@@ -3594,7 +3594,7 @@
         <v>0.87</v>
       </c>
       <c r="J50" t="n">
-        <v>0.778</v>
+        <v>0.7165</v>
       </c>
       <c r="K50" t="n">
         <v>2</v>
@@ -3645,10 +3645,10 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>0.75</v>
+        <v>0.64</v>
       </c>
       <c r="G51" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="H51" t="n">
         <v>0.86</v>
@@ -3657,7 +3657,7 @@
         <v>0.87</v>
       </c>
       <c r="J51" t="n">
-        <v>0.79</v>
+        <v>0.722</v>
       </c>
       <c r="K51" t="n">
         <v>1</v>
@@ -3708,10 +3708,10 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>0.78</v>
+        <v>0.68</v>
       </c>
       <c r="G52" t="n">
-        <v>0.78</v>
+        <v>0.68</v>
       </c>
       <c r="H52" t="n">
         <v>0.61</v>
@@ -3720,7 +3720,7 @@
         <v>0.87</v>
       </c>
       <c r="J52" t="n">
-        <v>0.7595</v>
+        <v>0.6945</v>
       </c>
       <c r="K52" t="n">
         <v>3</v>
@@ -3771,10 +3771,10 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="G53" t="n">
-        <v>0.78</v>
+        <v>0.68</v>
       </c>
       <c r="H53" t="n">
         <v>0.83</v>
@@ -3783,7 +3783,7 @@
         <v>0.84</v>
       </c>
       <c r="J53" t="n">
-        <v>0.799</v>
+        <v>0.731</v>
       </c>
       <c r="K53" t="n">
         <v>1</v>
@@ -3834,10 +3834,10 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>0.8</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G54" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="H54" t="n">
         <v>0.51</v>
@@ -3846,7 +3846,7 @@
         <v>0.84</v>
       </c>
       <c r="J54" t="n">
-        <v>0.748</v>
+        <v>0.68</v>
       </c>
       <c r="K54" t="n">
         <v>2</v>
@@ -3897,10 +3897,10 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0.82</v>
+        <v>0.71</v>
       </c>
       <c r="G55" t="n">
-        <v>0.82</v>
+        <v>0.72</v>
       </c>
       <c r="H55" t="n">
         <v>0.06</v>
@@ -3909,7 +3909,7 @@
         <v>0.65</v>
       </c>
       <c r="J55" t="n">
-        <v>0.6425</v>
+        <v>0.5745</v>
       </c>
       <c r="K55" t="n">
         <v>3</v>
@@ -3960,10 +3960,10 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>0.5</v>
+        <v>0.42</v>
       </c>
       <c r="G56" t="n">
-        <v>0.51</v>
+        <v>0.43</v>
       </c>
       <c r="H56" t="n">
         <v>0.51</v>
@@ -3972,7 +3972,7 @@
         <v>0.84</v>
       </c>
       <c r="J56" t="n">
-        <v>0.5565</v>
+        <v>0.5044999999999999</v>
       </c>
       <c r="K56" t="n">
         <v>3</v>
@@ -4023,10 +4023,10 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>0.55</v>
+        <v>0.47</v>
       </c>
       <c r="G57" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="H57" t="n">
         <v>0.92</v>
@@ -4035,7 +4035,7 @@
         <v>0.84</v>
       </c>
       <c r="J57" t="n">
-        <v>0.671</v>
+        <v>0.619</v>
       </c>
       <c r="K57" t="n">
         <v>1</v>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>0.61</v>
+        <v>0.52</v>
       </c>
       <c r="G58" t="n">
-        <v>0.61</v>
+        <v>0.53</v>
       </c>
       <c r="H58" t="n">
         <v>0.73</v>
@@ -4098,7 +4098,7 @@
         <v>0.84</v>
       </c>
       <c r="J58" t="n">
-        <v>0.6685</v>
+        <v>0.6135</v>
       </c>
       <c r="K58" t="n">
         <v>2</v>
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>0.35</v>
+        <v>0.72</v>
       </c>
       <c r="G59" t="n">
-        <v>0.36</v>
+        <v>0.73</v>
       </c>
       <c r="H59" t="n">
         <v>0.51</v>
@@ -4161,7 +4161,7 @@
         <v>0.65</v>
       </c>
       <c r="J59" t="n">
-        <v>0.4305</v>
+        <v>0.671</v>
       </c>
       <c r="K59" t="n">
         <v>2</v>
@@ -4212,10 +4212,10 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>0.28</v>
+        <v>0.66</v>
       </c>
       <c r="G60" t="n">
-        <v>0.29</v>
+        <v>0.66</v>
       </c>
       <c r="H60" t="n">
         <v>0.83</v>
@@ -4224,7 +4224,7 @@
         <v>0.65</v>
       </c>
       <c r="J60" t="n">
-        <v>0.449</v>
+        <v>0.6925</v>
       </c>
       <c r="K60" t="n">
         <v>1</v>
@@ -4275,10 +4275,10 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>0.2</v>
+        <v>0.59</v>
       </c>
       <c r="G61" t="n">
-        <v>0.22</v>
+        <v>0.6</v>
       </c>
       <c r="H61" t="n">
         <v>0.92</v>
@@ -4287,7 +4287,7 @@
         <v>0.65</v>
       </c>
       <c r="J61" t="n">
-        <v>0.4185</v>
+        <v>0.6685</v>
       </c>
       <c r="K61" t="n">
         <v>3</v>
@@ -4338,10 +4338,10 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>0.67</v>
+        <v>0.89</v>
       </c>
       <c r="G62" t="n">
-        <v>0.67</v>
+        <v>0.89</v>
       </c>
       <c r="H62" t="n">
         <v>0.51</v>
@@ -4350,7 +4350,7 @@
         <v>0.65</v>
       </c>
       <c r="J62" t="n">
-        <v>0.635</v>
+        <v>0.778</v>
       </c>
       <c r="K62" t="n">
         <v>3</v>
@@ -4401,10 +4401,10 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>0.61</v>
+        <v>0.84</v>
       </c>
       <c r="G63" t="n">
-        <v>0.62</v>
+        <v>0.84</v>
       </c>
       <c r="H63" t="n">
         <v>0.78</v>
@@ -4413,7 +4413,7 @@
         <v>0.65</v>
       </c>
       <c r="J63" t="n">
-        <v>0.6535</v>
+        <v>0.7995</v>
       </c>
       <c r="K63" t="n">
         <v>2</v>
@@ -4464,10 +4464,10 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="G64" t="n">
-        <v>0.57</v>
+        <v>0.79</v>
       </c>
       <c r="H64" t="n">
         <v>1</v>
@@ -4476,7 +4476,7 @@
         <v>0.65</v>
       </c>
       <c r="J64" t="n">
-        <v>0.665</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="K64" t="n">
         <v>1</v>
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>0.53</v>
+        <v>0.45</v>
       </c>
       <c r="G65" t="n">
-        <v>0.54</v>
+        <v>0.46</v>
       </c>
       <c r="H65" t="n">
         <v>0.92</v>
@@ -4539,7 +4539,7 @@
         <v>0.84</v>
       </c>
       <c r="J65" t="n">
-        <v>0.658</v>
+        <v>0.606</v>
       </c>
       <c r="K65" t="n">
         <v>2</v>
@@ -4590,10 +4590,10 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>0.58</v>
+        <v>0.5</v>
       </c>
       <c r="G66" t="n">
-        <v>0.59</v>
+        <v>0.51</v>
       </c>
       <c r="H66" t="n">
         <v>0.83</v>
@@ -4602,7 +4602,7 @@
         <v>0.87</v>
       </c>
       <c r="J66" t="n">
-        <v>0.677</v>
+        <v>0.625</v>
       </c>
       <c r="K66" t="n">
         <v>1</v>
@@ -4653,10 +4653,10 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>0.63</v>
+        <v>0.54</v>
       </c>
       <c r="G67" t="n">
-        <v>0.63</v>
+        <v>0.55</v>
       </c>
       <c r="H67" t="n">
         <v>0.51</v>
@@ -4665,7 +4665,7 @@
         <v>0.87</v>
       </c>
       <c r="J67" t="n">
-        <v>0.642</v>
+        <v>0.587</v>
       </c>
       <c r="K67" t="n">
         <v>3</v>
@@ -4716,10 +4716,10 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>0.41</v>
+        <v>0.73</v>
       </c>
       <c r="G68" t="n">
-        <v>0.42</v>
+        <v>0.73</v>
       </c>
       <c r="H68" t="n">
         <v>0.46</v>
@@ -4728,7 +4728,7 @@
         <v>0.65</v>
       </c>
       <c r="J68" t="n">
-        <v>0.4595</v>
+        <v>0.664</v>
       </c>
       <c r="K68" t="n">
         <v>3</v>
@@ -4779,10 +4779,10 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>0.34</v>
+        <v>0.67</v>
       </c>
       <c r="G69" t="n">
-        <v>0.36</v>
+        <v>0.67</v>
       </c>
       <c r="H69" t="n">
         <v>0.8100000000000001</v>
@@ -4791,7 +4791,7 @@
         <v>0.65</v>
       </c>
       <c r="J69" t="n">
-        <v>0.4875</v>
+        <v>0.695</v>
       </c>
       <c r="K69" t="n">
         <v>1</v>
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>0.27</v>
+        <v>0.61</v>
       </c>
       <c r="G70" t="n">
-        <v>0.29</v>
+        <v>0.61</v>
       </c>
       <c r="H70" t="n">
         <v>0.91</v>
@@ -4854,7 +4854,7 @@
         <v>0.65</v>
       </c>
       <c r="J70" t="n">
-        <v>0.462</v>
+        <v>0.676</v>
       </c>
       <c r="K70" t="n">
         <v>2</v>
@@ -4905,10 +4905,10 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>0.67</v>
+        <v>0.58</v>
       </c>
       <c r="G71" t="n">
-        <v>0.67</v>
+        <v>0.58</v>
       </c>
       <c r="H71" t="n">
         <v>0.86</v>
@@ -4917,7 +4917,7 @@
         <v>0.84</v>
       </c>
       <c r="J71" t="n">
-        <v>0.7335</v>
+        <v>0.675</v>
       </c>
       <c r="K71" t="n">
         <v>1</v>
@@ -4968,10 +4968,10 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>0.71</v>
+        <v>0.61</v>
       </c>
       <c r="G72" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="H72" t="n">
         <v>0.61</v>
@@ -4980,7 +4980,7 @@
         <v>0.87</v>
       </c>
       <c r="J72" t="n">
-        <v>0.714</v>
+        <v>0.6525</v>
       </c>
       <c r="K72" t="n">
         <v>2</v>
@@ -5031,10 +5031,10 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>0.75</v>
+        <v>0.64</v>
       </c>
       <c r="G73" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="H73" t="n">
         <v>0.29</v>
@@ -5043,7 +5043,7 @@
         <v>0.65</v>
       </c>
       <c r="J73" t="n">
-        <v>0.643</v>
+        <v>0.575</v>
       </c>
       <c r="K73" t="n">
         <v>3</v>
@@ -5094,10 +5094,10 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>0.38</v>
+        <v>0.31</v>
       </c>
       <c r="G74" t="n">
-        <v>0.39</v>
+        <v>0.33</v>
       </c>
       <c r="H74" t="n">
         <v>1</v>
@@ -5106,7 +5106,7 @@
         <v>0.84</v>
       </c>
       <c r="J74" t="n">
-        <v>0.5765</v>
+        <v>0.5345</v>
       </c>
       <c r="K74" t="n">
         <v>1</v>
@@ -5157,10 +5157,10 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>0.43</v>
+        <v>0.37</v>
       </c>
       <c r="G75" t="n">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="H75" t="n">
         <v>0.78</v>
@@ -5169,7 +5169,7 @@
         <v>0.84</v>
       </c>
       <c r="J75" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.526</v>
       </c>
       <c r="K75" t="n">
         <v>2</v>
@@ -5220,10 +5220,10 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>0.49</v>
+        <v>0.42</v>
       </c>
       <c r="G76" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="H76" t="n">
         <v>0.51</v>
@@ -5232,7 +5232,7 @@
         <v>0.87</v>
       </c>
       <c r="J76" t="n">
-        <v>0.5545</v>
+        <v>0.509</v>
       </c>
       <c r="K76" t="n">
         <v>3</v>
@@ -5283,10 +5283,10 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="G77" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="H77" t="n">
         <v>0.61</v>
@@ -5295,7 +5295,7 @@
         <v>0.65</v>
       </c>
       <c r="J77" t="n">
-        <v>0.6745</v>
+        <v>0.8045</v>
       </c>
       <c r="K77" t="n">
         <v>3</v>
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>0.65</v>
+        <v>0.86</v>
       </c>
       <c r="G78" t="n">
-        <v>0.65</v>
+        <v>0.86</v>
       </c>
       <c r="H78" t="n">
         <v>0.86</v>
@@ -5358,7 +5358,7 @@
         <v>0.65</v>
       </c>
       <c r="J78" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.8285</v>
       </c>
       <c r="K78" t="n">
         <v>1</v>
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>0.61</v>
+        <v>0.82</v>
       </c>
       <c r="G79" t="n">
-        <v>0.61</v>
+        <v>0.82</v>
       </c>
       <c r="H79" t="n">
         <v>0.93</v>
@@ -5421,7 +5421,7 @@
         <v>0.65</v>
       </c>
       <c r="J79" t="n">
-        <v>0.68</v>
+        <v>0.8165</v>
       </c>
       <c r="K79" t="n">
         <v>2</v>
@@ -5472,10 +5472,10 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>0.37</v>
+        <v>0.71</v>
       </c>
       <c r="G80" t="n">
-        <v>0.38</v>
+        <v>0.71</v>
       </c>
       <c r="H80" t="n">
         <v>0.61</v>
@@ -5484,7 +5484,7 @@
         <v>0.65</v>
       </c>
       <c r="J80" t="n">
-        <v>0.4635</v>
+        <v>0.681</v>
       </c>
       <c r="K80" t="n">
         <v>2</v>
@@ -5535,10 +5535,10 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>0.29</v>
+        <v>0.64</v>
       </c>
       <c r="G81" t="n">
-        <v>0.31</v>
+        <v>0.65</v>
       </c>
       <c r="H81" t="n">
         <v>0.86</v>
@@ -5547,7 +5547,7 @@
         <v>0.65</v>
       </c>
       <c r="J81" t="n">
-        <v>0.465</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="K81" t="n">
         <v>1</v>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>0.21</v>
+        <v>0.58</v>
       </c>
       <c r="G82" t="n">
-        <v>0.23</v>
+        <v>0.58</v>
       </c>
       <c r="H82" t="n">
         <v>0.93</v>
@@ -5610,7 +5610,7 @@
         <v>0.65</v>
       </c>
       <c r="J82" t="n">
-        <v>0.427</v>
+        <v>0.6605</v>
       </c>
       <c r="K82" t="n">
         <v>3</v>
@@ -5661,10 +5661,10 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
       <c r="G83" t="n">
-        <v>0.34</v>
+        <v>0.28</v>
       </c>
       <c r="H83" t="n">
         <v>0.85</v>
@@ -5673,7 +5673,7 @@
         <v>0.77</v>
       </c>
       <c r="J83" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.4645</v>
       </c>
       <c r="K83" t="n">
         <v>1</v>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>0.36</v>
+        <v>0.3</v>
       </c>
       <c r="G84" t="n">
-        <v>0.37</v>
+        <v>0.31</v>
       </c>
       <c r="H84" t="n">
         <v>0.67</v>
@@ -5736,7 +5736,7 @@
         <v>0.84</v>
       </c>
       <c r="J84" t="n">
-        <v>0.4975</v>
+        <v>0.4585</v>
       </c>
       <c r="K84" t="n">
         <v>2</v>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="G85" t="n">
-        <v>0.41</v>
+        <v>0.35</v>
       </c>
       <c r="H85" t="n">
         <v>0.45</v>
@@ -5799,7 +5799,7 @@
         <v>0.84</v>
       </c>
       <c r="J85" t="n">
-        <v>0.4795</v>
+        <v>0.4375</v>
       </c>
       <c r="K85" t="n">
         <v>3</v>
@@ -5850,10 +5850,10 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>0.28</v>
+        <v>0.23</v>
       </c>
       <c r="G86" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="H86" t="n">
         <v>0.73</v>
@@ -5862,7 +5862,7 @@
         <v>0.84</v>
       </c>
       <c r="J86" t="n">
-        <v>0.4575</v>
+        <v>0.425</v>
       </c>
       <c r="K86" t="n">
         <v>1</v>
@@ -5913,10 +5913,10 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>0.32</v>
+        <v>0.26</v>
       </c>
       <c r="G87" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="H87" t="n">
         <v>0.51</v>
@@ -5925,7 +5925,7 @@
         <v>0.84</v>
       </c>
       <c r="J87" t="n">
-        <v>0.4395</v>
+        <v>0.404</v>
       </c>
       <c r="K87" t="n">
         <v>2</v>
@@ -5976,10 +5976,10 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>0.36</v>
+        <v>0.3</v>
       </c>
       <c r="G88" t="n">
-        <v>0.37</v>
+        <v>0.31</v>
       </c>
       <c r="H88" t="n">
         <v>0.23</v>
@@ -5988,7 +5988,7 @@
         <v>0.74</v>
       </c>
       <c r="J88" t="n">
-        <v>0.3945</v>
+        <v>0.3555</v>
       </c>
       <c r="K88" t="n">
         <v>3</v>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>0.57</v>
+        <v>0.49</v>
       </c>
       <c r="G89" t="n">
-        <v>0.58</v>
+        <v>0.5</v>
       </c>
       <c r="H89" t="n">
         <v>0.93</v>
@@ -6051,7 +6051,7 @@
         <v>0.84</v>
       </c>
       <c r="J89" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.634</v>
       </c>
       <c r="K89" t="n">
         <v>1</v>
@@ -6102,10 +6102,10 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>0.6</v>
+        <v>0.51</v>
       </c>
       <c r="G90" t="n">
-        <v>0.61</v>
+        <v>0.52</v>
       </c>
       <c r="H90" t="n">
         <v>0.78</v>
@@ -6114,7 +6114,7 @@
         <v>0.84</v>
       </c>
       <c r="J90" t="n">
-        <v>0.6755</v>
+        <v>0.617</v>
       </c>
       <c r="K90" t="n">
         <v>2</v>
@@ -6165,10 +6165,10 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>0.63</v>
+        <v>0.54</v>
       </c>
       <c r="G91" t="n">
-        <v>0.63</v>
+        <v>0.55</v>
       </c>
       <c r="H91" t="n">
         <v>0.61</v>
@@ -6177,7 +6177,7 @@
         <v>0.84</v>
       </c>
       <c r="J91" t="n">
-        <v>0.6575</v>
+        <v>0.6025</v>
       </c>
       <c r="K91" t="n">
         <v>3</v>
@@ -6228,10 +6228,10 @@
         </is>
       </c>
       <c r="F92" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="G92" t="n">
-        <v>0.57</v>
+        <v>0.49</v>
       </c>
       <c r="H92" t="n">
         <v>0.45</v>
@@ -6240,7 +6240,7 @@
         <v>0.87</v>
       </c>
       <c r="J92" t="n">
-        <v>0.588</v>
+        <v>0.536</v>
       </c>
       <c r="K92" t="n">
         <v>2</v>
@@ -6291,10 +6291,10 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="G93" t="n">
-        <v>0.48</v>
+        <v>0.41</v>
       </c>
       <c r="H93" t="n">
         <v>1</v>
@@ -6303,7 +6303,7 @@
         <v>0.84</v>
       </c>
       <c r="J93" t="n">
-        <v>0.635</v>
+        <v>0.5895</v>
       </c>
       <c r="K93" t="n">
         <v>1</v>
@@ -6354,10 +6354,10 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>0.37</v>
+        <v>0.31</v>
       </c>
       <c r="G94" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="H94" t="n">
         <v>0.45</v>
@@ -6366,7 +6366,7 @@
         <v>0.71</v>
       </c>
       <c r="J94" t="n">
-        <v>0.4405</v>
+        <v>0.4015</v>
       </c>
       <c r="K94" t="n">
         <v>3</v>
@@ -6417,10 +6417,10 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>0.34</v>
+        <v>0.28</v>
       </c>
       <c r="G95" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="H95" t="n">
         <v>0.86</v>
@@ -6429,7 +6429,7 @@
         <v>0.77</v>
       </c>
       <c r="J95" t="n">
-        <v>0.512</v>
+        <v>0.4765</v>
       </c>
       <c r="K95" t="n">
         <v>1</v>
@@ -6480,10 +6480,10 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>0.37</v>
+        <v>0.31</v>
       </c>
       <c r="G96" t="n">
-        <v>0.39</v>
+        <v>0.33</v>
       </c>
       <c r="H96" t="n">
         <v>0.7</v>
@@ -6492,7 +6492,7 @@
         <v>0.77</v>
       </c>
       <c r="J96" t="n">
-        <v>0.503</v>
+        <v>0.464</v>
       </c>
       <c r="K96" t="n">
         <v>2</v>
@@ -6543,10 +6543,10 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>0.41</v>
+        <v>0.34</v>
       </c>
       <c r="G97" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="H97" t="n">
         <v>0.51</v>
@@ -6555,7 +6555,7 @@
         <v>0.77</v>
       </c>
       <c r="J97" t="n">
-        <v>0.4875</v>
+        <v>0.4455</v>
       </c>
       <c r="K97" t="n">
         <v>3</v>
@@ -6606,10 +6606,10 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="G98" t="n">
-        <v>0.39</v>
+        <v>0.33</v>
       </c>
       <c r="H98" t="n">
         <v>0.76</v>
@@ -6618,7 +6618,7 @@
         <v>0.84</v>
       </c>
       <c r="J98" t="n">
-        <v>0.5285</v>
+        <v>0.4895</v>
       </c>
       <c r="K98" t="n">
         <v>1</v>
@@ -6669,10 +6669,10 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>0.42</v>
+        <v>0.35</v>
       </c>
       <c r="G99" t="n">
-        <v>0.43</v>
+        <v>0.37</v>
       </c>
       <c r="H99" t="n">
         <v>0.5600000000000001</v>
@@ -6681,7 +6681,7 @@
         <v>0.84</v>
       </c>
       <c r="J99" t="n">
-        <v>0.5145</v>
+        <v>0.4725</v>
       </c>
       <c r="K99" t="n">
         <v>2</v>
@@ -6732,10 +6732,10 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>0.46</v>
+        <v>0.39</v>
       </c>
       <c r="G100" t="n">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="H100" t="n">
         <v>0.32</v>
@@ -6744,7 +6744,7 @@
         <v>0.74</v>
       </c>
       <c r="J100" t="n">
-        <v>0.4775</v>
+        <v>0.432</v>
       </c>
       <c r="K100" t="n">
         <v>3</v>
@@ -6795,10 +6795,10 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>0.65</v>
+        <v>0.55</v>
       </c>
       <c r="G101" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H101" t="n">
         <v>0.86</v>
@@ -6807,7 +6807,7 @@
         <v>0.84</v>
       </c>
       <c r="J101" t="n">
-        <v>0.7205</v>
+        <v>0.659</v>
       </c>
       <c r="K101" t="n">
         <v>1</v>
@@ -6858,10 +6858,10 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>0.67</v>
+        <v>0.58</v>
       </c>
       <c r="G102" t="n">
-        <v>0.68</v>
+        <v>0.59</v>
       </c>
       <c r="H102" t="n">
         <v>0.7</v>
@@ -6870,7 +6870,7 @@
         <v>0.87</v>
       </c>
       <c r="J102" t="n">
-        <v>0.7095</v>
+        <v>0.651</v>
       </c>
       <c r="K102" t="n">
         <v>2</v>
@@ -6921,10 +6921,10 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G103" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
       <c r="H103" t="n">
         <v>0.51</v>
@@ -6933,7 +6933,7 @@
         <v>0.87</v>
       </c>
       <c r="J103" t="n">
-        <v>0.6875</v>
+        <v>0.626</v>
       </c>
       <c r="K103" t="n">
         <v>3</v>
@@ -6984,10 +6984,10 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -6996,10 +6996,10 @@
         <v>0.31</v>
       </c>
       <c r="J104" t="n">
-        <v>0.0465</v>
+        <v>0.3945</v>
       </c>
       <c r="K104" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L104" t="n">
         <v>3000</v>
@@ -7047,10 +7047,10 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="H105" t="n">
         <v>0.06</v>
@@ -7059,10 +7059,10 @@
         <v>0.65</v>
       </c>
       <c r="J105" t="n">
-        <v>0.1095</v>
+        <v>0.3925</v>
       </c>
       <c r="K105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L105" t="n">
         <v>3000</v>
@@ -7110,10 +7110,10 @@
         </is>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="H106" t="n">
         <v>0.63</v>
@@ -7122,7 +7122,7 @@
         <v>0.65</v>
       </c>
       <c r="J106" t="n">
-        <v>0.2235</v>
+        <v>0.4255</v>
       </c>
       <c r="K106" t="n">
         <v>1</v>
@@ -7173,10 +7173,10 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>0.68</v>
+        <v>0.59</v>
       </c>
       <c r="G107" t="n">
-        <v>0.68</v>
+        <v>0.59</v>
       </c>
       <c r="H107" t="n">
         <v>0.78</v>
@@ -7185,7 +7185,7 @@
         <v>0.87</v>
       </c>
       <c r="J107" t="n">
-        <v>0.7285</v>
+        <v>0.67</v>
       </c>
       <c r="K107" t="n">
         <v>3</v>
@@ -7236,10 +7236,10 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
       <c r="G108" t="n">
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
       <c r="H108" t="n">
         <v>1</v>
@@ -7248,7 +7248,7 @@
         <v>0.87</v>
       </c>
       <c r="J108" t="n">
-        <v>0.805</v>
+        <v>0.74</v>
       </c>
       <c r="K108" t="n">
         <v>1</v>
@@ -7299,10 +7299,10 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>0.78</v>
+        <v>0.67</v>
       </c>
       <c r="G109" t="n">
-        <v>0.77</v>
+        <v>0.67</v>
       </c>
       <c r="H109" t="n">
         <v>0.78</v>
@@ -7311,7 +7311,7 @@
         <v>0.87</v>
       </c>
       <c r="J109" t="n">
-        <v>0.79</v>
+        <v>0.722</v>
       </c>
       <c r="K109" t="n">
         <v>2</v>
@@ -7362,10 +7362,10 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>0.45</v>
+        <v>0.38</v>
       </c>
       <c r="G110" t="n">
-        <v>0.46</v>
+        <v>0.39</v>
       </c>
       <c r="H110" t="n">
         <v>0.83</v>
@@ -7374,7 +7374,7 @@
         <v>0.87</v>
       </c>
       <c r="J110" t="n">
-        <v>0.5925</v>
+        <v>0.547</v>
       </c>
       <c r="K110" t="n">
         <v>3</v>
@@ -7425,10 +7425,10 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>0.53</v>
+        <v>0.45</v>
       </c>
       <c r="G111" t="n">
-        <v>0.54</v>
+        <v>0.46</v>
       </c>
       <c r="H111" t="n">
         <v>0.83</v>
@@ -7437,7 +7437,7 @@
         <v>0.87</v>
       </c>
       <c r="J111" t="n">
-        <v>0.6445</v>
+        <v>0.5925</v>
       </c>
       <c r="K111" t="n">
         <v>1</v>
@@ -7488,10 +7488,10 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>0.57</v>
+        <v>0.49</v>
       </c>
       <c r="G112" t="n">
-        <v>0.58</v>
+        <v>0.5</v>
       </c>
       <c r="H112" t="n">
         <v>0.63</v>
@@ -7500,7 +7500,7 @@
         <v>0.87</v>
       </c>
       <c r="J112" t="n">
-        <v>0.6304999999999999</v>
+        <v>0.5785</v>
       </c>
       <c r="K112" t="n">
         <v>2</v>
@@ -7566,7 +7566,7 @@
         <v>0.888</v>
       </c>
       <c r="K113" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L113" t="n">
         <v>2200</v>
@@ -7614,10 +7614,10 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="G114" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="H114" t="n">
         <v>0.85</v>
@@ -7626,10 +7626,10 @@
         <v>0.77</v>
       </c>
       <c r="J114" t="n">
-        <v>0.8995</v>
+        <v>0.9355</v>
       </c>
       <c r="K114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L114" t="n">
         <v>2200</v>
@@ -7677,10 +7677,10 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="G115" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="H115" t="n">
         <v>0.93</v>
@@ -7689,10 +7689,10 @@
         <v>0.77</v>
       </c>
       <c r="J115" t="n">
-        <v>0.8635</v>
+        <v>0.9515</v>
       </c>
       <c r="K115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L115" t="n">
         <v>2200</v>
@@ -7740,10 +7740,10 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="G116" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="H116" t="n">
         <v>0.51</v>
@@ -7752,10 +7752,10 @@
         <v>0.77</v>
       </c>
       <c r="J116" t="n">
-        <v>0.8575</v>
+        <v>0.8675</v>
       </c>
       <c r="K116" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L116" t="n">
         <v>1800</v>
@@ -7803,10 +7803,10 @@
         </is>
       </c>
       <c r="F117" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="G117" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="H117" t="n">
         <v>0.78</v>
@@ -7815,10 +7815,10 @@
         <v>0.77</v>
       </c>
       <c r="J117" t="n">
-        <v>0.8725000000000001</v>
+        <v>0.9215</v>
       </c>
       <c r="K117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L117" t="n">
         <v>1800</v>
@@ -7866,10 +7866,10 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="G118" t="n">
-        <v>0.84</v>
+        <v>1</v>
       </c>
       <c r="H118" t="n">
         <v>0.93</v>
@@ -7878,10 +7878,10 @@
         <v>0.77</v>
       </c>
       <c r="J118" t="n">
-        <v>0.8505</v>
+        <v>0.9515</v>
       </c>
       <c r="K118" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L118" t="n">
         <v>1800</v>
@@ -7929,10 +7929,10 @@
         </is>
       </c>
       <c r="F119" t="n">
-        <v>0.98</v>
+        <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>0.97</v>
+        <v>1</v>
       </c>
       <c r="H119" t="n">
         <v>0.5600000000000001</v>
@@ -7941,10 +7941,10 @@
         <v>0.77</v>
       </c>
       <c r="J119" t="n">
-        <v>0.861</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="K119" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L119" t="n">
         <v>1700</v>
@@ -7992,10 +7992,10 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G120" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H120" t="n">
         <v>0.93</v>
@@ -8004,7 +8004,7 @@
         <v>0.77</v>
       </c>
       <c r="J120" t="n">
-        <v>0.8865</v>
+        <v>0.9515</v>
       </c>
       <c r="K120" t="n">
         <v>1</v>
@@ -8055,10 +8055,10 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="H121" t="n">
         <v>0.76</v>
@@ -8067,10 +8067,10 @@
         <v>0.77</v>
       </c>
       <c r="J121" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.9175</v>
       </c>
       <c r="K121" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L121" t="n">
         <v>1700</v>
@@ -8118,10 +8118,10 @@
         </is>
       </c>
       <c r="F122" t="n">
-        <v>0.34</v>
+        <v>0.28</v>
       </c>
       <c r="G122" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="H122" t="n">
         <v>0.61</v>
@@ -8130,7 +8130,7 @@
         <v>0.77</v>
       </c>
       <c r="J122" t="n">
-        <v>0.462</v>
+        <v>0.4265</v>
       </c>
       <c r="K122" t="n">
         <v>3</v>
@@ -8181,10 +8181,10 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="G123" t="n">
-        <v>0.43</v>
+        <v>0.37</v>
       </c>
       <c r="H123" t="n">
         <v>1</v>
@@ -8193,7 +8193,7 @@
         <v>0.84</v>
       </c>
       <c r="J123" t="n">
-        <v>0.6025</v>
+        <v>0.5635</v>
       </c>
       <c r="K123" t="n">
         <v>1</v>
@@ -8244,10 +8244,10 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>0.52</v>
+        <v>0.45</v>
       </c>
       <c r="G124" t="n">
-        <v>0.53</v>
+        <v>0.46</v>
       </c>
       <c r="H124" t="n">
         <v>0.51</v>
@@ -8256,7 +8256,7 @@
         <v>0.84</v>
       </c>
       <c r="J124" t="n">
-        <v>0.5695</v>
+        <v>0.524</v>
       </c>
       <c r="K124" t="n">
         <v>2</v>
@@ -8307,10 +8307,10 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>0.77</v>
+        <v>0.98</v>
       </c>
       <c r="G125" t="n">
-        <v>0.77</v>
+        <v>0.97</v>
       </c>
       <c r="H125" t="n">
         <v>0.51</v>
@@ -8319,7 +8319,7 @@
         <v>0.65</v>
       </c>
       <c r="J125" t="n">
-        <v>0.7</v>
+        <v>0.833</v>
       </c>
       <c r="K125" t="n">
         <v>2</v>
@@ -8370,10 +8370,10 @@
         </is>
       </c>
       <c r="F126" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="G126" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="H126" t="n">
         <v>0.93</v>
@@ -8382,7 +8382,7 @@
         <v>0.65</v>
       </c>
       <c r="J126" t="n">
-        <v>0.732</v>
+        <v>0.875</v>
       </c>
       <c r="K126" t="n">
         <v>1</v>
@@ -8433,10 +8433,10 @@
         </is>
       </c>
       <c r="F127" t="n">
-        <v>0.6</v>
+        <v>0.83</v>
       </c>
       <c r="G127" t="n">
-        <v>0.6</v>
+        <v>0.83</v>
       </c>
       <c r="H127" t="n">
         <v>0.61</v>
@@ -8445,7 +8445,7 @@
         <v>0.65</v>
       </c>
       <c r="J127" t="n">
-        <v>0.6095</v>
+        <v>0.759</v>
       </c>
       <c r="K127" t="n">
         <v>3</v>
@@ -8496,10 +8496,10 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>0.51</v>
+        <v>0.43</v>
       </c>
       <c r="G128" t="n">
-        <v>0.51</v>
+        <v>0.44</v>
       </c>
       <c r="H128" t="n">
         <v>0.86</v>
@@ -8508,7 +8508,7 @@
         <v>0.84</v>
       </c>
       <c r="J128" t="n">
-        <v>0.6294999999999999</v>
+        <v>0.581</v>
       </c>
       <c r="K128" t="n">
         <v>2</v>
@@ -8559,10 +8559,10 @@
         </is>
       </c>
       <c r="F129" t="n">
-        <v>0.62</v>
+        <v>0.53</v>
       </c>
       <c r="G129" t="n">
-        <v>0.63</v>
+        <v>0.54</v>
       </c>
       <c r="H129" t="n">
         <v>0.15</v>
@@ -8571,7 +8571,7 @@
         <v>0.53</v>
       </c>
       <c r="J129" t="n">
-        <v>0.516</v>
+        <v>0.4575</v>
       </c>
       <c r="K129" t="n">
         <v>3</v>
@@ -8685,10 +8685,10 @@
         </is>
       </c>
       <c r="F131" t="n">
-        <v>0.55</v>
+        <v>0.46</v>
       </c>
       <c r="G131" t="n">
-        <v>0.55</v>
+        <v>0.47</v>
       </c>
       <c r="H131" t="n">
         <v>0.86</v>
@@ -8697,7 +8697,7 @@
         <v>0.84</v>
       </c>
       <c r="J131" t="n">
-        <v>0.6555</v>
+        <v>0.6005</v>
       </c>
       <c r="K131" t="n">
         <v>2</v>
@@ -8748,10 +8748,10 @@
         </is>
       </c>
       <c r="F132" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="G132" t="n">
-        <v>0.67</v>
+        <v>0.58</v>
       </c>
       <c r="H132" t="n">
         <v>0.15</v>
@@ -8760,7 +8760,7 @@
         <v>0.53</v>
       </c>
       <c r="J132" t="n">
-        <v>0.545</v>
+        <v>0.4835</v>
       </c>
       <c r="K132" t="n">
         <v>3</v>
@@ -8874,10 +8874,10 @@
         </is>
       </c>
       <c r="F134" t="n">
-        <v>0.31</v>
+        <v>0.26</v>
       </c>
       <c r="G134" t="n">
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
       <c r="H134" t="n">
         <v>0.76</v>
@@ -8886,7 +8886,7 @@
         <v>0.84</v>
       </c>
       <c r="J134" t="n">
-        <v>0.483</v>
+        <v>0.4505</v>
       </c>
       <c r="K134" t="n">
         <v>3</v>
@@ -8937,10 +8937,10 @@
         </is>
       </c>
       <c r="F135" t="n">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
       <c r="G135" t="n">
-        <v>0.41</v>
+        <v>0.35</v>
       </c>
       <c r="H135" t="n">
         <v>0.93</v>
@@ -8949,7 +8949,7 @@
         <v>0.87</v>
       </c>
       <c r="J135" t="n">
-        <v>0.58</v>
+        <v>0.541</v>
       </c>
       <c r="K135" t="n">
         <v>1</v>
@@ -9000,10 +9000,10 @@
         </is>
       </c>
       <c r="F136" t="n">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="G136" t="n">
-        <v>0.48</v>
+        <v>0.41</v>
       </c>
       <c r="H136" t="n">
         <v>0.67</v>
@@ -9012,7 +9012,7 @@
         <v>0.87</v>
       </c>
       <c r="J136" t="n">
-        <v>0.5735</v>
+        <v>0.528</v>
       </c>
       <c r="K136" t="n">
         <v>2</v>
@@ -9063,10 +9063,10 @@
         </is>
       </c>
       <c r="F137" t="n">
-        <v>0.21</v>
+        <v>0.59</v>
       </c>
       <c r="G137" t="n">
-        <v>0.31</v>
+        <v>0.6</v>
       </c>
       <c r="H137" t="n">
         <v>0.51</v>
@@ -9075,7 +9075,7 @@
         <v>0.65</v>
       </c>
       <c r="J137" t="n">
-        <v>0.371</v>
+        <v>0.5865</v>
       </c>
       <c r="K137" t="n">
         <v>2</v>
@@ -9126,10 +9126,10 @@
         </is>
       </c>
       <c r="F138" t="n">
-        <v>0.13</v>
+        <v>0.54</v>
       </c>
       <c r="G138" t="n">
-        <v>0.24</v>
+        <v>0.54</v>
       </c>
       <c r="H138" t="n">
         <v>0.78</v>
@@ -9138,7 +9138,7 @@
         <v>0.65</v>
       </c>
       <c r="J138" t="n">
-        <v>0.3765</v>
+        <v>0.6045</v>
       </c>
       <c r="K138" t="n">
         <v>1</v>
@@ -9189,10 +9189,10 @@
         </is>
       </c>
       <c r="F139" t="n">
-        <v>0.06</v>
+        <v>0.46</v>
       </c>
       <c r="G139" t="n">
-        <v>0.16</v>
+        <v>0.47</v>
       </c>
       <c r="H139" t="n">
         <v>0.93</v>
@@ -9201,7 +9201,7 @@
         <v>0.65</v>
       </c>
       <c r="J139" t="n">
-        <v>0.3575</v>
+        <v>0.586</v>
       </c>
       <c r="K139" t="n">
         <v>3</v>
@@ -9252,10 +9252,10 @@
         </is>
       </c>
       <c r="F140" t="n">
-        <v>0.41</v>
+        <v>0.76</v>
       </c>
       <c r="G140" t="n">
-        <v>0.42</v>
+        <v>0.76</v>
       </c>
       <c r="H140" t="n">
         <v>0.61</v>
@@ -9264,10 +9264,10 @@
         <v>0.65</v>
       </c>
       <c r="J140" t="n">
-        <v>0.4895</v>
+        <v>0.7135</v>
       </c>
       <c r="K140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L140" t="n">
         <v>2100</v>
@@ -9315,10 +9315,10 @@
         </is>
       </c>
       <c r="F141" t="n">
-        <v>0.29</v>
+        <v>0.68</v>
       </c>
       <c r="G141" t="n">
-        <v>0.33</v>
+        <v>0.68</v>
       </c>
       <c r="H141" t="n">
         <v>0.93</v>
@@ -9327,10 +9327,10 @@
         <v>0.65</v>
       </c>
       <c r="J141" t="n">
-        <v>0.486</v>
+        <v>0.7255</v>
       </c>
       <c r="K141" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L141" t="n">
         <v>2100</v>
@@ -9378,10 +9378,10 @@
         </is>
       </c>
       <c r="F142" t="n">
-        <v>0.19</v>
+        <v>0.61</v>
       </c>
       <c r="G142" t="n">
-        <v>0.27</v>
+        <v>0.62</v>
       </c>
       <c r="H142" t="n">
         <v>0.86</v>
@@ -9390,7 +9390,7 @@
         <v>0.65</v>
       </c>
       <c r="J142" t="n">
-        <v>0.421</v>
+        <v>0.6695</v>
       </c>
       <c r="K142" t="n">
         <v>3</v>
@@ -9441,10 +9441,10 @@
         </is>
       </c>
       <c r="F143" t="n">
-        <v>0.2</v>
+        <v>0.63</v>
       </c>
       <c r="G143" t="n">
-        <v>0.22</v>
+        <v>0.64</v>
       </c>
       <c r="H143" t="n">
         <v>0.7</v>
@@ -9453,7 +9453,7 @@
         <v>0.65</v>
       </c>
       <c r="J143" t="n">
-        <v>0.3745</v>
+        <v>0.6505</v>
       </c>
       <c r="K143" t="n">
         <v>1</v>
@@ -9504,10 +9504,10 @@
         </is>
       </c>
       <c r="F144" t="n">
-        <v>0.1</v>
+        <v>0.55</v>
       </c>
       <c r="G144" t="n">
-        <v>0.14</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H144" t="n">
         <v>0.93</v>
@@ -9516,7 +9516,7 @@
         <v>0.65</v>
       </c>
       <c r="J144" t="n">
-        <v>0.3625</v>
+        <v>0.6445</v>
       </c>
       <c r="K144" t="n">
         <v>2</v>
@@ -9567,10 +9567,10 @@
         </is>
       </c>
       <c r="F145" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="G145" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="H145" t="n">
         <v>0.7</v>
@@ -9579,7 +9579,7 @@
         <v>0.65</v>
       </c>
       <c r="J145" t="n">
-        <v>0.2375</v>
+        <v>0.5175</v>
       </c>
       <c r="K145" t="n">
         <v>3</v>
@@ -9630,10 +9630,10 @@
         </is>
       </c>
       <c r="F146" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.87</v>
       </c>
       <c r="G146" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.87</v>
       </c>
       <c r="H146" t="n">
         <v>0.61</v>
@@ -9642,7 +9642,7 @@
         <v>0.65</v>
       </c>
       <c r="J146" t="n">
-        <v>0.5835</v>
+        <v>0.785</v>
       </c>
       <c r="K146" t="n">
         <v>2</v>
@@ -9693,10 +9693,10 @@
         </is>
       </c>
       <c r="F147" t="n">
-        <v>0.49</v>
+        <v>0.8</v>
       </c>
       <c r="G147" t="n">
-        <v>0.49</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H147" t="n">
         <v>0.86</v>
@@ -9705,7 +9705,7 @@
         <v>0.65</v>
       </c>
       <c r="J147" t="n">
-        <v>0.588</v>
+        <v>0.793</v>
       </c>
       <c r="K147" t="n">
         <v>1</v>
@@ -9756,10 +9756,10 @@
         </is>
       </c>
       <c r="F148" t="n">
-        <v>0.39</v>
+        <v>0.72</v>
       </c>
       <c r="G148" t="n">
-        <v>0.4</v>
+        <v>0.72</v>
       </c>
       <c r="H148" t="n">
         <v>0.86</v>
@@ -9768,7 +9768,7 @@
         <v>0.65</v>
       </c>
       <c r="J148" t="n">
-        <v>0.5265</v>
+        <v>0.7375</v>
       </c>
       <c r="K148" t="n">
         <v>3</v>
@@ -9819,10 +9819,10 @@
         </is>
       </c>
       <c r="F149" t="n">
-        <v>0.31</v>
+        <v>0.26</v>
       </c>
       <c r="G149" t="n">
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
       <c r="H149" t="n">
         <v>0.45</v>
@@ -9831,7 +9831,7 @@
         <v>0.71</v>
       </c>
       <c r="J149" t="n">
-        <v>0.4015</v>
+        <v>0.369</v>
       </c>
       <c r="K149" t="n">
         <v>3</v>
@@ -9882,10 +9882,10 @@
         </is>
       </c>
       <c r="F150" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="G150" t="n">
-        <v>0.41</v>
+        <v>0.34</v>
       </c>
       <c r="H150" t="n">
         <v>0.93</v>
@@ -9894,7 +9894,7 @@
         <v>0.84</v>
       </c>
       <c r="J150" t="n">
-        <v>0.5755</v>
+        <v>0.53</v>
       </c>
       <c r="K150" t="n">
         <v>2</v>
@@ -9945,10 +9945,10 @@
         </is>
       </c>
       <c r="F151" t="n">
-        <v>0.48</v>
+        <v>0.41</v>
       </c>
       <c r="G151" t="n">
-        <v>0.49</v>
+        <v>0.42</v>
       </c>
       <c r="H151" t="n">
         <v>0.67</v>
@@ -9957,7 +9957,7 @@
         <v>0.84</v>
       </c>
       <c r="J151" t="n">
-        <v>0.5755</v>
+        <v>0.53</v>
       </c>
       <c r="K151" t="n">
         <v>1</v>
@@ -10008,10 +10008,10 @@
         </is>
       </c>
       <c r="F152" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="G152" t="n">
-        <v>0.43</v>
+        <v>0.37</v>
       </c>
       <c r="H152" t="n">
         <v>0.86</v>
@@ -10020,7 +10020,7 @@
         <v>0.84</v>
       </c>
       <c r="J152" t="n">
-        <v>0.5745</v>
+        <v>0.5355</v>
       </c>
       <c r="K152" t="n">
         <v>3</v>
@@ -10071,10 +10071,10 @@
         </is>
       </c>
       <c r="F153" t="n">
-        <v>0.49</v>
+        <v>0.42</v>
       </c>
       <c r="G153" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="H153" t="n">
         <v>0.86</v>
@@ -10083,7 +10083,7 @@
         <v>0.84</v>
       </c>
       <c r="J153" t="n">
-        <v>0.62</v>
+        <v>0.5745</v>
       </c>
       <c r="K153" t="n">
         <v>1</v>
@@ -10134,10 +10134,10 @@
         </is>
       </c>
       <c r="F154" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="G154" t="n">
-        <v>0.57</v>
+        <v>0.49</v>
       </c>
       <c r="H154" t="n">
         <v>0.51</v>
@@ -10146,7 +10146,7 @@
         <v>0.87</v>
       </c>
       <c r="J154" t="n">
-        <v>0.6</v>
+        <v>0.548</v>
       </c>
       <c r="K154" t="n">
         <v>2</v>
@@ -10197,10 +10197,10 @@
         </is>
       </c>
       <c r="F155" t="n">
-        <v>0.82</v>
+        <v>0.71</v>
       </c>
       <c r="G155" t="n">
-        <v>0.82</v>
+        <v>0.71</v>
       </c>
       <c r="H155" t="n">
         <v>0.29</v>
@@ -10209,7 +10209,7 @@
         <v>0.65</v>
       </c>
       <c r="J155" t="n">
-        <v>0.6885</v>
+        <v>0.617</v>
       </c>
       <c r="K155" t="n">
         <v>3</v>
@@ -10260,10 +10260,10 @@
         </is>
       </c>
       <c r="F156" t="n">
-        <v>0.84</v>
+        <v>0.73</v>
       </c>
       <c r="G156" t="n">
-        <v>0.84</v>
+        <v>0.73</v>
       </c>
       <c r="H156" t="n">
         <v>0.51</v>
@@ -10272,7 +10272,7 @@
         <v>0.8</v>
       </c>
       <c r="J156" t="n">
-        <v>0.768</v>
+        <v>0.6965</v>
       </c>
       <c r="K156" t="n">
         <v>2</v>
@@ -10323,10 +10323,10 @@
         </is>
       </c>
       <c r="F157" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="G157" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="H157" t="n">
         <v>0.7</v>
@@ -10335,7 +10335,7 @@
         <v>0.87</v>
       </c>
       <c r="J157" t="n">
-        <v>0.8295</v>
+        <v>0.758</v>
       </c>
       <c r="K157" t="n">
         <v>1</v>
@@ -10386,10 +10386,10 @@
         </is>
       </c>
       <c r="F158" t="n">
-        <v>0.84</v>
+        <v>0.92</v>
       </c>
       <c r="G158" t="n">
-        <v>0.83</v>
+        <v>0.91</v>
       </c>
       <c r="H158" t="n">
         <v>0.61</v>
@@ -10398,7 +10398,7 @@
         <v>0.65</v>
       </c>
       <c r="J158" t="n">
-        <v>0.762</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="K158" t="n">
         <v>3</v>
@@ -10449,10 +10449,10 @@
         </is>
       </c>
       <c r="F159" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="G159" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.89</v>
       </c>
       <c r="H159" t="n">
         <v>0.86</v>
@@ -10461,10 +10461,10 @@
         <v>0.65</v>
       </c>
       <c r="J159" t="n">
-        <v>0.796</v>
+        <v>0.848</v>
       </c>
       <c r="K159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L159" t="n">
         <v>980</v>
@@ -10512,10 +10512,10 @@
         </is>
       </c>
       <c r="F160" t="n">
-        <v>0.78</v>
+        <v>0.87</v>
       </c>
       <c r="G160" t="n">
-        <v>0.78</v>
+        <v>0.87</v>
       </c>
       <c r="H160" t="n">
         <v>0.93</v>
@@ -10524,10 +10524,10 @@
         <v>0.65</v>
       </c>
       <c r="J160" t="n">
-        <v>0.7905</v>
+        <v>0.849</v>
       </c>
       <c r="K160" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L160" t="n">
         <v>980</v>
@@ -10641,7 +10641,7 @@
         <v>1</v>
       </c>
       <c r="G162" t="n">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="H162" t="n">
         <v>0.76</v>
@@ -10650,7 +10650,7 @@
         <v>0.77</v>
       </c>
       <c r="J162" t="n">
-        <v>0.914</v>
+        <v>0.9175</v>
       </c>
       <c r="K162" t="n">
         <v>2</v>
@@ -10701,10 +10701,10 @@
         </is>
       </c>
       <c r="F163" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="G163" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="H163" t="n">
         <v>1</v>
@@ -10713,7 +10713,7 @@
         <v>0.77</v>
       </c>
       <c r="J163" t="n">
-        <v>0.9295</v>
+        <v>0.9655</v>
       </c>
       <c r="K163" t="n">
         <v>1</v>
@@ -10764,10 +10764,10 @@
         </is>
       </c>
       <c r="F164" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="G164" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -10776,7 +10776,7 @@
         <v>0.48</v>
       </c>
       <c r="J164" t="n">
-        <v>0.5595</v>
+        <v>0.4945</v>
       </c>
       <c r="K164" t="n">
         <v>3</v>
@@ -10827,10 +10827,10 @@
         </is>
       </c>
       <c r="F165" t="n">
-        <v>0.84</v>
+        <v>0.73</v>
       </c>
       <c r="G165" t="n">
-        <v>0.84</v>
+        <v>0.73</v>
       </c>
       <c r="H165" t="n">
         <v>0.7</v>
@@ -10839,7 +10839,7 @@
         <v>0.87</v>
       </c>
       <c r="J165" t="n">
-        <v>0.8165</v>
+        <v>0.745</v>
       </c>
       <c r="K165" t="n">
         <v>2</v>
@@ -10890,10 +10890,10 @@
         </is>
       </c>
       <c r="F166" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G166" t="n">
-        <v>0.93</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H166" t="n">
         <v>0.86</v>
@@ -10902,7 +10902,7 @@
         <v>0.84</v>
       </c>
       <c r="J166" t="n">
-        <v>0.9055</v>
+        <v>0.8245</v>
       </c>
       <c r="K166" t="n">
         <v>1</v>
@@ -10953,10 +10953,10 @@
         </is>
       </c>
       <c r="F167" t="n">
-        <v>0.91</v>
+        <v>0.79</v>
       </c>
       <c r="G167" t="n">
-        <v>0.91</v>
+        <v>0.79</v>
       </c>
       <c r="H167" t="n">
         <v>0.7</v>
@@ -10965,7 +10965,7 @@
         <v>0.87</v>
       </c>
       <c r="J167" t="n">
-        <v>0.862</v>
+        <v>0.784</v>
       </c>
       <c r="K167" t="n">
         <v>3</v>
@@ -11016,10 +11016,10 @@
         </is>
       </c>
       <c r="F168" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G168" t="n">
-        <v>0.93</v>
+        <v>0.82</v>
       </c>
       <c r="H168" t="n">
         <v>1</v>
@@ -11028,7 +11028,7 @@
         <v>0.87</v>
       </c>
       <c r="J168" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.8605</v>
       </c>
       <c r="K168" t="n">
         <v>1</v>
@@ -11079,10 +11079,10 @@
         </is>
       </c>
       <c r="F169" t="n">
-        <v>0.96</v>
+        <v>0.83</v>
       </c>
       <c r="G169" t="n">
-        <v>0.95</v>
+        <v>0.83</v>
       </c>
       <c r="H169" t="n">
         <v>0.78</v>
@@ -11091,7 +11091,7 @@
         <v>0.87</v>
       </c>
       <c r="J169" t="n">
-        <v>0.907</v>
+        <v>0.826</v>
       </c>
       <c r="K169" t="n">
         <v>2</v>
@@ -11142,10 +11142,10 @@
         </is>
       </c>
       <c r="F170" t="n">
-        <v>0.47</v>
+        <v>0.4</v>
       </c>
       <c r="G170" t="n">
-        <v>0.48</v>
+        <v>0.41</v>
       </c>
       <c r="H170" t="n">
         <v>0.67</v>
@@ -11154,7 +11154,7 @@
         <v>0.77</v>
       </c>
       <c r="J170" t="n">
-        <v>0.5585</v>
+        <v>0.513</v>
       </c>
       <c r="K170" t="n">
         <v>3</v>
@@ -11205,10 +11205,10 @@
         </is>
       </c>
       <c r="F171" t="n">
-        <v>0.52</v>
+        <v>0.44</v>
       </c>
       <c r="G171" t="n">
-        <v>0.53</v>
+        <v>0.46</v>
       </c>
       <c r="H171" t="n">
         <v>1</v>
@@ -11217,7 +11217,7 @@
         <v>0.77</v>
       </c>
       <c r="J171" t="n">
-        <v>0.657</v>
+        <v>0.6085</v>
       </c>
       <c r="K171" t="n">
         <v>1</v>
@@ -11268,10 +11268,10 @@
         </is>
       </c>
       <c r="F172" t="n">
-        <v>0.58</v>
+        <v>0.49</v>
       </c>
       <c r="G172" t="n">
-        <v>0.58</v>
+        <v>0.5</v>
       </c>
       <c r="H172" t="n">
         <v>0.67</v>
@@ -11280,7 +11280,7 @@
         <v>0.84</v>
       </c>
       <c r="J172" t="n">
-        <v>0.637</v>
+        <v>0.582</v>
       </c>
       <c r="K172" t="n">
         <v>2</v>
@@ -11331,10 +11331,10 @@
         </is>
       </c>
       <c r="F173" t="n">
-        <v>0.64</v>
+        <v>0.55</v>
       </c>
       <c r="G173" t="n">
-        <v>0.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H173" t="n">
         <v>0.73</v>
@@ -11343,7 +11343,7 @@
         <v>0.84</v>
       </c>
       <c r="J173" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.633</v>
       </c>
       <c r="K173" t="n">
         <v>3</v>
@@ -11394,10 +11394,10 @@
         </is>
       </c>
       <c r="F174" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.59</v>
       </c>
       <c r="G174" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="H174" t="n">
         <v>0.92</v>
@@ -11406,7 +11406,7 @@
         <v>0.84</v>
       </c>
       <c r="J174" t="n">
-        <v>0.7585</v>
+        <v>0.697</v>
       </c>
       <c r="K174" t="n">
         <v>1</v>
@@ -11457,10 +11457,10 @@
         </is>
       </c>
       <c r="F175" t="n">
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
       <c r="G175" t="n">
-        <v>0.73</v>
+        <v>0.63</v>
       </c>
       <c r="H175" t="n">
         <v>0.51</v>
@@ -11469,7 +11469,7 @@
         <v>0.87</v>
       </c>
       <c r="J175" t="n">
-        <v>0.707</v>
+        <v>0.642</v>
       </c>
       <c r="K175" t="n">
         <v>2</v>
@@ -11520,10 +11520,10 @@
         </is>
       </c>
       <c r="F176" t="n">
-        <v>0.73</v>
+        <v>0.98</v>
       </c>
       <c r="G176" t="n">
-        <v>0.73</v>
+        <v>0.98</v>
       </c>
       <c r="H176" t="n">
         <v>0.15</v>
@@ -11532,7 +11532,7 @@
         <v>0.65</v>
       </c>
       <c r="J176" t="n">
-        <v>0.602</v>
+        <v>0.7645</v>
       </c>
       <c r="K176" t="n">
         <v>3</v>
@@ -11583,10 +11583,10 @@
         </is>
       </c>
       <c r="F177" t="n">
-        <v>0.65</v>
+        <v>0.9</v>
       </c>
       <c r="G177" t="n">
-        <v>0.65</v>
+        <v>0.9</v>
       </c>
       <c r="H177" t="n">
         <v>0.61</v>
@@ -11595,7 +11595,7 @@
         <v>0.65</v>
       </c>
       <c r="J177" t="n">
-        <v>0.642</v>
+        <v>0.8045</v>
       </c>
       <c r="K177" t="n">
         <v>2</v>
@@ -11646,10 +11646,10 @@
         </is>
       </c>
       <c r="F178" t="n">
-        <v>0.58</v>
+        <v>0.85</v>
       </c>
       <c r="G178" t="n">
-        <v>0.59</v>
+        <v>0.85</v>
       </c>
       <c r="H178" t="n">
         <v>0.86</v>
@@ -11658,7 +11658,7 @@
         <v>0.65</v>
       </c>
       <c r="J178" t="n">
-        <v>0.65</v>
+        <v>0.822</v>
       </c>
       <c r="K178" t="n">
         <v>1</v>
@@ -11898,10 +11898,10 @@
         </is>
       </c>
       <c r="F182" t="n">
-        <v>0.57</v>
+        <v>0.86</v>
       </c>
       <c r="G182" t="n">
-        <v>0.58</v>
+        <v>0.86</v>
       </c>
       <c r="H182" t="n">
         <v>0.41</v>
@@ -11910,7 +11910,7 @@
         <v>0.65</v>
       </c>
       <c r="J182" t="n">
-        <v>0.5535</v>
+        <v>0.7385</v>
       </c>
       <c r="K182" t="n">
         <v>3</v>
@@ -11961,10 +11961,10 @@
         </is>
       </c>
       <c r="F183" t="n">
-        <v>0.51</v>
+        <v>0.8</v>
       </c>
       <c r="G183" t="n">
-        <v>0.51</v>
+        <v>0.8</v>
       </c>
       <c r="H183" t="n">
         <v>0.7</v>
@@ -11973,7 +11973,7 @@
         <v>0.65</v>
       </c>
       <c r="J183" t="n">
-        <v>0.569</v>
+        <v>0.7575</v>
       </c>
       <c r="K183" t="n">
         <v>2</v>
@@ -12024,10 +12024,10 @@
         </is>
       </c>
       <c r="F184" t="n">
-        <v>0.44</v>
+        <v>0.74</v>
       </c>
       <c r="G184" t="n">
-        <v>0.45</v>
+        <v>0.74</v>
       </c>
       <c r="H184" t="n">
         <v>0.93</v>
@@ -12036,7 +12036,7 @@
         <v>0.65</v>
       </c>
       <c r="J184" t="n">
-        <v>0.573</v>
+        <v>0.7645</v>
       </c>
       <c r="K184" t="n">
         <v>1</v>
@@ -12087,10 +12087,10 @@
         </is>
       </c>
       <c r="F185" t="n">
-        <v>0.38</v>
+        <v>0.73</v>
       </c>
       <c r="G185" t="n">
-        <v>0.4</v>
+        <v>0.74</v>
       </c>
       <c r="H185" t="n">
         <v>0.02</v>
@@ -12099,7 +12099,7 @@
         <v>0.55</v>
       </c>
       <c r="J185" t="n">
-        <v>0.3405</v>
+        <v>0.5645</v>
       </c>
       <c r="K185" t="n">
         <v>3</v>
@@ -12150,10 +12150,10 @@
         </is>
       </c>
       <c r="F186" t="n">
-        <v>0.31</v>
+        <v>0.67</v>
       </c>
       <c r="G186" t="n">
-        <v>0.32</v>
+        <v>0.67</v>
       </c>
       <c r="H186" t="n">
         <v>0.45</v>
@@ -12162,7 +12162,7 @@
         <v>0.65</v>
       </c>
       <c r="J186" t="n">
-        <v>0.3925</v>
+        <v>0.623</v>
       </c>
       <c r="K186" t="n">
         <v>2</v>
@@ -12213,10 +12213,10 @@
         </is>
       </c>
       <c r="F187" t="n">
-        <v>0.22</v>
+        <v>0.6</v>
       </c>
       <c r="G187" t="n">
-        <v>0.25</v>
+        <v>0.61</v>
       </c>
       <c r="H187" t="n">
         <v>0.76</v>
@@ -12225,7 +12225,7 @@
         <v>0.65</v>
       </c>
       <c r="J187" t="n">
-        <v>0.403</v>
+        <v>0.643</v>
       </c>
       <c r="K187" t="n">
         <v>1</v>
@@ -12276,10 +12276,10 @@
         </is>
       </c>
       <c r="F188" t="n">
-        <v>0.84</v>
+        <v>0.99</v>
       </c>
       <c r="G188" t="n">
-        <v>0.84</v>
+        <v>0.99</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -12288,7 +12288,7 @@
         <v>0.15</v>
       </c>
       <c r="J188" t="n">
-        <v>0.5685</v>
+        <v>0.666</v>
       </c>
       <c r="K188" t="n">
         <v>3</v>
@@ -12339,10 +12339,10 @@
         </is>
       </c>
       <c r="F189" t="n">
-        <v>0.8</v>
+        <v>0.96</v>
       </c>
       <c r="G189" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -12351,7 +12351,7 @@
         <v>0.44</v>
       </c>
       <c r="J189" t="n">
-        <v>0.586</v>
+        <v>0.6865</v>
       </c>
       <c r="K189" t="n">
         <v>2</v>
@@ -12402,10 +12402,10 @@
         </is>
       </c>
       <c r="F190" t="n">
-        <v>0.76</v>
+        <v>0.92</v>
       </c>
       <c r="G190" t="n">
-        <v>0.76</v>
+        <v>0.92</v>
       </c>
       <c r="H190" t="n">
         <v>0.41</v>
@@ -12414,7 +12414,7 @@
         <v>0.65</v>
       </c>
       <c r="J190" t="n">
-        <v>0.6735</v>
+        <v>0.7775</v>
       </c>
       <c r="K190" t="n">
         <v>1</v>
@@ -12465,10 +12465,10 @@
         </is>
       </c>
       <c r="F191" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="G191" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="H191" t="n">
         <v>0.41</v>
@@ -12477,7 +12477,7 @@
         <v>0.65</v>
       </c>
       <c r="J191" t="n">
-        <v>0.7125</v>
+        <v>0.8295</v>
       </c>
       <c r="K191" t="n">
         <v>3</v>
@@ -12528,10 +12528,10 @@
         </is>
       </c>
       <c r="F192" t="n">
-        <v>0.77</v>
+        <v>0.96</v>
       </c>
       <c r="G192" t="n">
-        <v>0.77</v>
+        <v>0.96</v>
       </c>
       <c r="H192" t="n">
         <v>0.7</v>
@@ -12540,7 +12540,7 @@
         <v>0.65</v>
       </c>
       <c r="J192" t="n">
-        <v>0.738</v>
+        <v>0.8615</v>
       </c>
       <c r="K192" t="n">
         <v>2</v>
@@ -12591,10 +12591,10 @@
         </is>
       </c>
       <c r="F193" t="n">
-        <v>0.72</v>
+        <v>0.92</v>
       </c>
       <c r="G193" t="n">
-        <v>0.72</v>
+        <v>0.92</v>
       </c>
       <c r="H193" t="n">
         <v>0.93</v>
@@ -12603,7 +12603,7 @@
         <v>0.65</v>
       </c>
       <c r="J193" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.8815</v>
       </c>
       <c r="K193" t="n">
         <v>1</v>
@@ -12654,10 +12654,10 @@
         </is>
       </c>
       <c r="F194" t="n">
-        <v>0.25</v>
+        <v>0.61</v>
       </c>
       <c r="G194" t="n">
-        <v>0.28</v>
+        <v>0.62</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -12666,7 +12666,7 @@
         <v>0.31</v>
       </c>
       <c r="J194" t="n">
-        <v>0.2195</v>
+        <v>0.4465</v>
       </c>
       <c r="K194" t="n">
         <v>3</v>
@@ -12717,10 +12717,10 @@
         </is>
       </c>
       <c r="F195" t="n">
-        <v>0.15</v>
+        <v>0.55</v>
       </c>
       <c r="G195" t="n">
-        <v>0.21</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H195" t="n">
         <v>0.29</v>
@@ -12729,7 +12729,7 @@
         <v>0.65</v>
       </c>
       <c r="J195" t="n">
-        <v>0.274</v>
+        <v>0.5165</v>
       </c>
       <c r="K195" t="n">
         <v>2</v>
@@ -12780,10 +12780,10 @@
         </is>
       </c>
       <c r="F196" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="G196" t="n">
-        <v>0.14</v>
+        <v>0.49</v>
       </c>
       <c r="H196" t="n">
         <v>0.61</v>
@@ -12792,7 +12792,7 @@
         <v>0.65</v>
       </c>
       <c r="J196" t="n">
-        <v>0.2895</v>
+        <v>0.535</v>
       </c>
       <c r="K196" t="n">
         <v>1</v>
@@ -12843,10 +12843,10 @@
         </is>
       </c>
       <c r="F197" t="n">
-        <v>0.17</v>
+        <v>0.57</v>
       </c>
       <c r="G197" t="n">
-        <v>0.3</v>
+        <v>0.57</v>
       </c>
       <c r="H197" t="n">
         <v>0.15</v>
@@ -12855,7 +12855,7 @@
         <v>0.55</v>
       </c>
       <c r="J197" t="n">
-        <v>0.2685</v>
+        <v>0.483</v>
       </c>
       <c r="K197" t="n">
         <v>3</v>
@@ -12906,10 +12906,10 @@
         </is>
       </c>
       <c r="F198" t="n">
-        <v>0.1</v>
+        <v>0.51</v>
       </c>
       <c r="G198" t="n">
-        <v>0.24</v>
+        <v>0.52</v>
       </c>
       <c r="H198" t="n">
         <v>0.51</v>
@@ -12918,7 +12918,7 @@
         <v>0.65</v>
       </c>
       <c r="J198" t="n">
-        <v>0.3135</v>
+        <v>0.5345</v>
       </c>
       <c r="K198" t="n">
         <v>2</v>
@@ -12969,10 +12969,10 @@
         </is>
       </c>
       <c r="F199" t="n">
-        <v>0.06</v>
+        <v>0.46</v>
       </c>
       <c r="G199" t="n">
-        <v>0.18</v>
+        <v>0.47</v>
       </c>
       <c r="H199" t="n">
         <v>0.78</v>
@@ -12981,7 +12981,7 @@
         <v>0.65</v>
       </c>
       <c r="J199" t="n">
-        <v>0.3345</v>
+        <v>0.556</v>
       </c>
       <c r="K199" t="n">
         <v>1</v>
@@ -13032,10 +13032,10 @@
         </is>
       </c>
       <c r="F200" t="n">
-        <v>0.76</v>
+        <v>0.96</v>
       </c>
       <c r="G200" t="n">
-        <v>0.75</v>
+        <v>0.96</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -13044,7 +13044,7 @@
         <v>0.31</v>
       </c>
       <c r="J200" t="n">
-        <v>0.537</v>
+        <v>0.6705</v>
       </c>
       <c r="K200" t="n">
         <v>3</v>
@@ -13095,10 +13095,10 @@
         </is>
       </c>
       <c r="F201" t="n">
-        <v>0.7</v>
+        <v>0.92</v>
       </c>
       <c r="G201" t="n">
-        <v>0.7</v>
+        <v>0.92</v>
       </c>
       <c r="H201" t="n">
         <v>0.29</v>
@@ -13107,7 +13107,7 @@
         <v>0.65</v>
       </c>
       <c r="J201" t="n">
-        <v>0.6105</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="K201" t="n">
         <v>2</v>
@@ -13158,10 +13158,10 @@
         </is>
       </c>
       <c r="F202" t="n">
-        <v>0.65</v>
+        <v>0.87</v>
       </c>
       <c r="G202" t="n">
-        <v>0.65</v>
+        <v>0.87</v>
       </c>
       <c r="H202" t="n">
         <v>0.61</v>
@@ -13170,7 +13170,7 @@
         <v>0.65</v>
       </c>
       <c r="J202" t="n">
-        <v>0.642</v>
+        <v>0.785</v>
       </c>
       <c r="K202" t="n">
         <v>1</v>
@@ -13221,10 +13221,10 @@
         </is>
       </c>
       <c r="F203" t="n">
-        <v>0.09</v>
+        <v>0.53</v>
       </c>
       <c r="G203" t="n">
-        <v>0.11</v>
+        <v>0.54</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
@@ -13233,7 +13233,7 @@
         <v>0.55</v>
       </c>
       <c r="J203" t="n">
-        <v>0.148</v>
+        <v>0.4305</v>
       </c>
       <c r="K203" t="n">
         <v>3</v>
@@ -13284,10 +13284,10 @@
         </is>
       </c>
       <c r="F204" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="G204" t="n">
-        <v>0.03</v>
+        <v>0.46</v>
       </c>
       <c r="H204" t="n">
         <v>0.38</v>
@@ -13296,7 +13296,7 @@
         <v>0.65</v>
       </c>
       <c r="J204" t="n">
-        <v>0.184</v>
+        <v>0.4695</v>
       </c>
       <c r="K204" t="n">
         <v>2</v>
@@ -13347,10 +13347,10 @@
         </is>
       </c>
       <c r="F205" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="G205" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="H205" t="n">
         <v>0.73</v>
@@ -13359,7 +13359,7 @@
         <v>0.65</v>
       </c>
       <c r="J205" t="n">
-        <v>0.2435</v>
+        <v>0.494</v>
       </c>
       <c r="K205" t="n">
         <v>1</v>
@@ -13410,10 +13410,10 @@
         </is>
       </c>
       <c r="F206" t="n">
-        <v>0.55</v>
+        <v>0.47</v>
       </c>
       <c r="G206" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="H206" t="n">
         <v>0.78</v>
@@ -13422,7 +13422,7 @@
         <v>0.84</v>
       </c>
       <c r="J206" t="n">
-        <v>0.643</v>
+        <v>0.591</v>
       </c>
       <c r="K206" t="n">
         <v>3</v>
@@ -13473,10 +13473,10 @@
         </is>
       </c>
       <c r="F207" t="n">
-        <v>0.6</v>
+        <v>0.51</v>
       </c>
       <c r="G207" t="n">
-        <v>0.6</v>
+        <v>0.52</v>
       </c>
       <c r="H207" t="n">
         <v>1</v>
@@ -13485,7 +13485,7 @@
         <v>0.84</v>
       </c>
       <c r="J207" t="n">
-        <v>0.716</v>
+        <v>0.661</v>
       </c>
       <c r="K207" t="n">
         <v>1</v>
@@ -13536,10 +13536,10 @@
         </is>
       </c>
       <c r="F208" t="n">
-        <v>0.64</v>
+        <v>0.55</v>
       </c>
       <c r="G208" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H208" t="n">
         <v>0.78</v>
@@ -13548,7 +13548,7 @@
         <v>0.84</v>
       </c>
       <c r="J208" t="n">
-        <v>0.7015</v>
+        <v>0.643</v>
       </c>
       <c r="K208" t="n">
         <v>2</v>
@@ -13599,10 +13599,10 @@
         </is>
       </c>
       <c r="F209" t="n">
-        <v>0.65</v>
+        <v>0.55</v>
       </c>
       <c r="G209" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H209" t="n">
         <v>0.86</v>
@@ -13611,7 +13611,7 @@
         <v>0.84</v>
       </c>
       <c r="J209" t="n">
-        <v>0.7205</v>
+        <v>0.659</v>
       </c>
       <c r="K209" t="n">
         <v>1</v>
@@ -13662,10 +13662,10 @@
         </is>
       </c>
       <c r="F210" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.59</v>
       </c>
       <c r="G210" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="H210" t="n">
         <v>0.61</v>
@@ -13674,7 +13674,7 @@
         <v>0.84</v>
       </c>
       <c r="J210" t="n">
-        <v>0.6965</v>
+        <v>0.635</v>
       </c>
       <c r="K210" t="n">
         <v>2</v>
@@ -13725,10 +13725,10 @@
         </is>
       </c>
       <c r="F211" t="n">
-        <v>0.72</v>
+        <v>0.62</v>
       </c>
       <c r="G211" t="n">
-        <v>0.72</v>
+        <v>0.63</v>
       </c>
       <c r="H211" t="n">
         <v>0.29</v>
@@ -13737,7 +13737,7 @@
         <v>0.65</v>
       </c>
       <c r="J211" t="n">
-        <v>0.6235000000000001</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K211" t="n">
         <v>3</v>
